--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1596,132 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125338805</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartabborrtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>780772</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7340787</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,6 +1722,7407 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125374131</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>780341</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7341192</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125374105</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>780579</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7341020</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125376205</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>780453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7341309</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125378911</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>780332</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7341195</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125374103</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>780777</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7340841</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125368568</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>780597</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7341251</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125368566</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90051</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>780905</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7340863</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125368579</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>780564</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7341334</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125374116</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>780554</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7340907</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125374084</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>780527</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7341044</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125374096</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>780394</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7341123</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125378920</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>780413</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7341084</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125378929</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>780910</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7340820</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125368569</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>780564</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7341334</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125368578</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>780865</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7340858</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125374075</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>780877</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7340946</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125374123</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>780428</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7341058</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125374094</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>780904</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7340832</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125368586</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>780564</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7341334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125368590</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>780707</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7340834</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125368573</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>658</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>780591</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7341254</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125374101</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>780924</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7340886</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125374099</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>780470</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7341026</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125368563</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>780865</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7340858</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125368593</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77738</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>780561</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7340968</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125368592</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>308</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>780845</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7340863</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125374132</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>780904</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7340872</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125374114</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>780332</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7341182</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125378928</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>780881</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7340820</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125378914</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>780360</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7341113</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125368564</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90051</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>780518</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7341011</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125374119</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91413</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>780501</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7341325</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125374129</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>780323</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7341197</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125378916</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>780956</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7340785</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125374078</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78834</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>780705</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7340829</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125376207</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>780564</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7340973</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125368595</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78194</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>780561</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7340968</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125378917</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>780909</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7340823</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125368582</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91172</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>780634</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7340886</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125376197</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>780912</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7340859</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125376199</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>780542</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7341352</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125368562</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>780722</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7340838</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125374109</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>780890</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7340825</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125368591</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>780620</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7340897</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125374111</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>780311</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7341211</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125374090</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>780353</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7341186</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125376201</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>780318</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7341215</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125374118</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>780370</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7341315</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristina  Berglund</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125378905</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>780354</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7341159</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125378926</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>780493</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7341109</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125368575</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92490</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>780910</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7340862</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125376203</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>780331</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7341207</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125378915</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>780825</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7340795</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125378924</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>780766</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7340885</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125378906</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>780955</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7340788</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125374127</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>780447</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7341241</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125374092</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>780743</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7340811</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125374086</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>780521</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7341051</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125378930</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>780354</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7341240</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125368571</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92321</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>780646</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7340861</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125368580</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>780337</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7341192</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>100-tals</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125368577</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>780480</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7341033</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125374080</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>780787</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7340766</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125368587</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>780344</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7341144</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125368584</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>780566</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7341030</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125378902</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>780545</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7341029</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125374108</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>658</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Boden, Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>780597</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7341251</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Maud Söderholm Häll</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125374124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>780876</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7340837</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Peter Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Peter Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125378919</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>780397</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7341092</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125368574</v>
+      </c>
+      <c r="B80" t="n">
+        <v>56725</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>780624</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7340950</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125374125</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91413</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>780339</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7341191</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Peter Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Peter Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125374088</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>780658</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7340942</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125374131</v>
+        <v>125374105</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,41 +1736,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780341</v>
+        <v>780579</v>
       </c>
       <c r="R11" t="n">
-        <v>7341192</v>
+        <v>7341020</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1814,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125374105</v>
+        <v>125374078</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>78834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780579</v>
+        <v>780705</v>
       </c>
       <c r="R12" t="n">
-        <v>7341020</v>
+        <v>7340829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,22 +1916,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125376205</v>
+        <v>125374080</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,21 +1944,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780453</v>
+        <v>780787</v>
       </c>
       <c r="R13" t="n">
-        <v>7341309</v>
+        <v>7340766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,14 +2016,24 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125378911</v>
+        <v>125374123</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,25 +2042,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780332</v>
+        <v>780428</v>
       </c>
       <c r="R14" t="n">
-        <v>7341195</v>
+        <v>7341058</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2110,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,22 +2125,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125374103</v>
+        <v>125374099</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,34 +2153,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780777</v>
+        <v>780470</v>
       </c>
       <c r="R15" t="n">
-        <v>7340841</v>
+        <v>7341026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,11 +2215,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2222,22 +2227,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125368568</v>
+        <v>125368587</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,21 +2255,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2274,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780597</v>
+        <v>780344</v>
       </c>
       <c r="R16" t="n">
-        <v>7341251</v>
+        <v>7341144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125368566</v>
+        <v>125374092</v>
       </c>
       <c r="B17" t="n">
-        <v>90051</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2376,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780905</v>
+        <v>780743</v>
       </c>
       <c r="R17" t="n">
-        <v>7340863</v>
+        <v>7340811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2431,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125368579</v>
+        <v>125378924</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2450,25 +2455,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,13 +2483,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780564</v>
+        <v>780766</v>
       </c>
       <c r="R18" t="n">
-        <v>7341334</v>
+        <v>7340885</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2528,19 +2533,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125374116</v>
+        <v>125378929</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2576,17 +2581,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780554</v>
+        <v>780910</v>
       </c>
       <c r="R19" t="n">
-        <v>7340907</v>
+        <v>7340820</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,22 +2635,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374084</v>
+        <v>125374124</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,21 +2663,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2682,13 +2687,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780527</v>
+        <v>780876</v>
       </c>
       <c r="R20" t="n">
-        <v>7341044</v>
+        <v>7340837</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,22 +2737,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125374096</v>
+        <v>125374109</v>
       </c>
       <c r="B21" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,21 +2765,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780394</v>
+        <v>780890</v>
       </c>
       <c r="R21" t="n">
-        <v>7341123</v>
+        <v>7340825</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,6 +2827,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2834,22 +2844,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125378920</v>
+        <v>125378911</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780413</v>
+        <v>780332</v>
       </c>
       <c r="R22" t="n">
-        <v>7341084</v>
+        <v>7341195</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,13 +2934,17 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2949,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125378929</v>
+        <v>125374103</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,41 +2975,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780910</v>
+        <v>780777</v>
       </c>
       <c r="R23" t="n">
-        <v>7340820</v>
+        <v>7340841</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3025,6 +3039,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,22 +3058,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125368569</v>
+        <v>125378917</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,41 +3082,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780564</v>
+        <v>780909</v>
       </c>
       <c r="R24" t="n">
-        <v>7341334</v>
+        <v>7340823</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3127,6 +3150,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,22 +3169,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125368578</v>
+        <v>125368569</v>
       </c>
       <c r="B25" t="n">
-        <v>78546</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3169,21 +3197,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780865</v>
+        <v>780564</v>
       </c>
       <c r="R25" t="n">
-        <v>7340858</v>
+        <v>7341334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,10 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374075</v>
+        <v>125368590</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3271,54 +3299,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780877</v>
+        <v>780707</v>
       </c>
       <c r="R26" t="n">
-        <v>7340946</v>
+        <v>7340834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,19 +3356,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,22 +3373,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125374123</v>
+        <v>125374119</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>91413</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,21 +3401,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3427,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780428</v>
+        <v>780501</v>
       </c>
       <c r="R27" t="n">
-        <v>7341058</v>
+        <v>7341325</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,11 +3463,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3480,11 +3473,21 @@
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristina Berglund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristina Berglund</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374094</v>
+        <v>125368586</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3524,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780904</v>
+        <v>780564</v>
       </c>
       <c r="R28" t="n">
-        <v>7340832</v>
+        <v>7341334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,22 +3577,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125368586</v>
+        <v>125368562</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3602,21 +3605,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3626,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780564</v>
+        <v>780722</v>
       </c>
       <c r="R29" t="n">
-        <v>7341334</v>
+        <v>7340838</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125368590</v>
+        <v>125368579</v>
       </c>
       <c r="B30" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3700,25 +3703,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3728,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780707</v>
+        <v>780564</v>
       </c>
       <c r="R30" t="n">
-        <v>7340834</v>
+        <v>7341334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3790,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125368573</v>
+        <v>125378915</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,37 +3809,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780591</v>
+        <v>780825</v>
       </c>
       <c r="R31" t="n">
-        <v>7341254</v>
+        <v>7340795</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3866,6 +3873,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,22 +3892,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125374101</v>
+        <v>125368591</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3904,38 +3916,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780924</v>
+        <v>780620</v>
       </c>
       <c r="R32" t="n">
-        <v>7340886</v>
+        <v>7340897</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,11 +3982,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3987,19 +3994,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125374099</v>
+        <v>125378930</v>
       </c>
       <c r="B33" t="n">
         <v>92293</v>
@@ -4039,13 +4046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780470</v>
+        <v>780354</v>
       </c>
       <c r="R33" t="n">
-        <v>7341026</v>
+        <v>7341240</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4089,22 +4096,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125368563</v>
+        <v>125374129</v>
       </c>
       <c r="B34" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4113,25 +4120,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4141,13 +4148,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780865</v>
+        <v>780323</v>
       </c>
       <c r="R34" t="n">
-        <v>7340858</v>
+        <v>7341197</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4191,22 +4198,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125368593</v>
+        <v>125374131</v>
       </c>
       <c r="B35" t="n">
-        <v>77738</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4215,25 +4222,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4243,13 +4250,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780561</v>
+        <v>780341</v>
       </c>
       <c r="R35" t="n">
-        <v>7340968</v>
+        <v>7341192</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4293,22 +4300,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125368592</v>
+        <v>125368578</v>
       </c>
       <c r="B36" t="n">
-        <v>74893</v>
+        <v>78546</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4321,21 +4328,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4345,10 +4352,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780845</v>
+        <v>780865</v>
       </c>
       <c r="R36" t="n">
-        <v>7340863</v>
+        <v>7340858</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4407,10 +4414,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125374132</v>
+        <v>125368574</v>
       </c>
       <c r="B37" t="n">
-        <v>92293</v>
+        <v>56725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4423,21 +4430,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>102613</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4447,13 +4454,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780904</v>
+        <v>780624</v>
       </c>
       <c r="R37" t="n">
-        <v>7340872</v>
+        <v>7340950</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4483,11 +4490,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,22 +4504,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374114</v>
+        <v>125378919</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4526,41 +4528,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780332</v>
+        <v>780397</v>
       </c>
       <c r="R38" t="n">
-        <v>7341182</v>
+        <v>7341092</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4592,39 +4594,35 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125378928</v>
+        <v>125378920</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4661,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780881</v>
+        <v>780413</v>
       </c>
       <c r="R39" t="n">
-        <v>7340820</v>
+        <v>7341084</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4705,6 +4703,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4723,10 +4722,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125378914</v>
+        <v>125368584</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4739,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4763,13 +4762,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780360</v>
+        <v>780566</v>
       </c>
       <c r="R40" t="n">
-        <v>7341113</v>
+        <v>7341030</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4813,22 +4812,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368564</v>
+        <v>125374108</v>
       </c>
       <c r="B41" t="n">
-        <v>90051</v>
+        <v>91299</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4841,34 +4840,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780518</v>
+        <v>780597</v>
       </c>
       <c r="R41" t="n">
-        <v>7341011</v>
+        <v>7341251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4915,22 +4914,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374119</v>
+        <v>125368564</v>
       </c>
       <c r="B42" t="n">
-        <v>91413</v>
+        <v>90051</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4939,25 +4938,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4217</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4967,10 +4966,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780501</v>
+        <v>780518</v>
       </c>
       <c r="R42" t="n">
-        <v>7341325</v>
+        <v>7341011</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,22 +5016,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374129</v>
+        <v>125378902</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5041,25 +5040,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5069,10 +5068,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780323</v>
+        <v>780545</v>
       </c>
       <c r="R43" t="n">
-        <v>7341197</v>
+        <v>7341029</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5119,22 +5118,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125378916</v>
+        <v>125378926</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5143,42 +5142,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780956</v>
+        <v>780493</v>
       </c>
       <c r="R44" t="n">
-        <v>7340785</v>
+        <v>7341109</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5211,11 +5206,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5242,10 +5232,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374078</v>
+        <v>125374127</v>
       </c>
       <c r="B45" t="n">
-        <v>78834</v>
+        <v>56722</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5258,21 +5248,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5282,13 +5272,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780705</v>
+        <v>780447</v>
       </c>
       <c r="R45" t="n">
-        <v>7340829</v>
+        <v>7341241</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5318,6 +5308,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5332,22 +5327,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125376207</v>
+        <v>125368566</v>
       </c>
       <c r="B46" t="n">
-        <v>92293</v>
+        <v>90051</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,25 +5351,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780564</v>
+        <v>780905</v>
       </c>
       <c r="R46" t="n">
-        <v>7340973</v>
+        <v>7340863</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,14 +5427,24 @@
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125368595</v>
+        <v>125378916</v>
       </c>
       <c r="B47" t="n">
-        <v>78194</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5448,41 +5453,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780561</v>
+        <v>780956</v>
       </c>
       <c r="R47" t="n">
-        <v>7340968</v>
+        <v>7340785</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5512,6 +5521,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5526,22 +5540,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125378917</v>
+        <v>125368592</v>
       </c>
       <c r="B48" t="n">
-        <v>56722</v>
+        <v>74893</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5550,45 +5564,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780909</v>
+        <v>780845</v>
       </c>
       <c r="R48" t="n">
-        <v>7340823</v>
+        <v>7340863</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5618,11 +5628,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5637,22 +5642,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125368582</v>
+        <v>125376207</v>
       </c>
       <c r="B49" t="n">
-        <v>91172</v>
+        <v>92293</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5661,41 +5666,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780634</v>
+        <v>780564</v>
       </c>
       <c r="R49" t="n">
-        <v>7340886</v>
+        <v>7340973</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5736,29 +5738,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125376197</v>
+        <v>125368568</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5771,21 +5772,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780912</v>
+        <v>780597</v>
       </c>
       <c r="R50" t="n">
-        <v>7340859</v>
+        <v>7341251</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5843,14 +5844,24 @@
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125376199</v>
+        <v>125368573</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5859,25 +5870,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5887,10 +5898,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780542</v>
+        <v>780591</v>
       </c>
       <c r="R51" t="n">
-        <v>7341352</v>
+        <v>7341254</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5935,14 +5946,24 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125368562</v>
+        <v>125374116</v>
       </c>
       <c r="B52" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5955,34 +5976,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780722</v>
+        <v>780554</v>
       </c>
       <c r="R52" t="n">
-        <v>7340838</v>
+        <v>7340907</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6029,22 +6050,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125374109</v>
+        <v>125378914</v>
       </c>
       <c r="B53" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,25 +6074,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6081,13 +6102,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780890</v>
+        <v>780360</v>
       </c>
       <c r="R53" t="n">
-        <v>7340825</v>
+        <v>7341113</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6117,11 +6138,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6136,22 +6152,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125368591</v>
+        <v>125374114</v>
       </c>
       <c r="B54" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6160,38 +6176,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780620</v>
+        <v>780332</v>
       </c>
       <c r="R54" t="n">
-        <v>7340897</v>
+        <v>7341182</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6226,6 +6242,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6238,22 +6259,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374111</v>
+        <v>125374125</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>91413</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6262,41 +6283,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780311</v>
+        <v>780339</v>
       </c>
       <c r="R55" t="n">
-        <v>7341211</v>
+        <v>7341191</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6326,11 +6347,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6345,22 +6361,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374090</v>
+        <v>125374132</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6369,25 +6385,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,13 +6413,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780353</v>
+        <v>780904</v>
       </c>
       <c r="R56" t="n">
-        <v>7341186</v>
+        <v>7340872</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6433,6 +6449,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6447,22 +6468,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125376201</v>
+        <v>125374088</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6471,25 +6492,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6499,10 +6520,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780318</v>
+        <v>780658</v>
       </c>
       <c r="R57" t="n">
-        <v>7341215</v>
+        <v>7340942</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6547,14 +6568,24 @@
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125374118</v>
+        <v>125374075</v>
       </c>
       <c r="B58" t="n">
-        <v>92293</v>
+        <v>57513</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6563,38 +6594,58 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780370</v>
+        <v>780877</v>
       </c>
       <c r="R58" t="n">
-        <v>7341315</v>
+        <v>7340946</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6624,14 +6675,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>4 st</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6646,22 +6702,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristina  Berglund</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125378905</v>
+        <v>125374111</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6670,45 +6726,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780354</v>
+        <v>780311</v>
       </c>
       <c r="R59" t="n">
-        <v>7341159</v>
+        <v>7341211</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6742,7 +6794,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ring hack</t>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6757,22 +6809,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125378926</v>
+        <v>125368580</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6781,25 +6833,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6809,13 +6861,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780493</v>
+        <v>780337</v>
       </c>
       <c r="R60" t="n">
-        <v>7341109</v>
+        <v>7341192</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6845,6 +6897,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>100-tals</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6859,22 +6916,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125368575</v>
+        <v>125368577</v>
       </c>
       <c r="B61" t="n">
-        <v>92490</v>
+        <v>78546</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6887,21 +6944,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6911,10 +6968,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780910</v>
+        <v>780480</v>
       </c>
       <c r="R61" t="n">
-        <v>7340862</v>
+        <v>7341033</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6973,10 +7030,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125376203</v>
+        <v>125374094</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6985,25 +7042,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7013,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780331</v>
+        <v>780904</v>
       </c>
       <c r="R62" t="n">
-        <v>7341207</v>
+        <v>7340832</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7061,14 +7118,24 @@
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125378915</v>
+        <v>125368582</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>91172</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7077,31 +7144,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7109,13 +7175,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780825</v>
+        <v>780634</v>
       </c>
       <c r="R63" t="n">
-        <v>7340795</v>
+        <v>7340886</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7147,39 +7213,35 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125378924</v>
+        <v>125374084</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7192,21 +7254,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7216,13 +7278,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780766</v>
+        <v>780527</v>
       </c>
       <c r="R64" t="n">
-        <v>7340885</v>
+        <v>7341044</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7266,22 +7328,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125378906</v>
+        <v>125376201</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7290,25 +7352,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7318,13 +7380,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780955</v>
+        <v>780318</v>
       </c>
       <c r="R65" t="n">
-        <v>7340788</v>
+        <v>7341215</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7368,22 +7430,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125374127</v>
+        <v>125368595</v>
       </c>
       <c r="B66" t="n">
-        <v>56722</v>
+        <v>78194</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7392,25 +7454,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7420,13 +7482,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780447</v>
+        <v>780561</v>
       </c>
       <c r="R66" t="n">
-        <v>7341241</v>
+        <v>7340968</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7456,11 +7518,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7475,22 +7532,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374092</v>
+        <v>125374101</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7503,34 +7560,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780743</v>
+        <v>780924</v>
       </c>
       <c r="R67" t="n">
-        <v>7340811</v>
+        <v>7340886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7565,6 +7622,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7577,22 +7639,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125374086</v>
+        <v>125376203</v>
       </c>
       <c r="B68" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7601,25 +7663,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7629,10 +7691,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780521</v>
+        <v>780331</v>
       </c>
       <c r="R68" t="n">
-        <v>7341051</v>
+        <v>7341207</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7679,19 +7741,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125378930</v>
+        <v>125374096</v>
       </c>
       <c r="B69" t="n">
         <v>92293</v>
@@ -7731,13 +7793,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780354</v>
+        <v>780394</v>
       </c>
       <c r="R69" t="n">
-        <v>7341240</v>
+        <v>7341123</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7781,22 +7843,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125368571</v>
+        <v>125374118</v>
       </c>
       <c r="B70" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7805,25 +7867,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7833,10 +7895,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780646</v>
+        <v>780370</v>
       </c>
       <c r="R70" t="n">
-        <v>7340861</v>
+        <v>7341315</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7871,6 +7933,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7883,22 +7950,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125368580</v>
+        <v>125378928</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7907,25 +7974,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7935,13 +8002,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780337</v>
+        <v>780881</v>
       </c>
       <c r="R71" t="n">
-        <v>7341192</v>
+        <v>7340820</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7971,11 +8038,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7990,22 +8052,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125368577</v>
+        <v>125368563</v>
       </c>
       <c r="B72" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8018,21 +8080,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8042,10 +8104,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780480</v>
+        <v>780865</v>
       </c>
       <c r="R72" t="n">
-        <v>7341033</v>
+        <v>7340858</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8104,10 +8166,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125374080</v>
+        <v>125374090</v>
       </c>
       <c r="B73" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8120,21 +8182,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8206,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780787</v>
+        <v>780353</v>
       </c>
       <c r="R73" t="n">
-        <v>7340766</v>
+        <v>7341186</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8206,10 +8268,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125368587</v>
+        <v>125376197</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8222,21 +8284,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8246,10 +8308,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780344</v>
+        <v>780912</v>
       </c>
       <c r="R74" t="n">
-        <v>7341144</v>
+        <v>7340859</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8296,22 +8358,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125368584</v>
+        <v>125368571</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>92321</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8324,21 +8386,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8348,10 +8410,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780566</v>
+        <v>780646</v>
       </c>
       <c r="R75" t="n">
-        <v>7341030</v>
+        <v>7340861</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8410,10 +8472,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125378902</v>
+        <v>125376199</v>
       </c>
       <c r="B76" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8422,25 +8484,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8450,13 +8512,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780545</v>
+        <v>780542</v>
       </c>
       <c r="R76" t="n">
-        <v>7341029</v>
+        <v>7341352</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8500,22 +8562,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125374108</v>
+        <v>125368575</v>
       </c>
       <c r="B77" t="n">
-        <v>91299</v>
+        <v>92490</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8528,34 +8590,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780597</v>
+        <v>780910</v>
       </c>
       <c r="R77" t="n">
-        <v>7341251</v>
+        <v>7340862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8602,22 +8664,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374124</v>
+        <v>125368593</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>77738</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8630,21 +8692,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8654,13 +8716,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780876</v>
+        <v>780561</v>
       </c>
       <c r="R78" t="n">
-        <v>7340837</v>
+        <v>7340968</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8704,22 +8766,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125378919</v>
+        <v>125374086</v>
       </c>
       <c r="B79" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8732,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8756,13 +8818,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780397</v>
+        <v>780521</v>
       </c>
       <c r="R79" t="n">
-        <v>7341092</v>
+        <v>7341051</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8800,29 +8862,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125368574</v>
+        <v>125376205</v>
       </c>
       <c r="B80" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8831,25 +8892,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8859,10 +8920,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780624</v>
+        <v>780453</v>
       </c>
       <c r="R80" t="n">
-        <v>7340950</v>
+        <v>7341309</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8909,22 +8970,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374125</v>
+        <v>125378906</v>
       </c>
       <c r="B81" t="n">
-        <v>91413</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8933,25 +8994,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8961,10 +9022,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780339</v>
+        <v>780955</v>
       </c>
       <c r="R81" t="n">
-        <v>7341191</v>
+        <v>7340788</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9011,22 +9072,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125374088</v>
+        <v>125378905</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9039,37 +9100,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780658</v>
+        <v>780354</v>
       </c>
       <c r="R82" t="n">
-        <v>7340942</v>
+        <v>7341159</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9099,6 +9164,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9113,12 +9183,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125378911</v>
+        <v>125368569</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780332</v>
+        <v>780564</v>
       </c>
       <c r="R22" t="n">
-        <v>7341195</v>
+        <v>7341334</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2932,11 +2932,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,22 +2946,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125374103</v>
+        <v>125368590</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>78455</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,38 +2970,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780777</v>
+        <v>780707</v>
       </c>
       <c r="R23" t="n">
-        <v>7340841</v>
+        <v>7340834</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,11 +3036,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3058,22 +3048,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125378917</v>
+        <v>125374119</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>91413</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,41 +3076,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780909</v>
+        <v>780501</v>
       </c>
       <c r="R24" t="n">
-        <v>7340823</v>
+        <v>7341325</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,11 +3136,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,22 +3150,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125368569</v>
+        <v>125378911</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,21 +3178,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3221,13 +3202,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780564</v>
+        <v>780332</v>
       </c>
       <c r="R25" t="n">
-        <v>7341334</v>
+        <v>7341195</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3257,6 +3238,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3257,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125368590</v>
+        <v>125368562</v>
       </c>
       <c r="B26" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3299,21 +3285,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,10 +3309,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780707</v>
+        <v>780722</v>
       </c>
       <c r="R26" t="n">
-        <v>7340834</v>
+        <v>7340838</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,10 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125374119</v>
+        <v>125368586</v>
       </c>
       <c r="B27" t="n">
-        <v>91413</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,25 +3383,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3425,10 +3411,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780501</v>
+        <v>780564</v>
       </c>
       <c r="R27" t="n">
-        <v>7341325</v>
+        <v>7341334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,22 +3461,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125368586</v>
+        <v>125374103</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3499,38 +3485,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780564</v>
+        <v>780777</v>
       </c>
       <c r="R28" t="n">
-        <v>7341334</v>
+        <v>7340841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3565,6 +3551,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3577,22 +3568,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125368562</v>
+        <v>125378917</v>
       </c>
       <c r="B29" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3601,41 +3592,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780722</v>
+        <v>780909</v>
       </c>
       <c r="R29" t="n">
-        <v>7340838</v>
+        <v>7340823</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3665,6 +3660,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,12 +3679,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125378915</v>
+        <v>125368591</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3805,45 +3805,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780825</v>
+        <v>780620</v>
       </c>
       <c r="R31" t="n">
-        <v>7340795</v>
+        <v>7340897</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,11 +3869,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,19 +3883,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125368591</v>
+        <v>125378930</v>
       </c>
       <c r="B32" t="n">
         <v>92293</v>
@@ -3944,13 +3935,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780620</v>
+        <v>780354</v>
       </c>
       <c r="R32" t="n">
-        <v>7340897</v>
+        <v>7341240</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3994,22 +3985,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125378930</v>
+        <v>125374129</v>
       </c>
       <c r="B33" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4018,25 +4009,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4037,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780354</v>
+        <v>780323</v>
       </c>
       <c r="R33" t="n">
-        <v>7341240</v>
+        <v>7341197</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,19 +4087,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374129</v>
+        <v>125374131</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4148,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780323</v>
+        <v>780341</v>
       </c>
       <c r="R34" t="n">
-        <v>7341197</v>
+        <v>7341192</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4210,10 +4201,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125374131</v>
+        <v>125368578</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4222,25 +4213,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4250,13 +4241,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780341</v>
+        <v>780865</v>
       </c>
       <c r="R35" t="n">
-        <v>7341192</v>
+        <v>7340858</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4300,22 +4291,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125368578</v>
+        <v>125368574</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>56725</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4324,25 +4315,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4352,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780865</v>
+        <v>780624</v>
       </c>
       <c r="R36" t="n">
-        <v>7340858</v>
+        <v>7340950</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4414,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125368574</v>
+        <v>125378919</v>
       </c>
       <c r="B37" t="n">
-        <v>56725</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4426,25 +4417,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4454,13 +4445,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780624</v>
+        <v>780397</v>
       </c>
       <c r="R37" t="n">
-        <v>7340950</v>
+        <v>7341092</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4498,25 +4489,26 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125378919</v>
+        <v>125378920</v>
       </c>
       <c r="B38" t="n">
         <v>78547</v>
@@ -4556,10 +4548,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780397</v>
+        <v>780413</v>
       </c>
       <c r="R38" t="n">
-        <v>7341092</v>
+        <v>7341084</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4619,10 +4611,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125378920</v>
+        <v>125374108</v>
       </c>
       <c r="B39" t="n">
-        <v>78547</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4635,37 +4627,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780413</v>
+        <v>780597</v>
       </c>
       <c r="R39" t="n">
-        <v>7341084</v>
+        <v>7341251</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4703,19 +4695,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4824,10 +4815,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374108</v>
+        <v>125368564</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>90051</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4840,34 +4831,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780597</v>
+        <v>780518</v>
       </c>
       <c r="R41" t="n">
-        <v>7341251</v>
+        <v>7341011</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,22 +4905,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125368564</v>
+        <v>125378902</v>
       </c>
       <c r="B42" t="n">
-        <v>90051</v>
+        <v>79428</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4942,21 +4933,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4966,13 +4957,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780518</v>
+        <v>780545</v>
       </c>
       <c r="R42" t="n">
-        <v>7341011</v>
+        <v>7341029</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5016,22 +5007,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125378902</v>
+        <v>125378926</v>
       </c>
       <c r="B43" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5044,21 +5035,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5068,10 +5059,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780545</v>
+        <v>780493</v>
       </c>
       <c r="R43" t="n">
-        <v>7341029</v>
+        <v>7341109</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5130,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125378926</v>
+        <v>125374127</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,25 +5133,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5170,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780493</v>
+        <v>780447</v>
       </c>
       <c r="R44" t="n">
-        <v>7341109</v>
+        <v>7341241</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5208,6 +5199,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5220,22 +5216,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374127</v>
+        <v>125368566</v>
       </c>
       <c r="B45" t="n">
-        <v>56722</v>
+        <v>90051</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5244,25 +5240,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5272,13 +5268,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780447</v>
+        <v>780905</v>
       </c>
       <c r="R45" t="n">
-        <v>7341241</v>
+        <v>7340863</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5308,11 +5304,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5327,22 +5318,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125368566</v>
+        <v>125378916</v>
       </c>
       <c r="B46" t="n">
-        <v>90051</v>
+        <v>56722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,41 +5342,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780905</v>
+        <v>780956</v>
       </c>
       <c r="R46" t="n">
-        <v>7340863</v>
+        <v>7340785</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5415,6 +5410,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5429,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125378916</v>
+        <v>125368592</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>74893</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5453,45 +5453,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780956</v>
+        <v>780845</v>
       </c>
       <c r="R47" t="n">
-        <v>7340785</v>
+        <v>7340863</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5521,11 +5517,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5540,22 +5531,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125368592</v>
+        <v>125376207</v>
       </c>
       <c r="B48" t="n">
-        <v>74893</v>
+        <v>92293</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5564,25 +5555,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5583,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780845</v>
+        <v>780564</v>
       </c>
       <c r="R48" t="n">
-        <v>7340863</v>
+        <v>7340973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,22 +5633,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125376207</v>
+        <v>125368568</v>
       </c>
       <c r="B49" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5666,25 +5657,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5685,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780564</v>
+        <v>780597</v>
       </c>
       <c r="R49" t="n">
-        <v>7340973</v>
+        <v>7341251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,22 +5735,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125368568</v>
+        <v>125368573</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5772,21 +5763,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5796,10 +5787,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780597</v>
+        <v>780591</v>
       </c>
       <c r="R50" t="n">
-        <v>7341251</v>
+        <v>7341254</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5858,10 +5849,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125368573</v>
+        <v>125374116</v>
       </c>
       <c r="B51" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5874,34 +5865,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780591</v>
+        <v>780554</v>
       </c>
       <c r="R51" t="n">
-        <v>7341254</v>
+        <v>7340907</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5948,22 +5939,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374116</v>
+        <v>125374125</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>91413</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5972,41 +5963,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780554</v>
+        <v>780339</v>
       </c>
       <c r="R52" t="n">
-        <v>7340907</v>
+        <v>7341191</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,22 +6041,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125378914</v>
+        <v>125374114</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6074,41 +6065,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780360</v>
+        <v>780332</v>
       </c>
       <c r="R53" t="n">
-        <v>7341113</v>
+        <v>7341182</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6138,6 +6129,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6152,22 +6148,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374114</v>
+        <v>125374132</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6176,41 +6172,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780332</v>
+        <v>780904</v>
       </c>
       <c r="R54" t="n">
-        <v>7341182</v>
+        <v>7340872</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6244,7 +6240,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6259,22 +6255,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374125</v>
+        <v>125374088</v>
       </c>
       <c r="B55" t="n">
-        <v>91413</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6283,25 +6279,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6311,13 +6307,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780339</v>
+        <v>780658</v>
       </c>
       <c r="R55" t="n">
-        <v>7341191</v>
+        <v>7340942</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6361,22 +6357,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374132</v>
+        <v>125374075</v>
       </c>
       <c r="B56" t="n">
-        <v>92293</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6385,41 +6381,61 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780904</v>
+        <v>780877</v>
       </c>
       <c r="R56" t="n">
-        <v>7340872</v>
+        <v>7340946</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6446,14 +6462,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,22 +6489,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374088</v>
+        <v>125374111</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6492,38 +6513,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780658</v>
+        <v>780311</v>
       </c>
       <c r="R57" t="n">
-        <v>7340942</v>
+        <v>7341211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6558,6 +6579,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6570,22 +6596,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125374075</v>
+        <v>125368580</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6594,58 +6620,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780877</v>
+        <v>780337</v>
       </c>
       <c r="R58" t="n">
-        <v>7340946</v>
+        <v>7341192</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6675,19 +6681,14 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>100-tals</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6702,22 +6703,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125374111</v>
+        <v>125368577</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6726,38 +6727,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780311</v>
+        <v>780480</v>
       </c>
       <c r="R59" t="n">
-        <v>7341211</v>
+        <v>7341033</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6792,11 +6793,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6809,22 +6805,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125368580</v>
+        <v>125374094</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6833,25 +6829,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6861,10 +6857,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780337</v>
+        <v>780904</v>
       </c>
       <c r="R60" t="n">
-        <v>7341192</v>
+        <v>7340832</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6899,11 +6895,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>100-tals</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6916,22 +6907,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125368577</v>
+        <v>125368582</v>
       </c>
       <c r="B61" t="n">
-        <v>78546</v>
+        <v>91172</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6940,38 +6931,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780480</v>
+        <v>780634</v>
       </c>
       <c r="R61" t="n">
-        <v>7341033</v>
+        <v>7340886</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7012,6 +7006,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7030,10 +7025,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125374094</v>
+        <v>125374084</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7046,21 +7041,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780904</v>
+        <v>780527</v>
       </c>
       <c r="R62" t="n">
-        <v>7340832</v>
+        <v>7341044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7132,10 +7127,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125368582</v>
+        <v>125376201</v>
       </c>
       <c r="B63" t="n">
-        <v>91172</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,37 +7143,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780634</v>
+        <v>780318</v>
       </c>
       <c r="R63" t="n">
-        <v>7340886</v>
+        <v>7341215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7219,29 +7211,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374084</v>
+        <v>125368595</v>
       </c>
       <c r="B64" t="n">
-        <v>78546</v>
+        <v>78194</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,21 +7245,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7278,10 +7269,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780527</v>
+        <v>780561</v>
       </c>
       <c r="R64" t="n">
-        <v>7341044</v>
+        <v>7340968</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7328,22 +7319,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125376201</v>
+        <v>125374101</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7352,38 +7343,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780318</v>
+        <v>780924</v>
       </c>
       <c r="R65" t="n">
-        <v>7341215</v>
+        <v>7340886</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7418,6 +7409,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7430,22 +7426,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125368595</v>
+        <v>125376203</v>
       </c>
       <c r="B66" t="n">
-        <v>78194</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7454,25 +7450,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7482,10 +7478,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780561</v>
+        <v>780331</v>
       </c>
       <c r="R66" t="n">
-        <v>7340968</v>
+        <v>7341207</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7532,22 +7528,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374101</v>
+        <v>125374096</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7556,38 +7552,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780924</v>
+        <v>780394</v>
       </c>
       <c r="R67" t="n">
-        <v>7340886</v>
+        <v>7341123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7622,11 +7618,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7639,22 +7630,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125376203</v>
+        <v>125374118</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7663,25 +7654,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7691,10 +7682,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780331</v>
+        <v>780370</v>
       </c>
       <c r="R68" t="n">
-        <v>7341207</v>
+        <v>7341315</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7729,6 +7720,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7741,22 +7737,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125374096</v>
+        <v>125378928</v>
       </c>
       <c r="B69" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7765,25 +7761,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7793,13 +7789,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780394</v>
+        <v>780881</v>
       </c>
       <c r="R69" t="n">
-        <v>7341123</v>
+        <v>7340820</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7843,22 +7839,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125374118</v>
+        <v>125368563</v>
       </c>
       <c r="B70" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7867,25 +7863,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7895,10 +7891,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780370</v>
+        <v>780865</v>
       </c>
       <c r="R70" t="n">
-        <v>7341315</v>
+        <v>7340858</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7933,11 +7929,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>4 st</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7950,19 +7941,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125378928</v>
+        <v>125374090</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -8002,13 +7993,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780881</v>
+        <v>780353</v>
       </c>
       <c r="R71" t="n">
-        <v>7340820</v>
+        <v>7341186</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8052,22 +8043,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125368563</v>
+        <v>125376197</v>
       </c>
       <c r="B72" t="n">
-        <v>79428</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8080,21 +8071,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8104,10 +8095,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780865</v>
+        <v>780912</v>
       </c>
       <c r="R72" t="n">
-        <v>7340858</v>
+        <v>7340859</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8154,22 +8145,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125374090</v>
+        <v>125368571</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>92321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8182,21 +8173,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8206,10 +8197,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780353</v>
+        <v>780646</v>
       </c>
       <c r="R73" t="n">
-        <v>7341186</v>
+        <v>7340861</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8256,22 +8247,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125376197</v>
+        <v>125376199</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8280,25 +8271,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8308,10 +8299,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780912</v>
+        <v>780542</v>
       </c>
       <c r="R74" t="n">
-        <v>7340859</v>
+        <v>7341352</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8370,10 +8361,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125368571</v>
+        <v>125368593</v>
       </c>
       <c r="B75" t="n">
-        <v>92321</v>
+        <v>77738</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8386,21 +8377,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>6487</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8410,10 +8401,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780646</v>
+        <v>780561</v>
       </c>
       <c r="R75" t="n">
-        <v>7340861</v>
+        <v>7340968</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8472,10 +8463,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125376199</v>
+        <v>125374086</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8484,25 +8475,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8512,10 +8503,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780542</v>
+        <v>780521</v>
       </c>
       <c r="R76" t="n">
-        <v>7341352</v>
+        <v>7341051</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8562,22 +8553,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125368575</v>
+        <v>125378906</v>
       </c>
       <c r="B77" t="n">
-        <v>92490</v>
+        <v>57513</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8590,21 +8581,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8614,13 +8605,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780910</v>
+        <v>780955</v>
       </c>
       <c r="R77" t="n">
-        <v>7340862</v>
+        <v>7340788</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8664,22 +8655,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125368593</v>
+        <v>125378905</v>
       </c>
       <c r="B78" t="n">
-        <v>77738</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8692,37 +8683,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780561</v>
+        <v>780354</v>
       </c>
       <c r="R78" t="n">
-        <v>7340968</v>
+        <v>7341159</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8752,6 +8747,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8766,22 +8766,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374086</v>
+        <v>125368575</v>
       </c>
       <c r="B79" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780521</v>
+        <v>780910</v>
       </c>
       <c r="R79" t="n">
-        <v>7341051</v>
+        <v>7340862</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8868,12 +8868,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8982,10 +8982,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125378906</v>
+        <v>125420114</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>92490</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9022,13 +9022,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780955</v>
+        <v>780701</v>
       </c>
       <c r="R81" t="n">
-        <v>7340788</v>
+        <v>7340825</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9072,22 +9072,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125378905</v>
+        <v>125420097</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>90051</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9100,41 +9100,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780354</v>
+        <v>780875</v>
       </c>
       <c r="R82" t="n">
-        <v>7341159</v>
+        <v>7340884</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9164,11 +9160,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9183,15 +9174,964 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125420098</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>780771</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7340901</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125420107</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>780339</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7341160</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125420111</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92490</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>780605</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7340903</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125420110</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92321</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>780581</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7340927</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125378914</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>780360</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7341113</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Avskals gran</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
           <t>Cecilia Lundin</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>Cecilia Lundin</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125420113</v>
+      </c>
+      <c r="B88" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>780740</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7340806</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125420109</v>
+      </c>
+      <c r="B89" t="n">
+        <v>88359</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>510</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>780379</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7341130</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125378915</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>780825</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7340795</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125420106</v>
+      </c>
+      <c r="B91" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Dragträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>780582</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7340956</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125374105</v>
+        <v>125376205</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,34 +1740,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780579</v>
+        <v>780453</v>
       </c>
       <c r="R11" t="n">
-        <v>7341020</v>
+        <v>7341309</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125374078</v>
+        <v>125374103</v>
       </c>
       <c r="B12" t="n">
-        <v>78834</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,34 +1842,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780705</v>
+        <v>780777</v>
       </c>
       <c r="R12" t="n">
-        <v>7340829</v>
+        <v>7340841</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,6 +1904,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1916,22 +1921,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125374080</v>
+        <v>125368577</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,21 +1949,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780787</v>
+        <v>780480</v>
       </c>
       <c r="R13" t="n">
-        <v>7340766</v>
+        <v>7341033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,22 +2023,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125374123</v>
+        <v>125374127</v>
       </c>
       <c r="B14" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,21 +2051,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2070,13 +2075,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780428</v>
+        <v>780447</v>
       </c>
       <c r="R14" t="n">
-        <v>7341058</v>
+        <v>7341241</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,22 +2130,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125374099</v>
+        <v>125368579</v>
       </c>
       <c r="B15" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2149,25 +2154,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780470</v>
+        <v>780564</v>
       </c>
       <c r="R15" t="n">
-        <v>7341026</v>
+        <v>7341334</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,22 +2232,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125368587</v>
+        <v>125378930</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,25 +2256,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780344</v>
+        <v>780354</v>
       </c>
       <c r="R16" t="n">
-        <v>7341144</v>
+        <v>7341240</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,22 +2334,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125374092</v>
+        <v>125378902</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,21 +2362,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,13 +2386,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780743</v>
+        <v>780545</v>
       </c>
       <c r="R17" t="n">
-        <v>7340811</v>
+        <v>7341029</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,19 +2436,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125378924</v>
+        <v>125378928</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2483,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780766</v>
+        <v>780881</v>
       </c>
       <c r="R18" t="n">
-        <v>7340885</v>
+        <v>7340820</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,10 +2550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125378929</v>
+        <v>125378905</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,34 +2566,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780910</v>
+        <v>780354</v>
       </c>
       <c r="R19" t="n">
-        <v>7340820</v>
+        <v>7341159</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2621,6 +2630,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,10 +2661,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374124</v>
+        <v>125374101</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2663,37 +2677,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780876</v>
+        <v>780924</v>
       </c>
       <c r="R20" t="n">
-        <v>7340837</v>
+        <v>7340886</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,6 +2737,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,22 +2756,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125374109</v>
+        <v>125368590</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>78455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,25 +2780,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2789,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780890</v>
+        <v>780707</v>
       </c>
       <c r="R21" t="n">
-        <v>7340825</v>
+        <v>7340834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,11 +2846,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2844,22 +2858,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368569</v>
+        <v>125378926</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,21 +2886,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,13 +2910,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780564</v>
+        <v>780493</v>
       </c>
       <c r="R22" t="n">
-        <v>7341334</v>
+        <v>7341109</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2946,22 +2960,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368590</v>
+        <v>125376197</v>
       </c>
       <c r="B23" t="n">
-        <v>78455</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,21 +2988,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780707</v>
+        <v>780912</v>
       </c>
       <c r="R23" t="n">
-        <v>7340834</v>
+        <v>7340859</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,22 +3062,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374119</v>
+        <v>125378920</v>
       </c>
       <c r="B24" t="n">
-        <v>91413</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,13 +3114,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780501</v>
+        <v>780413</v>
       </c>
       <c r="R24" t="n">
-        <v>7341325</v>
+        <v>7341084</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,28 +3158,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125378911</v>
+        <v>125374125</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91413</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3174,25 +3189,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3202,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780332</v>
+        <v>780339</v>
       </c>
       <c r="R25" t="n">
-        <v>7341195</v>
+        <v>7341191</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3240,11 +3255,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3257,12 +3267,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3371,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125368586</v>
+        <v>125368569</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,21 +3397,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3473,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374103</v>
+        <v>125374088</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3485,38 +3495,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780777</v>
+        <v>780658</v>
       </c>
       <c r="R28" t="n">
-        <v>7340841</v>
+        <v>7340942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,11 +3561,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3568,22 +3573,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125378917</v>
+        <v>125374114</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3592,45 +3597,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780909</v>
+        <v>780332</v>
       </c>
       <c r="R29" t="n">
-        <v>7340823</v>
+        <v>7341182</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3664,7 +3665,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,19 +3680,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125368579</v>
+        <v>125374131</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3731,13 +3732,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780564</v>
+        <v>780341</v>
       </c>
       <c r="R30" t="n">
-        <v>7341334</v>
+        <v>7341192</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3781,22 +3782,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125368591</v>
+        <v>125368595</v>
       </c>
       <c r="B31" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3805,25 +3806,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780620</v>
+        <v>780561</v>
       </c>
       <c r="R31" t="n">
-        <v>7340897</v>
+        <v>7340968</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3895,10 +3896,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125378930</v>
+        <v>125368575</v>
       </c>
       <c r="B32" t="n">
-        <v>92293</v>
+        <v>92490</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,25 +3908,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,13 +3936,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780354</v>
+        <v>780910</v>
       </c>
       <c r="R32" t="n">
-        <v>7341240</v>
+        <v>7340862</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,22 +3986,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125374129</v>
+        <v>125368582</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91172</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4013,37 +4014,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780323</v>
+        <v>780634</v>
       </c>
       <c r="R33" t="n">
-        <v>7341197</v>
+        <v>7340886</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4081,28 +4085,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374131</v>
+        <v>125374075</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4111,41 +4116,61 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780341</v>
+        <v>780877</v>
       </c>
       <c r="R34" t="n">
-        <v>7341192</v>
+        <v>7340946</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4172,9 +4197,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4189,22 +4224,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125368578</v>
+        <v>125376203</v>
       </c>
       <c r="B35" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4213,25 +4248,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4241,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780865</v>
+        <v>780331</v>
       </c>
       <c r="R35" t="n">
-        <v>7340858</v>
+        <v>7341207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,22 +4326,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125368574</v>
+        <v>125368587</v>
       </c>
       <c r="B36" t="n">
-        <v>56725</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,25 +4350,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4378,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780624</v>
+        <v>780344</v>
       </c>
       <c r="R36" t="n">
-        <v>7340950</v>
+        <v>7341144</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125378919</v>
+        <v>125374105</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,37 +4456,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780397</v>
+        <v>780579</v>
       </c>
       <c r="R37" t="n">
-        <v>7341092</v>
+        <v>7341020</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4489,29 +4524,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125378920</v>
+        <v>125374116</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4524,37 +4558,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780413</v>
+        <v>780554</v>
       </c>
       <c r="R38" t="n">
-        <v>7341084</v>
+        <v>7340907</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4592,29 +4626,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374108</v>
+        <v>125378919</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>78547</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4627,37 +4660,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780597</v>
+        <v>780397</v>
       </c>
       <c r="R39" t="n">
-        <v>7341251</v>
+        <v>7341092</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4695,28 +4728,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125368584</v>
+        <v>125368574</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>56725</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,25 +4759,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4753,10 +4787,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780566</v>
+        <v>780624</v>
       </c>
       <c r="R40" t="n">
-        <v>7341030</v>
+        <v>7340950</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4815,10 +4849,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368564</v>
+        <v>125374096</v>
       </c>
       <c r="B41" t="n">
-        <v>90051</v>
+        <v>92293</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,25 +4861,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4855,10 +4889,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780518</v>
+        <v>780394</v>
       </c>
       <c r="R41" t="n">
-        <v>7341011</v>
+        <v>7341123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4905,22 +4939,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125378902</v>
+        <v>125368566</v>
       </c>
       <c r="B42" t="n">
-        <v>79428</v>
+        <v>90051</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4933,21 +4967,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4957,13 +4991,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780545</v>
+        <v>780905</v>
       </c>
       <c r="R42" t="n">
-        <v>7341029</v>
+        <v>7340863</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5007,22 +5041,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125378926</v>
+        <v>125374132</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5031,25 +5065,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5059,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780493</v>
+        <v>780904</v>
       </c>
       <c r="R43" t="n">
-        <v>7341109</v>
+        <v>7340872</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5097,6 +5131,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5109,22 +5148,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374127</v>
+        <v>125374090</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5133,25 +5172,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5161,13 +5200,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780447</v>
+        <v>780353</v>
       </c>
       <c r="R44" t="n">
-        <v>7341241</v>
+        <v>7341186</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,11 +5236,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,22 +5250,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125368566</v>
+        <v>125378911</v>
       </c>
       <c r="B45" t="n">
-        <v>90051</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5244,21 +5278,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5268,13 +5302,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780905</v>
+        <v>780332</v>
       </c>
       <c r="R45" t="n">
-        <v>7340863</v>
+        <v>7341195</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5304,6 +5338,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,22 +5357,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125378916</v>
+        <v>125376199</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,45 +5381,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780956</v>
+        <v>780542</v>
       </c>
       <c r="R46" t="n">
-        <v>7340785</v>
+        <v>7341352</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5410,11 +5445,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5459,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125368592</v>
+        <v>125374119</v>
       </c>
       <c r="B47" t="n">
-        <v>74893</v>
+        <v>91413</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5453,25 +5483,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>4217</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5481,10 +5511,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780845</v>
+        <v>780501</v>
       </c>
       <c r="R47" t="n">
-        <v>7340863</v>
+        <v>7341325</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,22 +5561,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125376207</v>
+        <v>125368568</v>
       </c>
       <c r="B48" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5555,25 +5585,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5583,10 +5613,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780564</v>
+        <v>780597</v>
       </c>
       <c r="R48" t="n">
-        <v>7340973</v>
+        <v>7341251</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,22 +5663,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125368568</v>
+        <v>125374080</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5661,21 +5691,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5685,10 +5715,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780597</v>
+        <v>780787</v>
       </c>
       <c r="R49" t="n">
-        <v>7341251</v>
+        <v>7340766</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,22 +5765,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125368573</v>
+        <v>125368571</v>
       </c>
       <c r="B50" t="n">
-        <v>91299</v>
+        <v>92321</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5763,21 +5793,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5787,10 +5817,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780591</v>
+        <v>780646</v>
       </c>
       <c r="R50" t="n">
-        <v>7341254</v>
+        <v>7340861</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,10 +5879,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125374116</v>
+        <v>125376207</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5861,38 +5891,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780554</v>
+        <v>780564</v>
       </c>
       <c r="R51" t="n">
-        <v>7340907</v>
+        <v>7340973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5939,22 +5969,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374125</v>
+        <v>125374118</v>
       </c>
       <c r="B52" t="n">
-        <v>91413</v>
+        <v>92293</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5967,21 +5997,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5991,13 +6021,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780339</v>
+        <v>780370</v>
       </c>
       <c r="R52" t="n">
-        <v>7341191</v>
+        <v>7341315</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6027,6 +6057,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6041,22 +6076,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125374114</v>
+        <v>125374099</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6065,38 +6100,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780332</v>
+        <v>780470</v>
       </c>
       <c r="R53" t="n">
-        <v>7341182</v>
+        <v>7341026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6131,11 +6166,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6148,22 +6178,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374132</v>
+        <v>125368586</v>
       </c>
       <c r="B54" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6172,25 +6202,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6200,13 +6230,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780904</v>
+        <v>780564</v>
       </c>
       <c r="R54" t="n">
-        <v>7340872</v>
+        <v>7341334</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6236,11 +6266,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6255,19 +6280,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374088</v>
+        <v>125378924</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6307,13 +6332,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780658</v>
+        <v>780766</v>
       </c>
       <c r="R55" t="n">
-        <v>7340942</v>
+        <v>7340885</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6357,22 +6382,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374075</v>
+        <v>125374124</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6385,57 +6410,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780877</v>
+        <v>780876</v>
       </c>
       <c r="R56" t="n">
-        <v>7340946</v>
+        <v>7340837</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6462,19 +6467,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6489,22 +6484,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374111</v>
+        <v>125368584</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6513,38 +6508,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780311</v>
+        <v>780566</v>
       </c>
       <c r="R57" t="n">
-        <v>7341211</v>
+        <v>7341030</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6579,11 +6574,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6596,22 +6586,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125368580</v>
+        <v>125368573</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6620,25 +6610,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6648,10 +6638,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780337</v>
+        <v>780591</v>
       </c>
       <c r="R58" t="n">
-        <v>7341192</v>
+        <v>7341254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6684,11 +6674,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6715,10 +6700,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125368577</v>
+        <v>125368593</v>
       </c>
       <c r="B59" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6731,21 +6716,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6755,10 +6740,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780480</v>
+        <v>780561</v>
       </c>
       <c r="R59" t="n">
-        <v>7341033</v>
+        <v>7340968</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6817,10 +6802,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125374094</v>
+        <v>125374123</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6829,25 +6814,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6857,10 +6842,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780904</v>
+        <v>780428</v>
       </c>
       <c r="R60" t="n">
-        <v>7340832</v>
+        <v>7341058</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6895,6 +6880,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6907,22 +6897,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125368582</v>
+        <v>125368591</v>
       </c>
       <c r="B61" t="n">
-        <v>91172</v>
+        <v>92293</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6931,41 +6921,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780634</v>
+        <v>780620</v>
       </c>
       <c r="R61" t="n">
-        <v>7340886</v>
+        <v>7340897</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7006,7 +6993,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7025,10 +7011,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125374084</v>
+        <v>125368592</v>
       </c>
       <c r="B62" t="n">
-        <v>78546</v>
+        <v>74893</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7041,21 +7027,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7065,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780527</v>
+        <v>780845</v>
       </c>
       <c r="R62" t="n">
-        <v>7341044</v>
+        <v>7340863</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,12 +7101,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,10 +7215,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125368595</v>
+        <v>125374086</v>
       </c>
       <c r="B64" t="n">
-        <v>78194</v>
+        <v>78546</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7245,21 +7231,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7269,10 +7255,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780561</v>
+        <v>780521</v>
       </c>
       <c r="R64" t="n">
-        <v>7340968</v>
+        <v>7341051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7319,22 +7305,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374101</v>
+        <v>125374078</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>78834</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7343,38 +7329,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780924</v>
+        <v>780705</v>
       </c>
       <c r="R65" t="n">
-        <v>7340886</v>
+        <v>7340829</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7409,11 +7395,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7426,22 +7407,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125376203</v>
+        <v>125368578</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7450,25 +7431,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7478,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780331</v>
+        <v>780865</v>
       </c>
       <c r="R66" t="n">
-        <v>7341207</v>
+        <v>7340858</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7528,22 +7509,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374096</v>
+        <v>125374109</v>
       </c>
       <c r="B67" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7556,21 +7537,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7580,10 +7561,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780394</v>
+        <v>780890</v>
       </c>
       <c r="R67" t="n">
-        <v>7341123</v>
+        <v>7340825</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7618,6 +7599,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7630,22 +7616,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125374118</v>
+        <v>125378917</v>
       </c>
       <c r="B68" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7658,37 +7644,41 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780370</v>
+        <v>780909</v>
       </c>
       <c r="R68" t="n">
-        <v>7341315</v>
+        <v>7340823</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7722,7 +7712,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7737,22 +7727,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125378928</v>
+        <v>125368563</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7765,21 +7755,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7789,13 +7779,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780881</v>
+        <v>780865</v>
       </c>
       <c r="R69" t="n">
-        <v>7340820</v>
+        <v>7340858</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7839,22 +7829,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125368563</v>
+        <v>125378929</v>
       </c>
       <c r="B70" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7867,21 +7857,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7891,13 +7881,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780865</v>
+        <v>780910</v>
       </c>
       <c r="R70" t="n">
-        <v>7340858</v>
+        <v>7340820</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7941,22 +7931,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125374090</v>
+        <v>125374111</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7965,38 +7955,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780353</v>
+        <v>780311</v>
       </c>
       <c r="R71" t="n">
-        <v>7341186</v>
+        <v>7341211</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8031,6 +8021,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8043,22 +8038,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125376197</v>
+        <v>125374092</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8071,21 +8066,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8095,10 +8090,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780912</v>
+        <v>780743</v>
       </c>
       <c r="R72" t="n">
-        <v>7340859</v>
+        <v>7340811</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8145,22 +8140,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125368571</v>
+        <v>125374094</v>
       </c>
       <c r="B73" t="n">
-        <v>92321</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8173,21 +8168,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8197,10 +8192,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780646</v>
+        <v>780904</v>
       </c>
       <c r="R73" t="n">
-        <v>7340861</v>
+        <v>7340832</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8247,22 +8242,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125376199</v>
+        <v>125378906</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8271,25 +8266,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8299,13 +8294,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780542</v>
+        <v>780955</v>
       </c>
       <c r="R74" t="n">
-        <v>7341352</v>
+        <v>7340788</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8349,22 +8344,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125368593</v>
+        <v>125374129</v>
       </c>
       <c r="B75" t="n">
-        <v>77738</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8373,25 +8368,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8401,13 +8396,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780561</v>
+        <v>780323</v>
       </c>
       <c r="R75" t="n">
-        <v>7340968</v>
+        <v>7341197</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8451,22 +8446,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125374086</v>
+        <v>125368580</v>
       </c>
       <c r="B76" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8475,25 +8470,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8503,10 +8498,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780521</v>
+        <v>780337</v>
       </c>
       <c r="R76" t="n">
-        <v>7341051</v>
+        <v>7341192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8541,6 +8536,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>100-tals</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8553,22 +8553,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125378906</v>
+        <v>125378916</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8577,38 +8577,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780955</v>
+        <v>780956</v>
       </c>
       <c r="R77" t="n">
-        <v>7340788</v>
+        <v>7340785</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8641,6 +8645,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8667,10 +8676,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125378905</v>
+        <v>125374108</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8683,41 +8692,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780354</v>
+        <v>780597</v>
       </c>
       <c r="R78" t="n">
-        <v>7341159</v>
+        <v>7341251</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8747,11 +8752,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8766,22 +8766,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125368575</v>
+        <v>125368564</v>
       </c>
       <c r="B79" t="n">
-        <v>92490</v>
+        <v>90051</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780910</v>
+        <v>780518</v>
       </c>
       <c r="R79" t="n">
-        <v>7340862</v>
+        <v>7341011</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125376205</v>
+        <v>125374084</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8896,21 +8896,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8920,10 +8920,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780453</v>
+        <v>780527</v>
       </c>
       <c r="R80" t="n">
-        <v>7341309</v>
+        <v>7341044</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8970,22 +8970,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420114</v>
+        <v>125420107</v>
       </c>
       <c r="B81" t="n">
-        <v>92490</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780701</v>
+        <v>780339</v>
       </c>
       <c r="R81" t="n">
-        <v>7340825</v>
+        <v>7341160</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420097</v>
+        <v>125420098</v>
       </c>
       <c r="B82" t="n">
-        <v>90051</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780875</v>
+        <v>780771</v>
       </c>
       <c r="R82" t="n">
-        <v>7340884</v>
+        <v>7340901</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9160,6 +9160,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9186,10 +9191,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420098</v>
+        <v>125420114</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9202,21 +9207,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9226,10 +9231,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>780771</v>
+        <v>780701</v>
       </c>
       <c r="R83" t="n">
-        <v>7340901</v>
+        <v>7340825</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9262,11 +9267,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9293,10 +9293,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420107</v>
+        <v>125420097</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>90051</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9309,21 +9309,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>1962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>780339</v>
+        <v>780875</v>
       </c>
       <c r="R84" t="n">
-        <v>7341160</v>
+        <v>7340884</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9395,10 +9395,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420111</v>
+        <v>125420109</v>
       </c>
       <c r="B85" t="n">
-        <v>92490</v>
+        <v>88359</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9411,21 +9411,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>510</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9435,10 +9435,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780605</v>
+        <v>780379</v>
       </c>
       <c r="R85" t="n">
-        <v>7340903</v>
+        <v>7341130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420110</v>
+        <v>125378915</v>
       </c>
       <c r="B86" t="n">
-        <v>92321</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9513,37 +9513,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780581</v>
+        <v>780825</v>
       </c>
       <c r="R86" t="n">
-        <v>7340927</v>
+        <v>7340795</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9573,6 +9577,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9587,22 +9596,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125378914</v>
+        <v>125420110</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>92321</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9615,41 +9624,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780360</v>
+        <v>780581</v>
       </c>
       <c r="R87" t="n">
-        <v>7341113</v>
+        <v>7340927</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9679,11 +9684,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9698,22 +9698,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125420113</v>
+        <v>125378914</v>
       </c>
       <c r="B88" t="n">
-        <v>96985</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9722,41 +9722,45 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>780740</v>
+        <v>780360</v>
       </c>
       <c r="R88" t="n">
-        <v>7340806</v>
+        <v>7341113</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9786,6 +9790,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9800,22 +9809,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125420109</v>
+        <v>125420113</v>
       </c>
       <c r="B89" t="n">
-        <v>88359</v>
+        <v>96985</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9824,25 +9833,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9852,10 +9861,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780379</v>
+        <v>780740</v>
       </c>
       <c r="R89" t="n">
-        <v>7341130</v>
+        <v>7340806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9914,10 +9923,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125378915</v>
+        <v>125420106</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9926,31 +9935,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9958,13 +9971,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780825</v>
+        <v>780582</v>
       </c>
       <c r="R90" t="n">
-        <v>7340795</v>
+        <v>7340956</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9994,11 +10007,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10013,22 +10021,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125420106</v>
+        <v>125420111</v>
       </c>
       <c r="B91" t="n">
-        <v>56722</v>
+        <v>92490</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10037,46 +10045,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>780582</v>
+        <v>780605</v>
       </c>
       <c r="R91" t="n">
-        <v>7340956</v>
+        <v>7340903</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>125338805</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125376205</v>
+        <v>125376199</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,25 +1736,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780453</v>
+        <v>780542</v>
       </c>
       <c r="R11" t="n">
-        <v>7341309</v>
+        <v>7341352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125374103</v>
+        <v>125368578</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780777</v>
+        <v>780865</v>
       </c>
       <c r="R12" t="n">
-        <v>7340841</v>
+        <v>7340858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,11 +1904,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1921,22 +1916,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125368577</v>
+        <v>125378916</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,41 +1940,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780480</v>
+        <v>780956</v>
       </c>
       <c r="R13" t="n">
-        <v>7341033</v>
+        <v>7340785</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,6 +2008,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,22 +2027,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125374127</v>
+        <v>125376197</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,25 +2051,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780447</v>
+        <v>780912</v>
       </c>
       <c r="R14" t="n">
-        <v>7341241</v>
+        <v>7340859</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2111,11 +2115,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125368579</v>
+        <v>125374092</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780564</v>
+        <v>780743</v>
       </c>
       <c r="R15" t="n">
-        <v>7341334</v>
+        <v>7340811</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125378930</v>
+        <v>125368564</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>90204</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780354</v>
+        <v>780518</v>
       </c>
       <c r="R16" t="n">
-        <v>7341240</v>
+        <v>7341011</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,22 +2333,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125378902</v>
+        <v>125368568</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,21 +2361,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2386,13 +2385,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780545</v>
+        <v>780597</v>
       </c>
       <c r="R17" t="n">
-        <v>7341029</v>
+        <v>7341251</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,22 +2435,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125378928</v>
+        <v>125374086</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780881</v>
+        <v>780521</v>
       </c>
       <c r="R18" t="n">
-        <v>7340820</v>
+        <v>7341051</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,22 +2537,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125378905</v>
+        <v>125378930</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>92448</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2562,32 +2561,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
@@ -2597,7 +2592,7 @@
         <v>780354</v>
       </c>
       <c r="R19" t="n">
-        <v>7341159</v>
+        <v>7341240</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2630,11 +2625,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374101</v>
+        <v>125368584</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,34 +2667,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780924</v>
+        <v>780566</v>
       </c>
       <c r="R20" t="n">
-        <v>7340886</v>
+        <v>7341030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,11 +2729,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2756,22 +2741,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368590</v>
+        <v>125368592</v>
       </c>
       <c r="B21" t="n">
-        <v>78455</v>
+        <v>75017</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,21 +2769,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780707</v>
+        <v>780845</v>
       </c>
       <c r="R21" t="n">
-        <v>7340834</v>
+        <v>7340863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125378926</v>
+        <v>125368590</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78592</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,21 +2871,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2910,13 +2895,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780493</v>
+        <v>780707</v>
       </c>
       <c r="R22" t="n">
-        <v>7341109</v>
+        <v>7340834</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125376197</v>
+        <v>125368569</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,21 +2973,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3012,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780912</v>
+        <v>780564</v>
       </c>
       <c r="R23" t="n">
-        <v>7340859</v>
+        <v>7341334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,22 +3047,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125378920</v>
+        <v>125368593</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>77874</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,21 +3075,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,13 +3099,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780413</v>
+        <v>780561</v>
       </c>
       <c r="R24" t="n">
-        <v>7341084</v>
+        <v>7340968</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3158,29 +3143,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125374125</v>
+        <v>125374124</v>
       </c>
       <c r="B25" t="n">
-        <v>91413</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,25 +3173,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3217,10 +3201,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780339</v>
+        <v>780876</v>
       </c>
       <c r="R25" t="n">
-        <v>7341191</v>
+        <v>7340837</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3279,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125368562</v>
+        <v>125374118</v>
       </c>
       <c r="B26" t="n">
-        <v>79428</v>
+        <v>92448</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3291,25 +3275,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3319,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780722</v>
+        <v>780370</v>
       </c>
       <c r="R26" t="n">
-        <v>7340838</v>
+        <v>7341315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,6 +3341,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3369,22 +3358,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125368569</v>
+        <v>125378920</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>78684</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3421,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780564</v>
+        <v>780413</v>
       </c>
       <c r="R27" t="n">
-        <v>7341334</v>
+        <v>7341084</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,28 +3454,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374088</v>
+        <v>125378905</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3499,37 +3489,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780658</v>
+        <v>780354</v>
       </c>
       <c r="R28" t="n">
-        <v>7340942</v>
+        <v>7341159</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3559,6 +3553,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,22 +3572,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374114</v>
+        <v>125374078</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78971</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3597,38 +3596,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780332</v>
+        <v>780705</v>
       </c>
       <c r="R29" t="n">
-        <v>7341182</v>
+        <v>7340829</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3663,11 +3662,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3680,22 +3674,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125374131</v>
+        <v>125378926</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3704,25 +3698,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3732,10 +3726,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780341</v>
+        <v>780493</v>
       </c>
       <c r="R30" t="n">
-        <v>7341192</v>
+        <v>7341109</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3782,22 +3776,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125368595</v>
+        <v>125368577</v>
       </c>
       <c r="B31" t="n">
-        <v>78194</v>
+        <v>78683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3810,21 +3804,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780561</v>
+        <v>780480</v>
       </c>
       <c r="R31" t="n">
-        <v>7340968</v>
+        <v>7341033</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3896,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125368575</v>
+        <v>125374125</v>
       </c>
       <c r="B32" t="n">
-        <v>92490</v>
+        <v>91573</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3908,25 +3902,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3936,13 +3930,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780910</v>
+        <v>780339</v>
       </c>
       <c r="R32" t="n">
-        <v>7340862</v>
+        <v>7341191</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3986,22 +3980,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125368582</v>
+        <v>125368575</v>
       </c>
       <c r="B33" t="n">
-        <v>91172</v>
+        <v>92646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4010,41 +4004,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780634</v>
+        <v>780910</v>
       </c>
       <c r="R33" t="n">
-        <v>7340886</v>
+        <v>7340862</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4085,7 +4076,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4104,10 +4094,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374075</v>
+        <v>125374129</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4116,61 +4106,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780877</v>
+        <v>780323</v>
       </c>
       <c r="R34" t="n">
-        <v>7340946</v>
+        <v>7341197</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4197,19 +4167,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4224,22 +4184,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125376203</v>
+        <v>125368562</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4248,25 +4208,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4276,10 +4236,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780331</v>
+        <v>780722</v>
       </c>
       <c r="R35" t="n">
-        <v>7341207</v>
+        <v>7340838</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4326,22 +4286,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125368587</v>
+        <v>125374123</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>92448</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4350,25 +4310,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4378,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780344</v>
+        <v>780428</v>
       </c>
       <c r="R36" t="n">
-        <v>7341144</v>
+        <v>7341058</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4416,6 +4376,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4428,22 +4393,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125374105</v>
+        <v>125376207</v>
       </c>
       <c r="B37" t="n">
-        <v>91032</v>
+        <v>92448</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4452,38 +4417,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780579</v>
+        <v>780564</v>
       </c>
       <c r="R37" t="n">
-        <v>7341020</v>
+        <v>7340973</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,22 +4495,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374116</v>
+        <v>125376201</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4554,38 +4519,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780554</v>
+        <v>780318</v>
       </c>
       <c r="R38" t="n">
-        <v>7340907</v>
+        <v>7341215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4632,22 +4597,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125378919</v>
+        <v>125374094</v>
       </c>
       <c r="B39" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4660,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4684,13 +4649,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780397</v>
+        <v>780904</v>
       </c>
       <c r="R39" t="n">
-        <v>7341092</v>
+        <v>7340832</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4728,29 +4693,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125368574</v>
+        <v>125374099</v>
       </c>
       <c r="B40" t="n">
-        <v>56725</v>
+        <v>92448</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4763,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4787,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780624</v>
+        <v>780470</v>
       </c>
       <c r="R40" t="n">
-        <v>7340950</v>
+        <v>7341026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,22 +4801,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374096</v>
+        <v>125378919</v>
       </c>
       <c r="B41" t="n">
-        <v>92293</v>
+        <v>78684</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,25 +4825,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4889,13 +4853,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780394</v>
+        <v>780397</v>
       </c>
       <c r="R41" t="n">
-        <v>7341123</v>
+        <v>7341092</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4933,28 +4897,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125368566</v>
+        <v>125378911</v>
       </c>
       <c r="B42" t="n">
-        <v>90051</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4967,21 +4932,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4991,13 +4956,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780905</v>
+        <v>780332</v>
       </c>
       <c r="R42" t="n">
-        <v>7340863</v>
+        <v>7341195</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5027,6 +4992,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,22 +5011,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374132</v>
+        <v>125374096</v>
       </c>
       <c r="B43" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,13 +5063,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780904</v>
+        <v>780394</v>
       </c>
       <c r="R43" t="n">
-        <v>7340872</v>
+        <v>7341123</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5129,11 +5099,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,22 +5113,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374090</v>
+        <v>125368595</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78331</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5176,21 +5141,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5200,10 +5165,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780353</v>
+        <v>780561</v>
       </c>
       <c r="R44" t="n">
-        <v>7341186</v>
+        <v>7340968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5250,22 +5215,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125378911</v>
+        <v>125368573</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91459</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5278,21 +5243,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5302,13 +5267,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780332</v>
+        <v>780591</v>
       </c>
       <c r="R45" t="n">
-        <v>7341195</v>
+        <v>7341254</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5338,11 +5303,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5357,22 +5317,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125376199</v>
+        <v>125368586</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5381,25 +5341,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5409,10 +5369,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780542</v>
+        <v>780564</v>
       </c>
       <c r="R46" t="n">
-        <v>7341352</v>
+        <v>7341334</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5459,22 +5419,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374119</v>
+        <v>125368571</v>
       </c>
       <c r="B47" t="n">
-        <v>91413</v>
+        <v>92476</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5483,25 +5443,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4217</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5511,10 +5471,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780501</v>
+        <v>780646</v>
       </c>
       <c r="R47" t="n">
-        <v>7341325</v>
+        <v>7340861</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,22 +5521,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125368568</v>
+        <v>125368574</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>56839</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5585,25 +5545,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5613,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780597</v>
+        <v>780624</v>
       </c>
       <c r="R48" t="n">
-        <v>7341251</v>
+        <v>7340950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5675,10 +5635,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374080</v>
+        <v>125368591</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>92448</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5687,25 +5647,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5715,10 +5675,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780787</v>
+        <v>780620</v>
       </c>
       <c r="R49" t="n">
-        <v>7340766</v>
+        <v>7340897</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,22 +5725,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125368571</v>
+        <v>125378917</v>
       </c>
       <c r="B50" t="n">
-        <v>92321</v>
+        <v>56836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5789,41 +5749,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780646</v>
+        <v>780909</v>
       </c>
       <c r="R50" t="n">
-        <v>7340861</v>
+        <v>7340823</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5853,6 +5817,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5867,22 +5836,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125376207</v>
+        <v>125374109</v>
       </c>
       <c r="B51" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5895,21 +5864,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5919,10 +5888,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780564</v>
+        <v>780890</v>
       </c>
       <c r="R51" t="n">
-        <v>7340973</v>
+        <v>7340825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5957,6 +5926,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5969,22 +5943,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374118</v>
+        <v>125374116</v>
       </c>
       <c r="B52" t="n">
-        <v>92293</v>
+        <v>78947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5993,38 +5967,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780370</v>
+        <v>780554</v>
       </c>
       <c r="R52" t="n">
-        <v>7341315</v>
+        <v>7340907</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6059,11 +6033,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>4 st</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6076,22 +6045,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125374099</v>
+        <v>125376205</v>
       </c>
       <c r="B53" t="n">
-        <v>92293</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6100,25 +6069,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6128,10 +6097,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780470</v>
+        <v>780453</v>
       </c>
       <c r="R53" t="n">
-        <v>7341026</v>
+        <v>7341309</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6178,22 +6147,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125368586</v>
+        <v>125374105</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>91186</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,34 +6175,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780564</v>
+        <v>780579</v>
       </c>
       <c r="R54" t="n">
-        <v>7341334</v>
+        <v>7341020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6280,22 +6249,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125378924</v>
+        <v>125368579</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6304,25 +6273,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6332,13 +6301,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780766</v>
+        <v>780564</v>
       </c>
       <c r="R55" t="n">
-        <v>7340885</v>
+        <v>7341334</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6382,22 +6351,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374124</v>
+        <v>125376203</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6406,25 +6375,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6434,13 +6403,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780876</v>
+        <v>780331</v>
       </c>
       <c r="R56" t="n">
-        <v>7340837</v>
+        <v>7341207</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6484,22 +6453,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125368584</v>
+        <v>125374131</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,25 +6477,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6536,13 +6505,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780566</v>
+        <v>780341</v>
       </c>
       <c r="R57" t="n">
-        <v>7341030</v>
+        <v>7341192</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6586,22 +6555,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125368573</v>
+        <v>125368563</v>
       </c>
       <c r="B58" t="n">
-        <v>91299</v>
+        <v>79565</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6614,21 +6583,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6638,10 +6607,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780591</v>
+        <v>780865</v>
       </c>
       <c r="R58" t="n">
-        <v>7341254</v>
+        <v>7340858</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6700,10 +6669,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125368593</v>
+        <v>125374088</v>
       </c>
       <c r="B59" t="n">
-        <v>77738</v>
+        <v>78947</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6716,21 +6685,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6740,10 +6709,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780561</v>
+        <v>780658</v>
       </c>
       <c r="R59" t="n">
-        <v>7340968</v>
+        <v>7340942</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,22 +6759,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125374123</v>
+        <v>125368566</v>
       </c>
       <c r="B60" t="n">
-        <v>92293</v>
+        <v>90204</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6814,25 +6783,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6842,10 +6811,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780428</v>
+        <v>780905</v>
       </c>
       <c r="R60" t="n">
-        <v>7341058</v>
+        <v>7340863</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6880,11 +6849,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6897,22 +6861,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125368591</v>
+        <v>125378902</v>
       </c>
       <c r="B61" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6921,25 +6885,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6949,13 +6913,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780620</v>
+        <v>780545</v>
       </c>
       <c r="R61" t="n">
-        <v>7340897</v>
+        <v>7341029</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6999,22 +6963,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125368592</v>
+        <v>125368587</v>
       </c>
       <c r="B62" t="n">
-        <v>74893</v>
+        <v>78947</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7027,21 +6991,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7051,10 +7015,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780845</v>
+        <v>780344</v>
       </c>
       <c r="R62" t="n">
-        <v>7340863</v>
+        <v>7341144</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7113,10 +7077,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125376201</v>
+        <v>125378929</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7125,25 +7089,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7153,13 +7117,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780318</v>
+        <v>780910</v>
       </c>
       <c r="R63" t="n">
-        <v>7341215</v>
+        <v>7340820</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7203,22 +7167,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374086</v>
+        <v>125374114</v>
       </c>
       <c r="B64" t="n">
-        <v>78546</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7227,38 +7191,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780521</v>
+        <v>780332</v>
       </c>
       <c r="R64" t="n">
-        <v>7341051</v>
+        <v>7341182</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7293,6 +7257,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7305,22 +7274,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374078</v>
+        <v>125374101</v>
       </c>
       <c r="B65" t="n">
-        <v>78834</v>
+        <v>57635</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7329,38 +7298,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780705</v>
+        <v>780924</v>
       </c>
       <c r="R65" t="n">
-        <v>7340829</v>
+        <v>7340886</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7395,6 +7364,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7407,22 +7381,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125368578</v>
+        <v>125374108</v>
       </c>
       <c r="B66" t="n">
-        <v>78546</v>
+        <v>91459</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7435,34 +7409,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780865</v>
+        <v>780597</v>
       </c>
       <c r="R66" t="n">
-        <v>7340858</v>
+        <v>7341251</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7509,22 +7483,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374109</v>
+        <v>125374119</v>
       </c>
       <c r="B67" t="n">
-        <v>56722</v>
+        <v>91573</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7537,21 +7511,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7561,10 +7535,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780890</v>
+        <v>780501</v>
       </c>
       <c r="R67" t="n">
-        <v>7340825</v>
+        <v>7341325</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7597,11 +7571,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7628,10 +7597,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125378917</v>
+        <v>125374103</v>
       </c>
       <c r="B68" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7662,23 +7631,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780909</v>
+        <v>780777</v>
       </c>
       <c r="R68" t="n">
-        <v>7340823</v>
+        <v>7340841</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7727,22 +7692,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368563</v>
+        <v>125378924</v>
       </c>
       <c r="B69" t="n">
-        <v>79428</v>
+        <v>78947</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7755,21 +7720,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7779,13 +7744,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780865</v>
+        <v>780766</v>
       </c>
       <c r="R69" t="n">
-        <v>7340858</v>
+        <v>7340885</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7829,22 +7794,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125378929</v>
+        <v>125374111</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7853,41 +7818,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780910</v>
+        <v>780311</v>
       </c>
       <c r="R70" t="n">
-        <v>7340820</v>
+        <v>7341211</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7917,6 +7882,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7931,22 +7901,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125374111</v>
+        <v>125374132</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>92448</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7955,41 +7925,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780311</v>
+        <v>780904</v>
       </c>
       <c r="R71" t="n">
-        <v>7341211</v>
+        <v>7340872</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8023,7 +7993,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8038,22 +8008,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125374092</v>
+        <v>125374084</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8066,21 +8036,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8090,10 +8060,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780743</v>
+        <v>780527</v>
       </c>
       <c r="R72" t="n">
-        <v>7340811</v>
+        <v>7341044</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8152,10 +8122,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125374094</v>
+        <v>125374090</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8192,10 +8162,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780904</v>
+        <v>780353</v>
       </c>
       <c r="R73" t="n">
-        <v>7340832</v>
+        <v>7341186</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8254,10 +8224,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125378906</v>
+        <v>125374080</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>78684</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8270,21 +8240,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8294,13 +8264,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780955</v>
+        <v>780787</v>
       </c>
       <c r="R74" t="n">
-        <v>7340788</v>
+        <v>7340766</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8344,22 +8314,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374129</v>
+        <v>125374075</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8368,41 +8338,61 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780323</v>
+        <v>780877</v>
       </c>
       <c r="R75" t="n">
-        <v>7341197</v>
+        <v>7340946</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8429,9 +8419,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8446,22 +8446,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125368580</v>
+        <v>125378906</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8470,25 +8470,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8498,13 +8498,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780337</v>
+        <v>780955</v>
       </c>
       <c r="R76" t="n">
-        <v>7341192</v>
+        <v>7340788</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8534,11 +8534,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8553,22 +8548,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125378916</v>
+        <v>125378928</v>
       </c>
       <c r="B77" t="n">
-        <v>56722</v>
+        <v>78947</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8577,42 +8572,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780956</v>
+        <v>780881</v>
       </c>
       <c r="R77" t="n">
-        <v>7340785</v>
+        <v>7340820</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8645,11 +8636,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8676,10 +8662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374108</v>
+        <v>125368582</v>
       </c>
       <c r="B78" t="n">
-        <v>91299</v>
+        <v>91326</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8688,38 +8674,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1503</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780597</v>
+        <v>780634</v>
       </c>
       <c r="R78" t="n">
-        <v>7341251</v>
+        <v>7340886</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8760,28 +8749,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125368564</v>
+        <v>125368580</v>
       </c>
       <c r="B79" t="n">
-        <v>90051</v>
+        <v>98269</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8790,25 +8780,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8818,10 +8808,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780518</v>
+        <v>780337</v>
       </c>
       <c r="R79" t="n">
-        <v>7341011</v>
+        <v>7341192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8854,6 +8844,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>100-tals</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8880,10 +8875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374084</v>
+        <v>125374127</v>
       </c>
       <c r="B80" t="n">
-        <v>78546</v>
+        <v>56836</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8892,25 +8887,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8920,13 +8915,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780527</v>
+        <v>780447</v>
       </c>
       <c r="R80" t="n">
-        <v>7341044</v>
+        <v>7341241</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8956,6 +8951,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8970,12 +8970,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8985,7 +8985,7 @@
         <v>125420107</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420098</v>
+        <v>125420109</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>88512</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9100,21 +9100,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780771</v>
+        <v>780379</v>
       </c>
       <c r="R82" t="n">
-        <v>7340901</v>
+        <v>7341130</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9160,11 +9160,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9191,10 +9186,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420114</v>
+        <v>125420098</v>
       </c>
       <c r="B83" t="n">
-        <v>92490</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9207,21 +9202,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9231,10 +9226,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>780701</v>
+        <v>780771</v>
       </c>
       <c r="R83" t="n">
-        <v>7340825</v>
+        <v>7340901</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9267,6 +9262,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9293,10 +9293,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420097</v>
+        <v>125378915</v>
       </c>
       <c r="B84" t="n">
-        <v>90051</v>
+        <v>57635</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9309,37 +9309,41 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>780875</v>
+        <v>780825</v>
       </c>
       <c r="R84" t="n">
-        <v>7340884</v>
+        <v>7340795</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9369,6 +9373,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9383,22 +9392,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420109</v>
+        <v>125378914</v>
       </c>
       <c r="B85" t="n">
-        <v>88359</v>
+        <v>57635</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9411,37 +9420,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780379</v>
+        <v>780360</v>
       </c>
       <c r="R85" t="n">
-        <v>7341130</v>
+        <v>7341113</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9471,6 +9484,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9485,22 +9503,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125378915</v>
+        <v>125420113</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>97153</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9509,45 +9527,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780825</v>
+        <v>780740</v>
       </c>
       <c r="R86" t="n">
-        <v>7340795</v>
+        <v>7340806</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9577,11 +9591,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9596,12 +9605,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9611,7 +9620,7 @@
         <v>125420110</v>
       </c>
       <c r="B87" t="n">
-        <v>92321</v>
+        <v>92476</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9710,10 +9719,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125378914</v>
+        <v>125420097</v>
       </c>
       <c r="B88" t="n">
-        <v>57513</v>
+        <v>90204</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9726,41 +9735,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>780360</v>
+        <v>780875</v>
       </c>
       <c r="R88" t="n">
-        <v>7341113</v>
+        <v>7340884</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9790,11 +9795,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9809,22 +9809,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125420113</v>
+        <v>125420111</v>
       </c>
       <c r="B89" t="n">
-        <v>96985</v>
+        <v>92646</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9833,25 +9833,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780740</v>
+        <v>780605</v>
       </c>
       <c r="R89" t="n">
-        <v>7340806</v>
+        <v>7340903</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9923,10 +9923,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125420106</v>
+        <v>125420114</v>
       </c>
       <c r="B90" t="n">
-        <v>56722</v>
+        <v>92646</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9935,46 +9935,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780582</v>
+        <v>780701</v>
       </c>
       <c r="R90" t="n">
-        <v>7340956</v>
+        <v>7340825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10033,10 +10025,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125420111</v>
+        <v>125420106</v>
       </c>
       <c r="B91" t="n">
-        <v>92490</v>
+        <v>56836</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10045,38 +10037,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>780605</v>
+        <v>780582</v>
       </c>
       <c r="R91" t="n">
-        <v>7340903</v>
+        <v>7340956</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125368575</v>
+        <v>125374129</v>
       </c>
       <c r="B33" t="n">
-        <v>92646</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4004,25 +4004,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4032,13 +4032,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780910</v>
+        <v>780323</v>
       </c>
       <c r="R33" t="n">
-        <v>7340862</v>
+        <v>7341197</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4082,22 +4082,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374129</v>
+        <v>125368575</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>92646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4106,25 +4106,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780323</v>
+        <v>780910</v>
       </c>
       <c r="R34" t="n">
-        <v>7341197</v>
+        <v>7340862</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4184,12 +4184,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125368573</v>
+        <v>125368586</v>
       </c>
       <c r="B45" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780591</v>
+        <v>780564</v>
       </c>
       <c r="R45" t="n">
-        <v>7341254</v>
+        <v>7341334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125368586</v>
+        <v>125368573</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780564</v>
+        <v>780591</v>
       </c>
       <c r="R46" t="n">
-        <v>7341334</v>
+        <v>7341254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374075</v>
+        <v>125374127</v>
       </c>
       <c r="B75" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8338,61 +8338,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780877</v>
+        <v>780447</v>
       </c>
       <c r="R75" t="n">
-        <v>7340946</v>
+        <v>7341241</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8419,19 +8399,14 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8446,22 +8421,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125378906</v>
+        <v>125378928</v>
       </c>
       <c r="B76" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,21 +8449,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8498,10 +8473,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780955</v>
+        <v>780881</v>
       </c>
       <c r="R76" t="n">
-        <v>7340788</v>
+        <v>7340820</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8560,10 +8535,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125378928</v>
+        <v>125368582</v>
       </c>
       <c r="B77" t="n">
-        <v>78947</v>
+        <v>91326</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,41 +8547,44 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780881</v>
+        <v>780634</v>
       </c>
       <c r="R77" t="n">
-        <v>7340820</v>
+        <v>7340886</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8644,28 +8622,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125368582</v>
+        <v>125368580</v>
       </c>
       <c r="B78" t="n">
-        <v>91326</v>
+        <v>98269</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8678,37 +8657,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780634</v>
+        <v>780337</v>
       </c>
       <c r="R78" t="n">
-        <v>7340886</v>
+        <v>7341192</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8743,13 +8719,17 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>100-tals</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8768,10 +8748,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125368580</v>
+        <v>125374075</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8780,38 +8760,58 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780337</v>
+        <v>780877</v>
       </c>
       <c r="R79" t="n">
-        <v>7341192</v>
+        <v>7340946</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8841,14 +8841,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>100-tals</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8863,22 +8868,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374127</v>
+        <v>125378906</v>
       </c>
       <c r="B80" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8887,25 +8892,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8915,10 +8920,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780447</v>
+        <v>780955</v>
       </c>
       <c r="R80" t="n">
-        <v>7341241</v>
+        <v>7340788</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8953,11 +8958,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8970,12 +8970,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1717,14 +1717,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125376199</v>
+        <v>125368579</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780542</v>
+        <v>780564</v>
       </c>
       <c r="R11" t="n">
-        <v>7341352</v>
+        <v>7341334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125368578</v>
+        <v>125374108</v>
       </c>
       <c r="B12" t="n">
-        <v>78683</v>
+        <v>91459</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,34 +1842,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780865</v>
+        <v>780597</v>
       </c>
       <c r="R12" t="n">
-        <v>7340858</v>
+        <v>7341251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,22 +1916,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125378916</v>
+        <v>125368574</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
+        <v>56839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,41 +1944,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780956</v>
+        <v>780624</v>
       </c>
       <c r="R13" t="n">
-        <v>7340785</v>
+        <v>7340950</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2008,11 +2004,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,22 +2018,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125376197</v>
+        <v>125374127</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,25 +2042,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780912</v>
+        <v>780447</v>
       </c>
       <c r="R14" t="n">
-        <v>7340859</v>
+        <v>7341241</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,6 +2106,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,19 +2125,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125374092</v>
+        <v>125378928</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2181,13 +2177,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780743</v>
+        <v>780881</v>
       </c>
       <c r="R15" t="n">
-        <v>7340811</v>
+        <v>7340820</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,22 +2227,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125368564</v>
+        <v>125368587</v>
       </c>
       <c r="B16" t="n">
-        <v>90204</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2255,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780518</v>
+        <v>780344</v>
       </c>
       <c r="R16" t="n">
-        <v>7341011</v>
+        <v>7341144</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2341,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125368568</v>
+        <v>125376205</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780597</v>
+        <v>780453</v>
       </c>
       <c r="R17" t="n">
-        <v>7341251</v>
+        <v>7341309</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,22 +2431,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125374086</v>
+        <v>125374129</v>
       </c>
       <c r="B18" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,25 +2455,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2483,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780521</v>
+        <v>780323</v>
       </c>
       <c r="R18" t="n">
-        <v>7341051</v>
+        <v>7341197</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,22 +2533,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125378930</v>
+        <v>125368563</v>
       </c>
       <c r="B19" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,25 +2557,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2589,13 +2585,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780354</v>
+        <v>780865</v>
       </c>
       <c r="R19" t="n">
-        <v>7341240</v>
+        <v>7340858</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,19 +2635,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368584</v>
+        <v>125368586</v>
       </c>
       <c r="B20" t="n">
         <v>78947</v>
@@ -2691,10 +2687,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780566</v>
+        <v>780564</v>
       </c>
       <c r="R20" t="n">
-        <v>7341030</v>
+        <v>7341334</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2753,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368592</v>
+        <v>125368569</v>
       </c>
       <c r="B21" t="n">
-        <v>75017</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,21 +2765,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2793,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780845</v>
+        <v>780564</v>
       </c>
       <c r="R21" t="n">
-        <v>7340863</v>
+        <v>7341334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368590</v>
+        <v>125378916</v>
       </c>
       <c r="B22" t="n">
-        <v>78592</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,41 +2863,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780707</v>
+        <v>780956</v>
       </c>
       <c r="R22" t="n">
-        <v>7340834</v>
+        <v>7340785</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,6 +2931,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2950,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368569</v>
+        <v>125376207</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>92448</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,25 +2974,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,7 +3005,7 @@
         <v>780564</v>
       </c>
       <c r="R23" t="n">
-        <v>7341334</v>
+        <v>7340973</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125368593</v>
+        <v>125368595</v>
       </c>
       <c r="B24" t="n">
-        <v>77874</v>
+        <v>78331</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3075,21 +3080,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3161,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125374124</v>
+        <v>125374119</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
+        <v>91573</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,25 +3178,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3201,13 +3206,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780876</v>
+        <v>780501</v>
       </c>
       <c r="R25" t="n">
-        <v>7340837</v>
+        <v>7341325</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3251,22 +3256,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374118</v>
+        <v>125374075</v>
       </c>
       <c r="B26" t="n">
-        <v>92448</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,38 +3280,58 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780370</v>
+        <v>780877</v>
       </c>
       <c r="R26" t="n">
-        <v>7341315</v>
+        <v>7340946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,14 +3361,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>4 st</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3358,22 +3388,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125378920</v>
+        <v>125374114</v>
       </c>
       <c r="B27" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3382,41 +3412,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780413</v>
+        <v>780332</v>
       </c>
       <c r="R27" t="n">
-        <v>7341084</v>
+        <v>7341182</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3448,35 +3478,39 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125378905</v>
+        <v>125368564</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>90204</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3489,41 +3523,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780354</v>
+        <v>780518</v>
       </c>
       <c r="R28" t="n">
-        <v>7341159</v>
+        <v>7341011</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3553,11 +3583,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374078</v>
+        <v>125378905</v>
       </c>
       <c r="B29" t="n">
-        <v>78971</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3596,41 +3621,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780705</v>
+        <v>780354</v>
       </c>
       <c r="R29" t="n">
-        <v>7340829</v>
+        <v>7341159</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3660,6 +3689,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,22 +3708,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125378926</v>
+        <v>125378911</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3702,21 +3736,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3726,10 +3760,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780493</v>
+        <v>780332</v>
       </c>
       <c r="R30" t="n">
-        <v>7341109</v>
+        <v>7341195</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3762,6 +3796,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3788,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125368577</v>
+        <v>125374103</v>
       </c>
       <c r="B31" t="n">
-        <v>78683</v>
+        <v>56836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3800,38 +3839,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780480</v>
+        <v>780777</v>
       </c>
       <c r="R31" t="n">
-        <v>7341033</v>
+        <v>7340841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3866,6 +3905,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3878,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125374125</v>
+        <v>125378919</v>
       </c>
       <c r="B32" t="n">
-        <v>91573</v>
+        <v>78684</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3902,25 +3946,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3930,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780339</v>
+        <v>780397</v>
       </c>
       <c r="R32" t="n">
-        <v>7341191</v>
+        <v>7341092</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3974,28 +4018,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125374129</v>
+        <v>125368562</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4004,25 +4049,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4032,13 +4077,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780323</v>
+        <v>780722</v>
       </c>
       <c r="R33" t="n">
-        <v>7341197</v>
+        <v>7340838</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4082,22 +4127,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125368575</v>
+        <v>125374116</v>
       </c>
       <c r="B34" t="n">
-        <v>92646</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,34 +4155,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780910</v>
+        <v>780554</v>
       </c>
       <c r="R34" t="n">
-        <v>7340862</v>
+        <v>7340907</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4184,22 +4229,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125368562</v>
+        <v>125374118</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4208,25 +4253,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4236,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780722</v>
+        <v>780370</v>
       </c>
       <c r="R35" t="n">
-        <v>7340838</v>
+        <v>7341315</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,6 +4319,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4286,22 +4336,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374123</v>
+        <v>125368566</v>
       </c>
       <c r="B36" t="n">
-        <v>92448</v>
+        <v>90204</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4310,25 +4360,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4388,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780428</v>
+        <v>780905</v>
       </c>
       <c r="R36" t="n">
-        <v>7341058</v>
+        <v>7340863</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,11 +4426,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4393,22 +4438,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125376207</v>
+        <v>125374101</v>
       </c>
       <c r="B37" t="n">
-        <v>92448</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4417,38 +4462,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780564</v>
+        <v>780924</v>
       </c>
       <c r="R37" t="n">
-        <v>7340973</v>
+        <v>7340886</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4483,6 +4528,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4495,22 +4545,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125376201</v>
+        <v>125378926</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4519,25 +4569,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,13 +4597,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780318</v>
+        <v>780493</v>
       </c>
       <c r="R38" t="n">
-        <v>7341215</v>
+        <v>7341109</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4597,22 +4647,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374094</v>
+        <v>125368582</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>91326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4621,38 +4671,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780904</v>
+        <v>780634</v>
       </c>
       <c r="R39" t="n">
-        <v>7340832</v>
+        <v>7340886</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4693,28 +4746,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125374099</v>
+        <v>125374131</v>
       </c>
       <c r="B40" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4723,25 +4777,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,13 +4805,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780470</v>
+        <v>780341</v>
       </c>
       <c r="R40" t="n">
-        <v>7341026</v>
+        <v>7341192</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4801,22 +4855,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125378919</v>
+        <v>125368592</v>
       </c>
       <c r="B41" t="n">
-        <v>78684</v>
+        <v>75017</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4883,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,13 +4907,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780397</v>
+        <v>780845</v>
       </c>
       <c r="R41" t="n">
-        <v>7341092</v>
+        <v>7340863</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4897,29 +4951,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125378911</v>
+        <v>125374096</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
+        <v>92448</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4928,25 +4981,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4956,13 +5009,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780332</v>
+        <v>780394</v>
       </c>
       <c r="R42" t="n">
-        <v>7341195</v>
+        <v>7341123</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4992,11 +5045,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5011,22 +5059,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374096</v>
+        <v>125368577</v>
       </c>
       <c r="B43" t="n">
-        <v>92448</v>
+        <v>78683</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,25 +5083,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5063,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780394</v>
+        <v>780480</v>
       </c>
       <c r="R43" t="n">
-        <v>7341123</v>
+        <v>7341033</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5113,22 +5161,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125368595</v>
+        <v>125368591</v>
       </c>
       <c r="B44" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,25 +5185,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5165,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780561</v>
+        <v>780620</v>
       </c>
       <c r="R44" t="n">
-        <v>7340968</v>
+        <v>7340897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5227,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125368586</v>
+        <v>125374090</v>
       </c>
       <c r="B45" t="n">
         <v>78947</v>
@@ -5267,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780564</v>
+        <v>780353</v>
       </c>
       <c r="R45" t="n">
-        <v>7341334</v>
+        <v>7341186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5317,22 +5365,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125368573</v>
+        <v>125374080</v>
       </c>
       <c r="B46" t="n">
-        <v>91459</v>
+        <v>78684</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5345,21 +5393,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5369,10 +5417,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>780591</v>
+        <v>780787</v>
       </c>
       <c r="R46" t="n">
-        <v>7341254</v>
+        <v>7340766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5419,22 +5467,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125368571</v>
+        <v>125378920</v>
       </c>
       <c r="B47" t="n">
-        <v>92476</v>
+        <v>78684</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5447,21 +5495,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,13 +5519,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780646</v>
+        <v>780413</v>
       </c>
       <c r="R47" t="n">
-        <v>7340861</v>
+        <v>7341084</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5515,28 +5563,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125368574</v>
+        <v>125374092</v>
       </c>
       <c r="B48" t="n">
-        <v>56839</v>
+        <v>78947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5545,25 +5594,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5573,10 +5622,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780624</v>
+        <v>780743</v>
       </c>
       <c r="R48" t="n">
-        <v>7340950</v>
+        <v>7340811</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,22 +5672,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125368591</v>
+        <v>125374105</v>
       </c>
       <c r="B49" t="n">
-        <v>92448</v>
+        <v>91186</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5647,38 +5696,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780620</v>
+        <v>780579</v>
       </c>
       <c r="R49" t="n">
-        <v>7340897</v>
+        <v>7341020</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5725,22 +5774,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125378917</v>
+        <v>125374078</v>
       </c>
       <c r="B50" t="n">
-        <v>56836</v>
+        <v>78971</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5753,41 +5802,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780909</v>
+        <v>780705</v>
       </c>
       <c r="R50" t="n">
-        <v>7340823</v>
+        <v>7340829</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5817,11 +5862,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5836,22 +5876,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125374109</v>
+        <v>125368590</v>
       </c>
       <c r="B51" t="n">
-        <v>56836</v>
+        <v>78592</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5860,25 +5900,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5888,10 +5928,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780890</v>
+        <v>780707</v>
       </c>
       <c r="R51" t="n">
-        <v>7340825</v>
+        <v>7340834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5926,11 +5966,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5943,22 +5978,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374116</v>
+        <v>125376201</v>
       </c>
       <c r="B52" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5967,38 +6002,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780554</v>
+        <v>780318</v>
       </c>
       <c r="R52" t="n">
-        <v>7340907</v>
+        <v>7341215</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6045,22 +6080,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125376205</v>
+        <v>125368571</v>
       </c>
       <c r="B53" t="n">
-        <v>78947</v>
+        <v>92476</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6073,21 +6108,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6097,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780453</v>
+        <v>780646</v>
       </c>
       <c r="R53" t="n">
-        <v>7341309</v>
+        <v>7340861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6147,22 +6182,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374105</v>
+        <v>125374088</v>
       </c>
       <c r="B54" t="n">
-        <v>91186</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6175,34 +6210,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780579</v>
+        <v>780658</v>
       </c>
       <c r="R54" t="n">
-        <v>7341020</v>
+        <v>7340942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6249,22 +6284,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125368579</v>
+        <v>125374124</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6273,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6301,13 +6336,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780564</v>
+        <v>780876</v>
       </c>
       <c r="R55" t="n">
-        <v>7341334</v>
+        <v>7340837</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6351,22 +6386,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125376203</v>
+        <v>125374099</v>
       </c>
       <c r="B56" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6375,25 +6410,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6403,10 +6438,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780331</v>
+        <v>780470</v>
       </c>
       <c r="R56" t="n">
-        <v>7341207</v>
+        <v>7341026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6453,22 +6488,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374131</v>
+        <v>125374109</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6477,25 +6512,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6505,13 +6540,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780341</v>
+        <v>780890</v>
       </c>
       <c r="R57" t="n">
-        <v>7341192</v>
+        <v>7340825</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6541,6 +6576,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6555,19 +6595,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125368563</v>
+        <v>125378902</v>
       </c>
       <c r="B58" t="n">
         <v>79565</v>
@@ -6607,13 +6647,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780865</v>
+        <v>780545</v>
       </c>
       <c r="R58" t="n">
-        <v>7340858</v>
+        <v>7341029</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6657,22 +6697,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125374088</v>
+        <v>125378917</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6681,41 +6721,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780658</v>
+        <v>780909</v>
       </c>
       <c r="R59" t="n">
-        <v>7340942</v>
+        <v>7340823</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6745,6 +6789,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6759,22 +6808,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125368566</v>
+        <v>125368593</v>
       </c>
       <c r="B60" t="n">
-        <v>90204</v>
+        <v>77874</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6787,21 +6836,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6811,10 +6860,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780905</v>
+        <v>780561</v>
       </c>
       <c r="R60" t="n">
-        <v>7340863</v>
+        <v>7340968</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6873,10 +6922,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125378902</v>
+        <v>125374086</v>
       </c>
       <c r="B61" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6889,21 +6938,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6913,13 +6962,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780545</v>
+        <v>780521</v>
       </c>
       <c r="R61" t="n">
-        <v>7341029</v>
+        <v>7341051</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6963,19 +7012,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125368587</v>
+        <v>125378929</v>
       </c>
       <c r="B62" t="n">
         <v>78947</v>
@@ -7015,13 +7064,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780344</v>
+        <v>780910</v>
       </c>
       <c r="R62" t="n">
-        <v>7341144</v>
+        <v>7340820</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7065,22 +7114,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125378929</v>
+        <v>125378906</v>
       </c>
       <c r="B63" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7093,21 +7142,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7117,10 +7166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780910</v>
+        <v>780955</v>
       </c>
       <c r="R63" t="n">
-        <v>7340820</v>
+        <v>7340788</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7179,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374114</v>
+        <v>125368578</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7191,38 +7240,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780332</v>
+        <v>780865</v>
       </c>
       <c r="R64" t="n">
-        <v>7341182</v>
+        <v>7340858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7257,11 +7306,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7274,22 +7318,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374101</v>
+        <v>125368584</v>
       </c>
       <c r="B65" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7302,34 +7346,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780924</v>
+        <v>780566</v>
       </c>
       <c r="R65" t="n">
-        <v>7340886</v>
+        <v>7341030</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7364,11 +7408,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7381,22 +7420,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125374108</v>
+        <v>125374111</v>
       </c>
       <c r="B66" t="n">
-        <v>91459</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7405,25 +7444,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7433,10 +7472,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780597</v>
+        <v>780311</v>
       </c>
       <c r="R66" t="n">
-        <v>7341251</v>
+        <v>7341211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7469,6 +7508,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7495,10 +7539,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374119</v>
+        <v>125368580</v>
       </c>
       <c r="B67" t="n">
-        <v>91573</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7507,25 +7551,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7535,10 +7579,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780501</v>
+        <v>780337</v>
       </c>
       <c r="R67" t="n">
-        <v>7341325</v>
+        <v>7341192</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7573,6 +7617,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>100-tals</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7585,22 +7634,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125374103</v>
+        <v>125376197</v>
       </c>
       <c r="B68" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7609,38 +7658,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780777</v>
+        <v>780912</v>
       </c>
       <c r="R68" t="n">
-        <v>7340841</v>
+        <v>7340859</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7675,11 +7724,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7692,22 +7736,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125378924</v>
+        <v>125368575</v>
       </c>
       <c r="B69" t="n">
-        <v>78947</v>
+        <v>92646</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7720,21 +7764,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7744,13 +7788,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780766</v>
+        <v>780910</v>
       </c>
       <c r="R69" t="n">
-        <v>7340885</v>
+        <v>7340862</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7794,22 +7838,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125374111</v>
+        <v>125368568</v>
       </c>
       <c r="B70" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7818,38 +7862,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780311</v>
+        <v>780597</v>
       </c>
       <c r="R70" t="n">
-        <v>7341211</v>
+        <v>7341251</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7884,11 +7928,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7901,12 +7940,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8020,10 +8059,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125374084</v>
+        <v>125378924</v>
       </c>
       <c r="B72" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8036,21 +8075,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8060,13 +8099,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780527</v>
+        <v>780766</v>
       </c>
       <c r="R72" t="n">
-        <v>7341044</v>
+        <v>7340885</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8110,22 +8149,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125374090</v>
+        <v>125368573</v>
       </c>
       <c r="B73" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8138,21 +8177,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8162,10 +8201,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780353</v>
+        <v>780591</v>
       </c>
       <c r="R73" t="n">
-        <v>7341186</v>
+        <v>7341254</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8212,22 +8251,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374080</v>
+        <v>125374094</v>
       </c>
       <c r="B74" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8240,21 +8279,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8264,10 +8303,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780787</v>
+        <v>780904</v>
       </c>
       <c r="R74" t="n">
-        <v>7340766</v>
+        <v>7340832</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8326,10 +8365,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374127</v>
+        <v>125374084</v>
       </c>
       <c r="B75" t="n">
-        <v>56836</v>
+        <v>78683</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8338,25 +8377,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8366,13 +8405,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780447</v>
+        <v>780527</v>
       </c>
       <c r="R75" t="n">
-        <v>7341241</v>
+        <v>7341044</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8402,11 +8441,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8421,22 +8455,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125378928</v>
+        <v>125376203</v>
       </c>
       <c r="B76" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8445,25 +8479,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8473,13 +8507,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780881</v>
+        <v>780331</v>
       </c>
       <c r="R76" t="n">
-        <v>7340820</v>
+        <v>7341207</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8523,22 +8557,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125368582</v>
+        <v>125374123</v>
       </c>
       <c r="B77" t="n">
-        <v>91326</v>
+        <v>92448</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8547,41 +8581,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780634</v>
+        <v>780428</v>
       </c>
       <c r="R77" t="n">
-        <v>7340886</v>
+        <v>7341058</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8616,35 +8647,39 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125368580</v>
+        <v>125378930</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8653,25 +8688,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8681,13 +8716,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780337</v>
+        <v>780354</v>
       </c>
       <c r="R78" t="n">
-        <v>7341192</v>
+        <v>7341240</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8717,11 +8752,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8736,22 +8766,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374075</v>
+        <v>125374125</v>
       </c>
       <c r="B79" t="n">
-        <v>57635</v>
+        <v>91573</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8760,61 +8790,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780877</v>
+        <v>780339</v>
       </c>
       <c r="R79" t="n">
-        <v>7340946</v>
+        <v>7341191</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8841,19 +8851,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8868,22 +8868,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125378906</v>
+        <v>125376199</v>
       </c>
       <c r="B80" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8892,25 +8892,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8920,13 +8920,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780955</v>
+        <v>780542</v>
       </c>
       <c r="R80" t="n">
-        <v>7340788</v>
+        <v>7341352</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8970,22 +8970,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420107</v>
+        <v>125420098</v>
       </c>
       <c r="B81" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780339</v>
+        <v>780771</v>
       </c>
       <c r="R81" t="n">
-        <v>7341160</v>
+        <v>7340901</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9058,6 +9058,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9084,10 +9089,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420109</v>
+        <v>125378915</v>
       </c>
       <c r="B82" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9100,37 +9105,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780379</v>
+        <v>780825</v>
       </c>
       <c r="R82" t="n">
-        <v>7341130</v>
+        <v>7340795</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9160,6 +9169,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9174,22 +9188,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420098</v>
+        <v>125420113</v>
       </c>
       <c r="B83" t="n">
-        <v>78947</v>
+        <v>97153</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9198,25 +9212,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9226,10 +9240,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>780771</v>
+        <v>780740</v>
       </c>
       <c r="R83" t="n">
-        <v>7340901</v>
+        <v>7340806</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9262,11 +9276,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9293,10 +9302,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125378915</v>
+        <v>125420111</v>
       </c>
       <c r="B84" t="n">
-        <v>57635</v>
+        <v>92646</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9309,41 +9318,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>780825</v>
+        <v>780605</v>
       </c>
       <c r="R84" t="n">
-        <v>7340795</v>
+        <v>7340903</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9373,11 +9378,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9392,22 +9392,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125378914</v>
+        <v>125420110</v>
       </c>
       <c r="B85" t="n">
-        <v>57635</v>
+        <v>92476</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9420,41 +9420,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780360</v>
+        <v>780581</v>
       </c>
       <c r="R85" t="n">
-        <v>7341113</v>
+        <v>7340927</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9484,11 +9480,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9503,22 +9494,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420113</v>
+        <v>125420107</v>
       </c>
       <c r="B86" t="n">
-        <v>97153</v>
+        <v>91166</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9527,25 +9518,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9555,10 +9546,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780740</v>
+        <v>780339</v>
       </c>
       <c r="R86" t="n">
-        <v>7340806</v>
+        <v>7341160</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9617,10 +9608,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420110</v>
+        <v>125420114</v>
       </c>
       <c r="B87" t="n">
-        <v>92476</v>
+        <v>92646</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9633,21 +9624,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9657,10 +9648,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780581</v>
+        <v>780701</v>
       </c>
       <c r="R87" t="n">
-        <v>7340927</v>
+        <v>7340825</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9719,10 +9710,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125420097</v>
+        <v>125420106</v>
       </c>
       <c r="B88" t="n">
-        <v>90204</v>
+        <v>56836</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9731,38 +9722,46 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>780875</v>
+        <v>780582</v>
       </c>
       <c r="R88" t="n">
-        <v>7340884</v>
+        <v>7340956</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9821,10 +9820,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125420111</v>
+        <v>125420109</v>
       </c>
       <c r="B89" t="n">
-        <v>92646</v>
+        <v>88512</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9837,21 +9836,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9861,10 +9860,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780605</v>
+        <v>780379</v>
       </c>
       <c r="R89" t="n">
-        <v>7340903</v>
+        <v>7341130</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9923,10 +9922,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125420114</v>
+        <v>125420097</v>
       </c>
       <c r="B90" t="n">
-        <v>92646</v>
+        <v>90204</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9939,21 +9938,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9963,10 +9962,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780701</v>
+        <v>780875</v>
       </c>
       <c r="R90" t="n">
-        <v>7340825</v>
+        <v>7340884</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10025,10 +10024,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125420106</v>
+        <v>125378914</v>
       </c>
       <c r="B91" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10037,35 +10036,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10073,13 +10068,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>780582</v>
+        <v>780360</v>
       </c>
       <c r="R91" t="n">
-        <v>7340956</v>
+        <v>7341113</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10109,6 +10104,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10123,12 +10123,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -2443,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125374129</v>
+        <v>125368563</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2455,25 +2455,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780323</v>
+        <v>780865</v>
       </c>
       <c r="R18" t="n">
-        <v>7341197</v>
+        <v>7340858</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,22 +2533,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125368563</v>
+        <v>125368586</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780865</v>
+        <v>780564</v>
       </c>
       <c r="R19" t="n">
-        <v>7340858</v>
+        <v>7341334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368586</v>
+        <v>125374129</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,25 +2659,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780564</v>
+        <v>780323</v>
       </c>
       <c r="R20" t="n">
-        <v>7341334</v>
+        <v>7341197</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125378916</v>
+        <v>125374075</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2863,45 +2863,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780956</v>
+        <v>780877</v>
       </c>
       <c r="R22" t="n">
-        <v>7340785</v>
+        <v>7340946</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,14 +2944,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,22 +2971,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125376207</v>
+        <v>125378916</v>
       </c>
       <c r="B23" t="n">
-        <v>92448</v>
+        <v>56836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,37 +2999,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780564</v>
+        <v>780956</v>
       </c>
       <c r="R23" t="n">
-        <v>7340973</v>
+        <v>7340785</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3038,6 +3063,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,22 +3082,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125368595</v>
+        <v>125376207</v>
       </c>
       <c r="B24" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,25 +3106,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3104,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780561</v>
+        <v>780564</v>
       </c>
       <c r="R24" t="n">
-        <v>7340968</v>
+        <v>7340973</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,22 +3184,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125374119</v>
+        <v>125368595</v>
       </c>
       <c r="B25" t="n">
-        <v>91573</v>
+        <v>78331</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,25 +3208,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4217</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780501</v>
+        <v>780561</v>
       </c>
       <c r="R25" t="n">
-        <v>7341325</v>
+        <v>7340968</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,22 +3286,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374075</v>
+        <v>125374119</v>
       </c>
       <c r="B26" t="n">
-        <v>57635</v>
+        <v>91573</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3280,58 +3310,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780877</v>
+        <v>780501</v>
       </c>
       <c r="R26" t="n">
-        <v>7340946</v>
+        <v>7341325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,19 +3371,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,22 +3388,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125374114</v>
+        <v>125368564</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
+        <v>90204</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3412,38 +3412,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780332</v>
+        <v>780518</v>
       </c>
       <c r="R27" t="n">
-        <v>7341182</v>
+        <v>7341011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,11 +3478,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3495,22 +3490,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125368564</v>
+        <v>125374103</v>
       </c>
       <c r="B28" t="n">
-        <v>90204</v>
+        <v>56836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3519,38 +3514,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780518</v>
+        <v>780777</v>
       </c>
       <c r="R28" t="n">
-        <v>7341011</v>
+        <v>7340841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3585,6 +3580,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3597,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125378905</v>
+        <v>125374114</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,45 +3621,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780354</v>
+        <v>780332</v>
       </c>
       <c r="R29" t="n">
-        <v>7341159</v>
+        <v>7341182</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3693,7 +3689,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ring hack</t>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,19 +3704,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125378911</v>
+        <v>125378905</v>
       </c>
       <c r="B30" t="n">
         <v>57635</v>
@@ -3754,16 +3750,20 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780332</v>
+        <v>780354</v>
       </c>
       <c r="R30" t="n">
-        <v>7341195</v>
+        <v>7341159</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374103</v>
+        <v>125378911</v>
       </c>
       <c r="B31" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,41 +3839,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780777</v>
+        <v>780332</v>
       </c>
       <c r="R31" t="n">
-        <v>7340841</v>
+        <v>7341195</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125378919</v>
+        <v>125368562</v>
       </c>
       <c r="B32" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780397</v>
+        <v>780722</v>
       </c>
       <c r="R32" t="n">
-        <v>7341092</v>
+        <v>7340838</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4018,29 +4018,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125368562</v>
+        <v>125374116</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4053,34 +4052,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780722</v>
+        <v>780554</v>
       </c>
       <c r="R33" t="n">
-        <v>7340838</v>
+        <v>7340907</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,22 +4126,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374116</v>
+        <v>125374118</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,38 +4150,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780554</v>
+        <v>780370</v>
       </c>
       <c r="R34" t="n">
-        <v>7340907</v>
+        <v>7341315</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,6 +4216,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4229,22 +4233,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125374118</v>
+        <v>125378919</v>
       </c>
       <c r="B35" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4253,25 +4257,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4281,13 +4285,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780370</v>
+        <v>780397</v>
       </c>
       <c r="R35" t="n">
-        <v>7341315</v>
+        <v>7341092</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4319,29 +4323,25 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4 st</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368592</v>
+        <v>125374096</v>
       </c>
       <c r="B41" t="n">
-        <v>75017</v>
+        <v>92448</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780845</v>
+        <v>780394</v>
       </c>
       <c r="R41" t="n">
-        <v>7340863</v>
+        <v>7341123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,22 +4957,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374096</v>
+        <v>125368577</v>
       </c>
       <c r="B42" t="n">
-        <v>92448</v>
+        <v>78683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780394</v>
+        <v>780480</v>
       </c>
       <c r="R42" t="n">
-        <v>7341123</v>
+        <v>7341033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,22 +5059,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125368577</v>
+        <v>125368591</v>
       </c>
       <c r="B43" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5083,25 +5083,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780480</v>
+        <v>780620</v>
       </c>
       <c r="R43" t="n">
-        <v>7341033</v>
+        <v>7340897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125368591</v>
+        <v>125374090</v>
       </c>
       <c r="B44" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,25 +5185,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780620</v>
+        <v>780353</v>
       </c>
       <c r="R44" t="n">
-        <v>7340897</v>
+        <v>7341186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,22 +5263,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374090</v>
+        <v>125368592</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
+        <v>75017</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780353</v>
+        <v>780845</v>
       </c>
       <c r="R45" t="n">
-        <v>7341186</v>
+        <v>7340863</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5365,12 +5365,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125368578</v>
+        <v>125376197</v>
       </c>
       <c r="B64" t="n">
-        <v>78683</v>
+        <v>57635</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7244,21 +7244,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780865</v>
+        <v>780912</v>
       </c>
       <c r="R64" t="n">
-        <v>7340858</v>
+        <v>7340859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,22 +7318,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125368584</v>
+        <v>125368578</v>
       </c>
       <c r="B65" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7346,21 +7346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780566</v>
+        <v>780865</v>
       </c>
       <c r="R65" t="n">
-        <v>7341030</v>
+        <v>7340858</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125374111</v>
+        <v>125368584</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7444,38 +7444,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780311</v>
+        <v>780566</v>
       </c>
       <c r="R66" t="n">
-        <v>7341211</v>
+        <v>7341030</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7510,11 +7510,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7527,19 +7522,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125368580</v>
+        <v>125374111</v>
       </c>
       <c r="B67" t="n">
         <v>98269</v>
@@ -7575,14 +7570,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780337</v>
+        <v>780311</v>
       </c>
       <c r="R67" t="n">
-        <v>7341192</v>
+        <v>7341211</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7619,7 +7614,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>100-tals</t>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7634,22 +7629,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125376197</v>
+        <v>125368580</v>
       </c>
       <c r="B68" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7658,25 +7653,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7686,10 +7681,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>780912</v>
+        <v>780337</v>
       </c>
       <c r="R68" t="n">
-        <v>7340859</v>
+        <v>7341192</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7724,6 +7719,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>100-tals</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7736,12 +7736,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3400,10 +3400,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125368564</v>
+        <v>125374114</v>
       </c>
       <c r="B27" t="n">
-        <v>90204</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3412,38 +3412,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780518</v>
+        <v>780332</v>
       </c>
       <c r="R27" t="n">
-        <v>7341011</v>
+        <v>7341182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,6 +3478,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3490,22 +3495,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374103</v>
+        <v>125368564</v>
       </c>
       <c r="B28" t="n">
-        <v>56836</v>
+        <v>90204</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3514,38 +3519,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780777</v>
+        <v>780518</v>
       </c>
       <c r="R28" t="n">
-        <v>7340841</v>
+        <v>7341011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,11 +3585,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3597,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374114</v>
+        <v>125378905</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,41 +3621,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780332</v>
+        <v>780354</v>
       </c>
       <c r="R29" t="n">
-        <v>7341182</v>
+        <v>7341159</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3689,7 +3693,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,19 +3708,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125378905</v>
+        <v>125378911</v>
       </c>
       <c r="B30" t="n">
         <v>57635</v>
@@ -3750,20 +3754,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780354</v>
+        <v>780332</v>
       </c>
       <c r="R30" t="n">
-        <v>7341159</v>
+        <v>7341195</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ring hack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125378911</v>
+        <v>125374103</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,41 +3839,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780332</v>
+        <v>780777</v>
       </c>
       <c r="R31" t="n">
-        <v>7341195</v>
+        <v>7340841</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,12 +3922,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374096</v>
+        <v>125368592</v>
       </c>
       <c r="B41" t="n">
-        <v>92448</v>
+        <v>75017</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780394</v>
+        <v>780845</v>
       </c>
       <c r="R41" t="n">
-        <v>7341123</v>
+        <v>7340863</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,22 +4957,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125368577</v>
+        <v>125374096</v>
       </c>
       <c r="B42" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780480</v>
+        <v>780394</v>
       </c>
       <c r="R42" t="n">
-        <v>7341033</v>
+        <v>7341123</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,22 +5059,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125368591</v>
+        <v>125368577</v>
       </c>
       <c r="B43" t="n">
-        <v>92448</v>
+        <v>78683</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5083,25 +5083,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780620</v>
+        <v>780480</v>
       </c>
       <c r="R43" t="n">
-        <v>7340897</v>
+        <v>7341033</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374090</v>
+        <v>125368591</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,25 +5185,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780353</v>
+        <v>780620</v>
       </c>
       <c r="R44" t="n">
-        <v>7341186</v>
+        <v>7340897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,22 +5263,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125368592</v>
+        <v>125374090</v>
       </c>
       <c r="B45" t="n">
-        <v>75017</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>780845</v>
+        <v>780353</v>
       </c>
       <c r="R45" t="n">
-        <v>7340863</v>
+        <v>7341186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5365,12 +5365,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125378920</v>
+        <v>125374092</v>
       </c>
       <c r="B47" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5495,21 +5495,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780413</v>
+        <v>780743</v>
       </c>
       <c r="R47" t="n">
-        <v>7341084</v>
+        <v>7340811</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5563,29 +5563,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125374092</v>
+        <v>125374105</v>
       </c>
       <c r="B48" t="n">
-        <v>78947</v>
+        <v>91186</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5598,34 +5597,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780743</v>
+        <v>780579</v>
       </c>
       <c r="R48" t="n">
-        <v>7340811</v>
+        <v>7341020</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5672,22 +5671,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374105</v>
+        <v>125374078</v>
       </c>
       <c r="B49" t="n">
-        <v>91186</v>
+        <v>78971</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5696,38 +5695,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780579</v>
+        <v>780705</v>
       </c>
       <c r="R49" t="n">
-        <v>7341020</v>
+        <v>7340829</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,22 +5773,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374078</v>
+        <v>125378920</v>
       </c>
       <c r="B50" t="n">
-        <v>78971</v>
+        <v>78684</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5798,25 +5797,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5826,13 +5825,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780705</v>
+        <v>780413</v>
       </c>
       <c r="R50" t="n">
-        <v>7340829</v>
+        <v>7341084</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5870,18 +5869,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6500,10 +6500,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374109</v>
+        <v>125378902</v>
       </c>
       <c r="B57" t="n">
-        <v>56836</v>
+        <v>79565</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6512,25 +6512,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780890</v>
+        <v>780545</v>
       </c>
       <c r="R57" t="n">
-        <v>7340825</v>
+        <v>7341029</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6576,11 +6576,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6595,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125378902</v>
+        <v>125374109</v>
       </c>
       <c r="B58" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6619,25 +6614,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6647,13 +6642,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780545</v>
+        <v>780890</v>
       </c>
       <c r="R58" t="n">
-        <v>7341029</v>
+        <v>7340825</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6683,6 +6678,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125368563</v>
+        <v>125374094</v>
       </c>
       <c r="B11" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780865</v>
+        <v>780904</v>
       </c>
       <c r="R11" t="n">
-        <v>7340858</v>
+        <v>7340832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,22 +1804,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125368562</v>
+        <v>125374088</v>
       </c>
       <c r="B12" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780722</v>
+        <v>780658</v>
       </c>
       <c r="R12" t="n">
-        <v>7340838</v>
+        <v>7340942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,22 +1901,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125374094</v>
+        <v>125368563</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780904</v>
+        <v>780865</v>
       </c>
       <c r="R13" t="n">
-        <v>7340832</v>
+        <v>7340858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,22 +1998,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125374088</v>
+        <v>125368562</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780658</v>
+        <v>780722</v>
       </c>
       <c r="R14" t="n">
-        <v>7340942</v>
+        <v>7340838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,12 +2095,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374108</v>
+        <v>125378906</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,37 +2633,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780597</v>
+        <v>780955</v>
       </c>
       <c r="R20" t="n">
-        <v>7341251</v>
+        <v>7340788</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368564</v>
+        <v>125374108</v>
       </c>
       <c r="B21" t="n">
-        <v>90258</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,34 +2730,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780518</v>
+        <v>780597</v>
       </c>
       <c r="R21" t="n">
-        <v>7341011</v>
+        <v>7341251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,22 +2804,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368593</v>
+        <v>125368564</v>
       </c>
       <c r="B22" t="n">
-        <v>77916</v>
+        <v>90258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780561</v>
+        <v>780518</v>
       </c>
       <c r="R22" t="n">
-        <v>7340968</v>
+        <v>7341011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125374086</v>
+        <v>125368593</v>
       </c>
       <c r="B23" t="n">
-        <v>78725</v>
+        <v>77916</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780521</v>
+        <v>780561</v>
       </c>
       <c r="R23" t="n">
-        <v>7341051</v>
+        <v>7340968</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,22 +2998,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125378906</v>
+        <v>125374086</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>78725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780955</v>
+        <v>780521</v>
       </c>
       <c r="R24" t="n">
-        <v>7340788</v>
+        <v>7341051</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3095,12 +3095,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374118</v>
+        <v>125376203</v>
       </c>
       <c r="B38" t="n">
-        <v>92502</v>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780370</v>
+        <v>780331</v>
       </c>
       <c r="R38" t="n">
-        <v>7341315</v>
+        <v>7341207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,11 +4457,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>4 st</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4474,19 +4469,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125376203</v>
+        <v>125374131</v>
       </c>
       <c r="B39" t="n">
         <v>98324</v>
@@ -4521,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780331</v>
+        <v>780341</v>
       </c>
       <c r="R39" t="n">
-        <v>7341207</v>
+        <v>7341192</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4571,44 +4566,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125374131</v>
+        <v>125368573</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>91513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,13 +4613,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780341</v>
+        <v>780591</v>
       </c>
       <c r="R40" t="n">
-        <v>7341192</v>
+        <v>7341254</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4668,44 +4663,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368573</v>
+        <v>125374118</v>
       </c>
       <c r="B41" t="n">
-        <v>91513</v>
+        <v>92502</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4715,10 +4710,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780591</v>
+        <v>780370</v>
       </c>
       <c r="R41" t="n">
-        <v>7341254</v>
+        <v>7341315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,6 +4748,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4765,12 +4765,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -7454,48 +7454,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368582</v>
+        <v>125368586</v>
       </c>
       <c r="B69" t="n">
-        <v>91380</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780634</v>
+        <v>780564</v>
       </c>
       <c r="R69" t="n">
-        <v>7340886</v>
+        <v>7341334</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7536,7 +7533,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7555,45 +7551,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125376197</v>
+        <v>125368582</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>91380</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780912</v>
+        <v>780634</v>
       </c>
       <c r="R70" t="n">
-        <v>7340859</v>
+        <v>7340886</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7634,28 +7633,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125368586</v>
+        <v>125376197</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7663,21 +7663,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780564</v>
+        <v>780912</v>
       </c>
       <c r="R71" t="n">
-        <v>7341334</v>
+        <v>7340859</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,12 +7737,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7851,32 +7851,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125376201</v>
+        <v>125368595</v>
       </c>
       <c r="B73" t="n">
-        <v>98324</v>
+        <v>78373</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780318</v>
+        <v>780561</v>
       </c>
       <c r="R73" t="n">
-        <v>7341215</v>
+        <v>7340968</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7936,44 +7936,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125368595</v>
+        <v>125376201</v>
       </c>
       <c r="B74" t="n">
-        <v>78373</v>
+        <v>98324</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780561</v>
+        <v>780318</v>
       </c>
       <c r="R74" t="n">
-        <v>7340968</v>
+        <v>7341215</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8033,44 +8033,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125368591</v>
+        <v>125368568</v>
       </c>
       <c r="B75" t="n">
-        <v>92502</v>
+        <v>91220</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780620</v>
+        <v>780597</v>
       </c>
       <c r="R75" t="n">
-        <v>7340897</v>
+        <v>7341251</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125368568</v>
+        <v>125374116</v>
       </c>
       <c r="B76" t="n">
-        <v>91220</v>
+        <v>78967</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,34 +8153,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780597</v>
+        <v>780554</v>
       </c>
       <c r="R76" t="n">
-        <v>7341251</v>
+        <v>7340907</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8227,19 +8227,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125374116</v>
+        <v>125374090</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -8270,14 +8270,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780554</v>
+        <v>780353</v>
       </c>
       <c r="R77" t="n">
-        <v>7340907</v>
+        <v>7341186</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8324,44 +8324,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374090</v>
+        <v>125368591</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>92502</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780353</v>
+        <v>780620</v>
       </c>
       <c r="R78" t="n">
-        <v>7341186</v>
+        <v>7340897</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8421,44 +8421,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125376205</v>
+        <v>125374099</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>92502</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780453</v>
+        <v>780470</v>
       </c>
       <c r="R79" t="n">
-        <v>7341309</v>
+        <v>7341026</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8518,44 +8518,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374099</v>
+        <v>125376205</v>
       </c>
       <c r="B80" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780470</v>
+        <v>780453</v>
       </c>
       <c r="R80" t="n">
-        <v>7341026</v>
+        <v>7341309</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8615,12 +8615,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125378915</v>
+        <v>125420114</v>
       </c>
       <c r="B89" t="n">
-        <v>57651</v>
+        <v>92700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9436,41 +9436,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780825</v>
+        <v>780701</v>
       </c>
       <c r="R89" t="n">
-        <v>7340795</v>
+        <v>7340825</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9500,11 +9496,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9519,22 +9510,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125420114</v>
+        <v>125378915</v>
       </c>
       <c r="B90" t="n">
-        <v>92700</v>
+        <v>57651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9542,37 +9533,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780701</v>
+        <v>780825</v>
       </c>
       <c r="R90" t="n">
-        <v>7340825</v>
+        <v>7340795</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9602,6 +9597,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9616,12 +9616,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1712,17 +1712,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125374094</v>
+        <v>125368563</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780904</v>
+        <v>780865</v>
       </c>
       <c r="R11" t="n">
-        <v>7340832</v>
+        <v>7340858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,22 +1804,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125374088</v>
+        <v>125368562</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780658</v>
+        <v>780722</v>
       </c>
       <c r="R12" t="n">
-        <v>7340942</v>
+        <v>7340838</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,22 +1901,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125368563</v>
+        <v>125374094</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780865</v>
+        <v>780904</v>
       </c>
       <c r="R13" t="n">
-        <v>7340858</v>
+        <v>7340832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,22 +1998,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125368562</v>
+        <v>125374088</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780722</v>
+        <v>780658</v>
       </c>
       <c r="R14" t="n">
-        <v>7340838</v>
+        <v>7340942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,12 +2095,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2204,32 +2204,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125376199</v>
+        <v>125378930</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>92509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780542</v>
+        <v>780354</v>
       </c>
       <c r="R16" t="n">
-        <v>7341352</v>
+        <v>7341240</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,12 +2289,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2398,48 +2398,68 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125378930</v>
+        <v>125374075</v>
       </c>
       <c r="B18" t="n">
-        <v>92502</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780354</v>
+        <v>780877</v>
       </c>
       <c r="R18" t="n">
-        <v>7341240</v>
+        <v>7340946</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2466,9 +2486,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,77 +2513,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125374075</v>
+        <v>125376199</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780877</v>
+        <v>780542</v>
       </c>
       <c r="R19" t="n">
-        <v>7340946</v>
+        <v>7341352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,19 +2593,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125374108</v>
+        <v>125368593</v>
       </c>
       <c r="B21" t="n">
-        <v>91513</v>
+        <v>77916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,34 +2730,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780597</v>
+        <v>780561</v>
       </c>
       <c r="R21" t="n">
-        <v>7341251</v>
+        <v>7340968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,22 +2804,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368564</v>
+        <v>125374108</v>
       </c>
       <c r="B22" t="n">
-        <v>90258</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,34 +2827,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780518</v>
+        <v>780597</v>
       </c>
       <c r="R22" t="n">
-        <v>7341011</v>
+        <v>7341251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,22 +2901,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368593</v>
+        <v>125368564</v>
       </c>
       <c r="B23" t="n">
-        <v>77916</v>
+        <v>90265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,21 +2924,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780561</v>
+        <v>780518</v>
       </c>
       <c r="R23" t="n">
-        <v>7340968</v>
+        <v>7341011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,32 +3107,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125368580</v>
+        <v>125378902</v>
       </c>
       <c r="B25" t="n">
-        <v>98324</v>
+        <v>79585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780337</v>
+        <v>780545</v>
       </c>
       <c r="R25" t="n">
-        <v>7341192</v>
+        <v>7341029</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3178,11 +3178,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,44 +3192,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125378902</v>
+        <v>125368580</v>
       </c>
       <c r="B26" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,13 +3239,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780545</v>
+        <v>780337</v>
       </c>
       <c r="R26" t="n">
-        <v>7341029</v>
+        <v>7341192</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,6 +3275,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>100-tals</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,12 +3294,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
         <v>125368569</v>
       </c>
       <c r="B28" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>125374123</v>
       </c>
       <c r="B30" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,32 +3699,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125376207</v>
+        <v>125368571</v>
       </c>
       <c r="B31" t="n">
-        <v>92502</v>
+        <v>92537</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780564</v>
+        <v>780646</v>
       </c>
       <c r="R31" t="n">
-        <v>7340973</v>
+        <v>7340861</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3784,44 +3784,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125374109</v>
+        <v>125368587</v>
       </c>
       <c r="B32" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780890</v>
+        <v>780344</v>
       </c>
       <c r="R32" t="n">
-        <v>7340825</v>
+        <v>7341144</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3869,11 +3869,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3886,44 +3881,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125374129</v>
+        <v>125378924</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3933,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780323</v>
+        <v>780766</v>
       </c>
       <c r="R33" t="n">
-        <v>7341197</v>
+        <v>7340885</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3983,44 +3978,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125378920</v>
+        <v>125376207</v>
       </c>
       <c r="B34" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4030,13 +4025,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780413</v>
+        <v>780564</v>
       </c>
       <c r="R34" t="n">
-        <v>7341084</v>
+        <v>7340973</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4074,51 +4069,50 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125368571</v>
+        <v>125374129</v>
       </c>
       <c r="B35" t="n">
-        <v>92530</v>
+        <v>98331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4128,13 +4122,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780646</v>
+        <v>780323</v>
       </c>
       <c r="R35" t="n">
-        <v>7340861</v>
+        <v>7341197</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,44 +4172,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125368587</v>
+        <v>125374109</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4225,10 +4219,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780344</v>
+        <v>780890</v>
       </c>
       <c r="R36" t="n">
-        <v>7341144</v>
+        <v>7340825</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4263,6 +4257,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4275,22 +4274,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125378924</v>
+        <v>125378920</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,21 +4297,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780766</v>
+        <v>780413</v>
       </c>
       <c r="R37" t="n">
-        <v>7340885</v>
+        <v>7341084</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4366,6 +4365,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>125376203</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>125374131</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125368573</v>
+        <v>125378926</v>
       </c>
       <c r="B40" t="n">
-        <v>91513</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,21 +4589,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780591</v>
+        <v>780493</v>
       </c>
       <c r="R40" t="n">
-        <v>7341254</v>
+        <v>7341109</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4663,12 +4663,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
         <v>125374118</v>
       </c>
       <c r="B41" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125378926</v>
+        <v>125368584</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780493</v>
+        <v>780566</v>
       </c>
       <c r="R42" t="n">
-        <v>7341109</v>
+        <v>7341030</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4862,22 +4862,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125368584</v>
+        <v>125368573</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>91520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780566</v>
+        <v>780591</v>
       </c>
       <c r="R43" t="n">
-        <v>7341030</v>
+        <v>7341254</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
         <v>125374132</v>
       </c>
       <c r="B45" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>125374119</v>
       </c>
       <c r="B46" t="n">
-        <v>91627</v>
+        <v>91634</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>125374096</v>
       </c>
       <c r="B47" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>125368575</v>
       </c>
       <c r="B48" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5466,45 +5466,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374114</v>
+        <v>125368577</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780332</v>
+        <v>780480</v>
       </c>
       <c r="R49" t="n">
-        <v>7341182</v>
+        <v>7341033</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5539,11 +5539,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5556,12 +5551,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5665,45 +5660,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125368590</v>
+        <v>125374114</v>
       </c>
       <c r="B51" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780707</v>
+        <v>780332</v>
       </c>
       <c r="R51" t="n">
-        <v>7340834</v>
+        <v>7341182</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,6 +5733,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5750,22 +5750,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125368577</v>
+        <v>125368590</v>
       </c>
       <c r="B52" t="n">
-        <v>78725</v>
+        <v>78634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780480</v>
+        <v>780707</v>
       </c>
       <c r="R52" t="n">
-        <v>7341033</v>
+        <v>7340834</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5965,32 +5965,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374125</v>
+        <v>125378928</v>
       </c>
       <c r="B54" t="n">
-        <v>91627</v>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780339</v>
+        <v>780881</v>
       </c>
       <c r="R54" t="n">
-        <v>7341191</v>
+        <v>7340820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6050,22 +6050,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125378928</v>
+        <v>125374105</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>91247</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,37 +6073,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780881</v>
+        <v>780579</v>
       </c>
       <c r="R55" t="n">
-        <v>7340820</v>
+        <v>7341020</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,60 +6147,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374105</v>
+        <v>125374125</v>
       </c>
       <c r="B56" t="n">
-        <v>91240</v>
+        <v>91634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780579</v>
+        <v>780339</v>
       </c>
       <c r="R56" t="n">
-        <v>7341020</v>
+        <v>7341191</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6244,12 +6244,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125368578</v>
+        <v>125374101</v>
       </c>
       <c r="B58" t="n">
-        <v>78725</v>
+        <v>57651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,34 +6364,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780865</v>
+        <v>780924</v>
       </c>
       <c r="R58" t="n">
-        <v>7340858</v>
+        <v>7340886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6426,6 +6426,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6438,22 +6443,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125374101</v>
+        <v>125368578</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>78725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,34 +6466,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780924</v>
+        <v>780865</v>
       </c>
       <c r="R59" t="n">
-        <v>7340886</v>
+        <v>7340858</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6523,11 +6528,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6540,12 +6540,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125374078</v>
+        <v>125378911</v>
       </c>
       <c r="B62" t="n">
-        <v>78991</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780705</v>
+        <v>780332</v>
       </c>
       <c r="R62" t="n">
-        <v>7340829</v>
+        <v>7341195</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6826,6 +6826,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6840,44 +6845,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125378911</v>
+        <v>125374078</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>78991</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6887,13 +6892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780332</v>
+        <v>780705</v>
       </c>
       <c r="R63" t="n">
-        <v>7341195</v>
+        <v>7340829</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6923,11 +6928,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6942,12 +6942,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6957,7 +6957,7 @@
         <v>125368566</v>
       </c>
       <c r="B64" t="n">
-        <v>90258</v>
+        <v>90265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>125374111</v>
       </c>
       <c r="B66" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>125368579</v>
       </c>
       <c r="B67" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7454,45 +7454,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368586</v>
+        <v>125368582</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>91387</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780564</v>
+        <v>780634</v>
       </c>
       <c r="R69" t="n">
-        <v>7341334</v>
+        <v>7340886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7533,6 +7536,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7551,48 +7555,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125368582</v>
+        <v>125376197</v>
       </c>
       <c r="B70" t="n">
-        <v>91380</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780634</v>
+        <v>780912</v>
       </c>
       <c r="R70" t="n">
-        <v>7340886</v>
+        <v>7340859</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7633,29 +7634,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125376197</v>
+        <v>125368586</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7663,21 +7663,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780912</v>
+        <v>780564</v>
       </c>
       <c r="R71" t="n">
-        <v>7340859</v>
+        <v>7341334</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,44 +7737,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125374127</v>
+        <v>125376201</v>
       </c>
       <c r="B72" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7784,13 +7784,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780447</v>
+        <v>780318</v>
       </c>
       <c r="R72" t="n">
-        <v>7341241</v>
+        <v>7341215</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7820,11 +7820,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7839,12 +7834,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7948,32 +7943,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125376201</v>
+        <v>125374127</v>
       </c>
       <c r="B74" t="n">
-        <v>98324</v>
+        <v>56843</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7983,13 +7978,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780318</v>
+        <v>780447</v>
       </c>
       <c r="R74" t="n">
-        <v>7341215</v>
+        <v>7341241</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8019,6 +8014,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8033,12 +8033,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8048,7 +8048,7 @@
         <v>125368568</v>
       </c>
       <c r="B75" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8239,32 +8239,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125374090</v>
+        <v>125368591</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780353</v>
+        <v>780620</v>
       </c>
       <c r="R77" t="n">
-        <v>7341186</v>
+        <v>7340897</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8324,44 +8324,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125368591</v>
+        <v>125374090</v>
       </c>
       <c r="B78" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780620</v>
+        <v>780353</v>
       </c>
       <c r="R78" t="n">
-        <v>7340897</v>
+        <v>7341186</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8421,44 +8421,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374099</v>
+        <v>125376205</v>
       </c>
       <c r="B79" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780470</v>
+        <v>780453</v>
       </c>
       <c r="R79" t="n">
-        <v>7341026</v>
+        <v>7341309</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8518,44 +8518,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125376205</v>
+        <v>125374099</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780453</v>
+        <v>780470</v>
       </c>
       <c r="R80" t="n">
-        <v>7341309</v>
+        <v>7341026</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8615,12 +8615,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
         <v>125420111</v>
       </c>
       <c r="B81" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>125420107</v>
       </c>
       <c r="B83" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>125420113</v>
       </c>
       <c r="B84" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>125420110</v>
       </c>
       <c r="B86" t="n">
-        <v>92530</v>
+        <v>92537</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>125420109</v>
       </c>
       <c r="B88" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125420114</v>
+        <v>125378915</v>
       </c>
       <c r="B89" t="n">
-        <v>92700</v>
+        <v>57651</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9436,37 +9436,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780701</v>
+        <v>780825</v>
       </c>
       <c r="R89" t="n">
-        <v>7340825</v>
+        <v>7340795</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9496,6 +9500,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9510,22 +9519,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125378915</v>
+        <v>125420114</v>
       </c>
       <c r="B90" t="n">
-        <v>57651</v>
+        <v>92707</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9533,41 +9542,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780825</v>
+        <v>780701</v>
       </c>
       <c r="R90" t="n">
-        <v>7340795</v>
+        <v>7340825</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9597,11 +9602,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9616,12 +9616,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9631,7 +9631,7 @@
         <v>125420097</v>
       </c>
       <c r="B91" t="n">
-        <v>90258</v>
+        <v>90265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -2816,10 +2816,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125374108</v>
+        <v>125374086</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>78725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,34 +2827,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780597</v>
+        <v>780521</v>
       </c>
       <c r="R22" t="n">
-        <v>7341251</v>
+        <v>7341051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,22 +2901,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368564</v>
+        <v>125374108</v>
       </c>
       <c r="B23" t="n">
-        <v>90265</v>
+        <v>91520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,34 +2924,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780518</v>
+        <v>780597</v>
       </c>
       <c r="R23" t="n">
-        <v>7341011</v>
+        <v>7341251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,22 +2998,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374086</v>
+        <v>125368564</v>
       </c>
       <c r="B24" t="n">
-        <v>78725</v>
+        <v>90265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780521</v>
+        <v>780518</v>
       </c>
       <c r="R24" t="n">
-        <v>7341051</v>
+        <v>7341011</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,12 +3095,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3204,32 +3204,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125368580</v>
+        <v>125374124</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780337</v>
+        <v>780876</v>
       </c>
       <c r="R26" t="n">
-        <v>7341192</v>
+        <v>7340837</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3275,11 +3275,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>100-tals</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,44 +3289,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125374124</v>
+        <v>125368580</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>780876</v>
+        <v>780337</v>
       </c>
       <c r="R27" t="n">
-        <v>7340837</v>
+        <v>7341192</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3377,6 +3372,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>100-tals</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,12 +3391,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4087,32 +4087,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125374129</v>
+        <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4122,13 +4122,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780323</v>
+        <v>780890</v>
       </c>
       <c r="R35" t="n">
-        <v>7341197</v>
+        <v>7340825</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,6 +4158,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4172,44 +4177,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374109</v>
+        <v>125378920</v>
       </c>
       <c r="B36" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4219,13 +4224,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780890</v>
+        <v>780413</v>
       </c>
       <c r="R36" t="n">
-        <v>7340825</v>
+        <v>7341084</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4257,61 +4262,57 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125378920</v>
+        <v>125374129</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780413</v>
+        <v>780323</v>
       </c>
       <c r="R37" t="n">
-        <v>7341084</v>
+        <v>7341197</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4365,51 +4366,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125376203</v>
+        <v>125378926</v>
       </c>
       <c r="B38" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780331</v>
+        <v>780493</v>
       </c>
       <c r="R38" t="n">
-        <v>7341207</v>
+        <v>7341109</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4469,44 +4469,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374131</v>
+        <v>125374118</v>
       </c>
       <c r="B39" t="n">
-        <v>98331</v>
+        <v>92509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780341</v>
+        <v>780370</v>
       </c>
       <c r="R39" t="n">
-        <v>7341192</v>
+        <v>7341315</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,6 +4552,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4566,19 +4571,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125378926</v>
+        <v>125368584</v>
       </c>
       <c r="B40" t="n">
         <v>78967</v>
@@ -4613,13 +4618,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780493</v>
+        <v>780566</v>
       </c>
       <c r="R40" t="n">
-        <v>7341109</v>
+        <v>7341030</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4663,44 +4668,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374118</v>
+        <v>125368573</v>
       </c>
       <c r="B41" t="n">
-        <v>92509</v>
+        <v>91520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4710,10 +4715,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780370</v>
+        <v>780591</v>
       </c>
       <c r="R41" t="n">
-        <v>7341315</v>
+        <v>7341254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,11 +4753,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>4 st</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4765,57 +4765,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125368584</v>
+        <v>125374103</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780566</v>
+        <v>780777</v>
       </c>
       <c r="R42" t="n">
-        <v>7341030</v>
+        <v>7340841</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,6 +4850,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4862,44 +4867,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125368573</v>
+        <v>125376203</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4909,10 +4914,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780591</v>
+        <v>780331</v>
       </c>
       <c r="R43" t="n">
-        <v>7341254</v>
+        <v>7341207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,60 +4964,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374103</v>
+        <v>125374131</v>
       </c>
       <c r="B44" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780777</v>
+        <v>780341</v>
       </c>
       <c r="R44" t="n">
-        <v>7340841</v>
+        <v>7341192</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5042,11 +5047,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5061,12 +5061,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125374101</v>
+        <v>125368578</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>78725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,34 +6364,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>780924</v>
+        <v>780865</v>
       </c>
       <c r="R58" t="n">
-        <v>7340886</v>
+        <v>7340858</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6426,11 +6426,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gamla spår</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6443,22 +6438,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125368578</v>
+        <v>125374101</v>
       </c>
       <c r="B59" t="n">
-        <v>78725</v>
+        <v>57651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6466,34 +6461,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>780865</v>
+        <v>780924</v>
       </c>
       <c r="R59" t="n">
-        <v>7340858</v>
+        <v>7340886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6528,6 +6523,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack gamla spår</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6540,22 +6540,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125378905</v>
+        <v>125374080</v>
       </c>
       <c r="B60" t="n">
-        <v>57651</v>
+        <v>78726</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6563,41 +6563,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780354</v>
+        <v>780787</v>
       </c>
       <c r="R60" t="n">
-        <v>7341159</v>
+        <v>7340766</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6627,11 +6623,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6646,22 +6637,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125374080</v>
+        <v>125378905</v>
       </c>
       <c r="B61" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6669,37 +6660,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780787</v>
+        <v>780354</v>
       </c>
       <c r="R61" t="n">
-        <v>7340766</v>
+        <v>7341159</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6729,6 +6724,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6743,12 +6743,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6954,48 +6954,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125368566</v>
+        <v>125378917</v>
       </c>
       <c r="B64" t="n">
-        <v>90265</v>
+        <v>56843</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780905</v>
+        <v>780909</v>
       </c>
       <c r="R64" t="n">
-        <v>7340863</v>
+        <v>7340823</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7025,6 +7029,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7039,64 +7048,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125378917</v>
+        <v>125368566</v>
       </c>
       <c r="B65" t="n">
-        <v>56843</v>
+        <v>90265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780909</v>
+        <v>780905</v>
       </c>
       <c r="R65" t="n">
-        <v>7340823</v>
+        <v>7340863</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7126,11 +7131,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,12 +7145,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8829,32 +8829,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420107</v>
+        <v>125420113</v>
       </c>
       <c r="B83" t="n">
-        <v>91227</v>
+        <v>97215</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>780339</v>
+        <v>780740</v>
       </c>
       <c r="R83" t="n">
-        <v>7341160</v>
+        <v>7340806</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8926,32 +8926,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420113</v>
+        <v>125420107</v>
       </c>
       <c r="B84" t="n">
-        <v>97215</v>
+        <v>91227</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>780740</v>
+        <v>780339</v>
       </c>
       <c r="R84" t="n">
-        <v>7340806</v>
+        <v>7341160</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125378915</v>
+        <v>125420114</v>
       </c>
       <c r="B89" t="n">
-        <v>57651</v>
+        <v>92707</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9436,41 +9436,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780825</v>
+        <v>780701</v>
       </c>
       <c r="R89" t="n">
-        <v>7340795</v>
+        <v>7340825</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9500,11 +9496,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9519,22 +9510,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125420114</v>
+        <v>125378915</v>
       </c>
       <c r="B90" t="n">
-        <v>92707</v>
+        <v>57651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9542,37 +9533,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780701</v>
+        <v>780825</v>
       </c>
       <c r="R90" t="n">
-        <v>7340825</v>
+        <v>7340795</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9602,6 +9597,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9616,12 +9616,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125378929</v>
+        <v>125368592</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>75058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,21 +2118,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780910</v>
+        <v>780845</v>
       </c>
       <c r="R15" t="n">
-        <v>7340820</v>
+        <v>7340863</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,60 +2192,80 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125378930</v>
+        <v>125374075</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780354</v>
+        <v>780877</v>
       </c>
       <c r="R16" t="n">
-        <v>7341240</v>
+        <v>7340946</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,9 +2292,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,44 +2319,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125368592</v>
+        <v>125376199</v>
       </c>
       <c r="B17" t="n">
-        <v>75058</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780845</v>
+        <v>780542</v>
       </c>
       <c r="R17" t="n">
-        <v>7340863</v>
+        <v>7341352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,22 +2416,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125374075</v>
+        <v>125378929</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,57 +2439,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780877</v>
+        <v>780910</v>
       </c>
       <c r="R18" t="n">
-        <v>7340946</v>
+        <v>7340820</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,19 +2496,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,44 +2513,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125376199</v>
+        <v>125378930</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>92509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780542</v>
+        <v>780354</v>
       </c>
       <c r="R19" t="n">
-        <v>7341352</v>
+        <v>7341240</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,12 +2610,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125374086</v>
+        <v>125374108</v>
       </c>
       <c r="B22" t="n">
-        <v>78725</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,34 +2827,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780521</v>
+        <v>780597</v>
       </c>
       <c r="R22" t="n">
-        <v>7341051</v>
+        <v>7341251</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,22 +2901,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125374108</v>
+        <v>125368564</v>
       </c>
       <c r="B23" t="n">
-        <v>91520</v>
+        <v>90265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,34 +2924,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780597</v>
+        <v>780518</v>
       </c>
       <c r="R23" t="n">
-        <v>7341251</v>
+        <v>7341011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,22 +2998,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125368564</v>
+        <v>125374086</v>
       </c>
       <c r="B24" t="n">
-        <v>90265</v>
+        <v>78725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780518</v>
+        <v>780521</v>
       </c>
       <c r="R24" t="n">
-        <v>7341011</v>
+        <v>7341051</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,12 +3095,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4189,32 +4189,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125378920</v>
+        <v>125374129</v>
       </c>
       <c r="B36" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780413</v>
+        <v>780323</v>
       </c>
       <c r="R36" t="n">
-        <v>7341084</v>
+        <v>7341197</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4268,51 +4268,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125374129</v>
+        <v>125378920</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>78726</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>780323</v>
+        <v>780413</v>
       </c>
       <c r="R37" t="n">
-        <v>7341197</v>
+        <v>7341084</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4366,18 +4365,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5660,45 +5660,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125374114</v>
+        <v>125368590</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>78634</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780332</v>
+        <v>780707</v>
       </c>
       <c r="R51" t="n">
-        <v>7341182</v>
+        <v>7340834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5733,11 +5733,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5750,57 +5745,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125368590</v>
+        <v>125374114</v>
       </c>
       <c r="B52" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780707</v>
+        <v>780332</v>
       </c>
       <c r="R52" t="n">
-        <v>7340834</v>
+        <v>7341182</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5835,6 +5830,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5847,12 +5847,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125378911</v>
+        <v>125374078</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>78991</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780332</v>
+        <v>780705</v>
       </c>
       <c r="R62" t="n">
-        <v>7341195</v>
+        <v>7340829</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6826,11 +6826,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6845,44 +6840,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125374078</v>
+        <v>125378911</v>
       </c>
       <c r="B63" t="n">
-        <v>78991</v>
+        <v>57651</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6892,13 +6887,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780705</v>
+        <v>780332</v>
       </c>
       <c r="R63" t="n">
-        <v>7340829</v>
+        <v>7341195</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6928,6 +6923,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6942,12 +6942,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8829,32 +8829,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125420113</v>
+        <v>125420107</v>
       </c>
       <c r="B83" t="n">
-        <v>97215</v>
+        <v>91227</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>780740</v>
+        <v>780339</v>
       </c>
       <c r="R83" t="n">
-        <v>7340806</v>
+        <v>7341160</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8926,32 +8926,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125420107</v>
+        <v>125420113</v>
       </c>
       <c r="B84" t="n">
-        <v>91227</v>
+        <v>97215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>780339</v>
+        <v>780740</v>
       </c>
       <c r="R84" t="n">
-        <v>7341160</v>
+        <v>7340806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9023,10 +9023,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420098</v>
+        <v>125378914</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9034,37 +9034,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780771</v>
+        <v>780360</v>
       </c>
       <c r="R85" t="n">
-        <v>7340901</v>
+        <v>7341113</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>flera draperade granar</t>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9113,22 +9117,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420110</v>
+        <v>125420098</v>
       </c>
       <c r="B86" t="n">
-        <v>92537</v>
+        <v>78967</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9136,21 +9140,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9160,10 +9164,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780581</v>
+        <v>780771</v>
       </c>
       <c r="R86" t="n">
-        <v>7340927</v>
+        <v>7340901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9196,6 +9200,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9222,10 +9231,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125378914</v>
+        <v>125420110</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>92537</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9233,41 +9242,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780360</v>
+        <v>780581</v>
       </c>
       <c r="R87" t="n">
-        <v>7341113</v>
+        <v>7340927</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9297,11 +9302,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9316,12 +9316,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125420114</v>
+        <v>125378915</v>
       </c>
       <c r="B89" t="n">
-        <v>92707</v>
+        <v>57651</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9436,37 +9436,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>780701</v>
+        <v>780825</v>
       </c>
       <c r="R89" t="n">
-        <v>7340825</v>
+        <v>7340795</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9496,6 +9500,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9510,22 +9519,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125378915</v>
+        <v>125420114</v>
       </c>
       <c r="B90" t="n">
-        <v>57651</v>
+        <v>92707</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9533,41 +9542,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>780825</v>
+        <v>780701</v>
       </c>
       <c r="R90" t="n">
-        <v>7340795</v>
+        <v>7340825</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9597,11 +9602,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>avskalat gran där den hittat föda</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9616,12 +9616,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125368563</v>
       </c>
       <c r="B11" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125368562</v>
       </c>
       <c r="B12" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>125374094</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>125374088</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>125368592</v>
       </c>
       <c r="B15" t="n">
-        <v>75058</v>
+        <v>75059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,32 +2331,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125376199</v>
+        <v>125378929</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780542</v>
+        <v>780910</v>
       </c>
       <c r="R17" t="n">
-        <v>7341352</v>
+        <v>7340820</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,44 +2416,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125378929</v>
+        <v>125378930</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780910</v>
+        <v>780354</v>
       </c>
       <c r="R18" t="n">
-        <v>7340820</v>
+        <v>7341240</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2525,32 +2525,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125378930</v>
+        <v>125376199</v>
       </c>
       <c r="B19" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780354</v>
+        <v>780542</v>
       </c>
       <c r="R19" t="n">
-        <v>7341240</v>
+        <v>7341352</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,22 +2610,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125378906</v>
+        <v>125368593</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>77917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780955</v>
+        <v>780561</v>
       </c>
       <c r="R20" t="n">
-        <v>7340788</v>
+        <v>7340968</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2707,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368593</v>
+        <v>125374086</v>
       </c>
       <c r="B21" t="n">
-        <v>77916</v>
+        <v>78726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780561</v>
+        <v>780521</v>
       </c>
       <c r="R21" t="n">
-        <v>7340968</v>
+        <v>7341051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,22 +2804,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125374108</v>
+        <v>125378906</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,37 +2827,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780597</v>
+        <v>780955</v>
       </c>
       <c r="R22" t="n">
-        <v>7341251</v>
+        <v>7340788</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2901,22 +2901,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368564</v>
+        <v>125374108</v>
       </c>
       <c r="B23" t="n">
-        <v>90265</v>
+        <v>91524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,34 +2924,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780518</v>
+        <v>780597</v>
       </c>
       <c r="R23" t="n">
-        <v>7341011</v>
+        <v>7341251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,22 +2998,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374086</v>
+        <v>125368564</v>
       </c>
       <c r="B24" t="n">
-        <v>78725</v>
+        <v>90266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780521</v>
+        <v>780518</v>
       </c>
       <c r="R24" t="n">
-        <v>7341051</v>
+        <v>7341011</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,12 +3095,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
         <v>125378902</v>
       </c>
       <c r="B25" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>125374124</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>125368580</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>125368569</v>
       </c>
       <c r="B28" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,32 +3597,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125374123</v>
+        <v>125374129</v>
       </c>
       <c r="B30" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3632,13 +3632,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780428</v>
+        <v>780323</v>
       </c>
       <c r="R30" t="n">
-        <v>7341058</v>
+        <v>7341197</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3668,11 +3668,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3687,44 +3682,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125368571</v>
+        <v>125374123</v>
       </c>
       <c r="B31" t="n">
-        <v>92537</v>
+        <v>92518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3734,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780646</v>
+        <v>780428</v>
       </c>
       <c r="R31" t="n">
-        <v>7340861</v>
+        <v>7341058</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3772,6 +3767,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3784,22 +3784,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125368587</v>
+        <v>125368571</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>92546</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780344</v>
+        <v>780646</v>
       </c>
       <c r="R32" t="n">
-        <v>7341144</v>
+        <v>7340861</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125378924</v>
+        <v>125368587</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780766</v>
+        <v>780344</v>
       </c>
       <c r="R33" t="n">
-        <v>7340885</v>
+        <v>7341144</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3978,44 +3978,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125376207</v>
+        <v>125378924</v>
       </c>
       <c r="B34" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780564</v>
+        <v>780766</v>
       </c>
       <c r="R34" t="n">
-        <v>7340973</v>
+        <v>7340885</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4075,22 +4075,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125374109</v>
+        <v>125376207</v>
       </c>
       <c r="B35" t="n">
-        <v>56843</v>
+        <v>92518</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780890</v>
+        <v>780564</v>
       </c>
       <c r="R35" t="n">
-        <v>7340825</v>
+        <v>7340973</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4160,11 +4160,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4177,44 +4172,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374129</v>
+        <v>125374109</v>
       </c>
       <c r="B36" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4224,13 +4219,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780323</v>
+        <v>780890</v>
       </c>
       <c r="R36" t="n">
-        <v>7341197</v>
+        <v>7340825</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4260,6 +4255,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4274,12 +4274,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
         <v>125378920</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4384,48 +4384,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125378926</v>
+        <v>125374103</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780493</v>
+        <v>780777</v>
       </c>
       <c r="R38" t="n">
-        <v>7341109</v>
+        <v>7340841</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4455,6 +4455,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4469,44 +4474,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374118</v>
+        <v>125378926</v>
       </c>
       <c r="B39" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4516,13 +4521,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780370</v>
+        <v>780493</v>
       </c>
       <c r="R39" t="n">
-        <v>7341315</v>
+        <v>7341109</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,11 +4557,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4571,44 +4571,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125368584</v>
+        <v>125374118</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780566</v>
+        <v>780370</v>
       </c>
       <c r="R40" t="n">
-        <v>7341030</v>
+        <v>7341315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,6 +4656,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4668,22 +4673,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368573</v>
+        <v>125368584</v>
       </c>
       <c r="B41" t="n">
-        <v>91520</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4691,21 +4696,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4715,10 +4720,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780591</v>
+        <v>780566</v>
       </c>
       <c r="R41" t="n">
-        <v>7341254</v>
+        <v>7341030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4777,45 +4782,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374103</v>
+        <v>125368573</v>
       </c>
       <c r="B42" t="n">
-        <v>56843</v>
+        <v>91524</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780777</v>
+        <v>780591</v>
       </c>
       <c r="R42" t="n">
-        <v>7340841</v>
+        <v>7341254</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,11 +4855,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4867,12 +4867,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4882,7 +4882,7 @@
         <v>125376203</v>
       </c>
       <c r="B43" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>125374131</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>125374132</v>
       </c>
       <c r="B45" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>125374119</v>
       </c>
       <c r="B46" t="n">
-        <v>91634</v>
+        <v>91638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>125374096</v>
       </c>
       <c r="B47" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>125368575</v>
       </c>
       <c r="B48" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>125368577</v>
       </c>
       <c r="B49" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>125374092</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5660,48 +5660,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125368590</v>
+        <v>125378916</v>
       </c>
       <c r="B51" t="n">
-        <v>78634</v>
+        <v>56843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780707</v>
+        <v>780956</v>
       </c>
       <c r="R51" t="n">
-        <v>7340834</v>
+        <v>7340785</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,6 +5735,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5745,12 +5754,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5760,7 +5769,7 @@
         <v>125374114</v>
       </c>
       <c r="B52" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5859,52 +5868,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125378916</v>
+        <v>125368590</v>
       </c>
       <c r="B53" t="n">
-        <v>56843</v>
+        <v>78635</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780956</v>
+        <v>780707</v>
       </c>
       <c r="R53" t="n">
-        <v>7340785</v>
+        <v>7340834</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5934,11 +5939,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5953,22 +5953,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125378928</v>
+        <v>125374084</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5976,21 +5976,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,13 +6000,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780881</v>
+        <v>780527</v>
       </c>
       <c r="R54" t="n">
-        <v>7340820</v>
+        <v>7341044</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374105</v>
+        <v>125378928</v>
       </c>
       <c r="B55" t="n">
-        <v>91247</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,37 +6073,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780579</v>
+        <v>780881</v>
       </c>
       <c r="R55" t="n">
-        <v>7341020</v>
+        <v>7340820</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,60 +6147,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374125</v>
+        <v>125374105</v>
       </c>
       <c r="B56" t="n">
-        <v>91634</v>
+        <v>91248</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780339</v>
+        <v>780579</v>
       </c>
       <c r="R56" t="n">
-        <v>7341191</v>
+        <v>7341020</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6244,44 +6244,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374084</v>
+        <v>125374125</v>
       </c>
       <c r="B57" t="n">
-        <v>78725</v>
+        <v>91638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4217</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780527</v>
+        <v>780339</v>
       </c>
       <c r="R57" t="n">
-        <v>7341044</v>
+        <v>7341191</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6341,12 +6341,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
         <v>125368578</v>
       </c>
       <c r="B58" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6552,10 +6552,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125374080</v>
+        <v>125378905</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6563,37 +6563,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>780787</v>
+        <v>780354</v>
       </c>
       <c r="R60" t="n">
-        <v>7340766</v>
+        <v>7341159</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6623,6 +6627,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6637,22 +6646,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125378905</v>
+        <v>125374080</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6660,41 +6669,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>780354</v>
+        <v>780787</v>
       </c>
       <c r="R61" t="n">
-        <v>7341159</v>
+        <v>7340766</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6724,11 +6729,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ring hack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6743,44 +6743,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125374078</v>
+        <v>125378911</v>
       </c>
       <c r="B62" t="n">
-        <v>78991</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780705</v>
+        <v>780332</v>
       </c>
       <c r="R62" t="n">
-        <v>7340829</v>
+        <v>7341195</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6826,6 +6826,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6840,44 +6845,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125378911</v>
+        <v>125374078</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>78992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6887,13 +6892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780332</v>
+        <v>780705</v>
       </c>
       <c r="R63" t="n">
-        <v>7341195</v>
+        <v>7340829</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6923,11 +6928,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6942,12 +6942,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7060,45 +7060,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125368566</v>
+        <v>125374111</v>
       </c>
       <c r="B65" t="n">
-        <v>90265</v>
+        <v>98334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780905</v>
+        <v>780311</v>
       </c>
       <c r="R65" t="n">
-        <v>7340863</v>
+        <v>7341211</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7133,6 +7133,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7145,22 +7150,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125374111</v>
+        <v>125368579</v>
       </c>
       <c r="B66" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7188,14 +7193,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780311</v>
+        <v>780564</v>
       </c>
       <c r="R66" t="n">
-        <v>7341211</v>
+        <v>7341334</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7230,11 +7235,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7247,44 +7247,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125368579</v>
+        <v>125368566</v>
       </c>
       <c r="B67" t="n">
-        <v>98331</v>
+        <v>90266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780564</v>
+        <v>780905</v>
       </c>
       <c r="R67" t="n">
-        <v>7341334</v>
+        <v>7340863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>125378919</v>
       </c>
       <c r="B68" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>125368582</v>
       </c>
       <c r="B69" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125376197</v>
+        <v>125368586</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780912</v>
+        <v>780564</v>
       </c>
       <c r="R70" t="n">
-        <v>7340859</v>
+        <v>7341334</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7640,22 +7640,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125368586</v>
+        <v>125376197</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7663,21 +7663,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780564</v>
+        <v>780912</v>
       </c>
       <c r="R71" t="n">
-        <v>7341334</v>
+        <v>7340859</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,44 +7737,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125376201</v>
+        <v>125368595</v>
       </c>
       <c r="B72" t="n">
-        <v>98331</v>
+        <v>78374</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>780318</v>
+        <v>780561</v>
       </c>
       <c r="R72" t="n">
-        <v>7341215</v>
+        <v>7340968</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7834,44 +7834,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125368595</v>
+        <v>125374127</v>
       </c>
       <c r="B73" t="n">
-        <v>78373</v>
+        <v>56843</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7881,13 +7881,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>780561</v>
+        <v>780447</v>
       </c>
       <c r="R73" t="n">
-        <v>7340968</v>
+        <v>7341241</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7917,6 +7917,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7931,44 +7936,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374127</v>
+        <v>125376201</v>
       </c>
       <c r="B74" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7978,13 +7983,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>780447</v>
+        <v>780318</v>
       </c>
       <c r="R74" t="n">
-        <v>7341241</v>
+        <v>7341215</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8014,11 +8019,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8033,22 +8033,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125368568</v>
+        <v>125374116</v>
       </c>
       <c r="B75" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8056,34 +8056,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780597</v>
+        <v>780554</v>
       </c>
       <c r="R75" t="n">
-        <v>7341251</v>
+        <v>7340907</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,57 +8130,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125374116</v>
+        <v>125368591</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780554</v>
+        <v>780620</v>
       </c>
       <c r="R76" t="n">
-        <v>7340907</v>
+        <v>7340897</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8227,44 +8227,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125368591</v>
+        <v>125374090</v>
       </c>
       <c r="B77" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>780620</v>
+        <v>780353</v>
       </c>
       <c r="R77" t="n">
-        <v>7340897</v>
+        <v>7341186</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8324,22 +8324,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374090</v>
+        <v>125368568</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>780353</v>
+        <v>780597</v>
       </c>
       <c r="R78" t="n">
-        <v>7341186</v>
+        <v>7341251</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8421,12 +8421,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8436,7 +8436,7 @@
         <v>125376205</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>125374099</v>
       </c>
       <c r="B80" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>125420111</v>
       </c>
       <c r="B81" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>125420107</v>
       </c>
       <c r="B83" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>125420113</v>
       </c>
       <c r="B84" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420098</v>
+        <v>125420110</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>92546</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9140,21 +9140,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780771</v>
+        <v>780581</v>
       </c>
       <c r="R86" t="n">
-        <v>7340901</v>
+        <v>7340927</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9200,11 +9200,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9231,10 +9226,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420110</v>
+        <v>125420098</v>
       </c>
       <c r="B87" t="n">
-        <v>92537</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9242,21 +9237,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9266,10 +9261,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780581</v>
+        <v>780771</v>
       </c>
       <c r="R87" t="n">
-        <v>7340927</v>
+        <v>7340901</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9302,6 +9297,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9331,7 +9331,7 @@
         <v>125420109</v>
       </c>
       <c r="B88" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>125420114</v>
       </c>
       <c r="B90" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>125420097</v>
       </c>
       <c r="B91" t="n">
-        <v>90265</v>
+        <v>90266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -5965,10 +5965,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374084</v>
+        <v>125378928</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5976,21 +5976,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,13 +6000,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780527</v>
+        <v>780881</v>
       </c>
       <c r="R54" t="n">
-        <v>7341044</v>
+        <v>7340820</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6050,22 +6050,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125378928</v>
+        <v>125374105</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>91248</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,37 +6073,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780881</v>
+        <v>780579</v>
       </c>
       <c r="R55" t="n">
-        <v>7340820</v>
+        <v>7341020</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,60 +6147,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374105</v>
+        <v>125374125</v>
       </c>
       <c r="B56" t="n">
-        <v>91248</v>
+        <v>91638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780579</v>
+        <v>780339</v>
       </c>
       <c r="R56" t="n">
-        <v>7341020</v>
+        <v>7341191</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6244,44 +6244,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374125</v>
+        <v>125374084</v>
       </c>
       <c r="B57" t="n">
-        <v>91638</v>
+        <v>78726</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4217</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780339</v>
+        <v>780527</v>
       </c>
       <c r="R57" t="n">
-        <v>7341191</v>
+        <v>7341044</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6341,12 +6341,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7454,48 +7454,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368582</v>
+        <v>125368586</v>
       </c>
       <c r="B69" t="n">
-        <v>91389</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780634</v>
+        <v>780564</v>
       </c>
       <c r="R69" t="n">
-        <v>7340886</v>
+        <v>7341334</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7536,7 +7533,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7555,10 +7551,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125368586</v>
+        <v>125376197</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7566,21 +7562,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7590,10 +7586,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780564</v>
+        <v>780912</v>
       </c>
       <c r="R70" t="n">
-        <v>7341334</v>
+        <v>7340859</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7640,57 +7636,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125376197</v>
+        <v>125368582</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>91389</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780912</v>
+        <v>780634</v>
       </c>
       <c r="R71" t="n">
-        <v>7340859</v>
+        <v>7340886</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,18 +7730,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125368563</v>
       </c>
       <c r="B11" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125368562</v>
       </c>
       <c r="B12" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>125374094</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>125374088</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125368592</v>
+        <v>125374075</v>
       </c>
       <c r="B15" t="n">
-        <v>75059</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,34 +2118,54 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780845</v>
+        <v>780877</v>
       </c>
       <c r="R15" t="n">
-        <v>7340863</v>
+        <v>7340946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,9 +2195,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,77 +2222,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125374075</v>
+        <v>125376199</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780877</v>
+        <v>780542</v>
       </c>
       <c r="R16" t="n">
-        <v>7340946</v>
+        <v>7341352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,19 +2302,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,12 +2319,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
         <v>125378929</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,32 +2428,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125378930</v>
+        <v>125368592</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>75059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780354</v>
+        <v>780845</v>
       </c>
       <c r="R18" t="n">
-        <v>7341240</v>
+        <v>7340863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2513,44 +2513,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125376199</v>
+        <v>125378930</v>
       </c>
       <c r="B19" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780542</v>
+        <v>780354</v>
       </c>
       <c r="R19" t="n">
-        <v>7341352</v>
+        <v>7341240</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,22 +2610,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368593</v>
+        <v>125374108</v>
       </c>
       <c r="B20" t="n">
-        <v>77917</v>
+        <v>91528</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,34 +2633,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780561</v>
+        <v>780597</v>
       </c>
       <c r="R20" t="n">
-        <v>7340968</v>
+        <v>7341251</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125374086</v>
+        <v>125368564</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>90270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780521</v>
+        <v>780518</v>
       </c>
       <c r="R21" t="n">
-        <v>7341051</v>
+        <v>7341011</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,22 +2804,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125378906</v>
+        <v>125374086</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,13 +2851,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780955</v>
+        <v>780521</v>
       </c>
       <c r="R22" t="n">
-        <v>7340788</v>
+        <v>7341051</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2901,22 +2901,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125374108</v>
+        <v>125368593</v>
       </c>
       <c r="B23" t="n">
-        <v>91524</v>
+        <v>77921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,34 +2924,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780597</v>
+        <v>780561</v>
       </c>
       <c r="R23" t="n">
-        <v>7341251</v>
+        <v>7340968</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,22 +2998,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125368564</v>
+        <v>125378906</v>
       </c>
       <c r="B24" t="n">
-        <v>90266</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,21 +3021,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780518</v>
+        <v>780955</v>
       </c>
       <c r="R24" t="n">
-        <v>7341011</v>
+        <v>7340788</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3095,22 +3095,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125378902</v>
+        <v>125374124</v>
       </c>
       <c r="B25" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780545</v>
+        <v>780876</v>
       </c>
       <c r="R25" t="n">
-        <v>7341029</v>
+        <v>7340837</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3192,22 +3192,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374124</v>
+        <v>125378902</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3215,21 +3215,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780876</v>
+        <v>780545</v>
       </c>
       <c r="R26" t="n">
-        <v>7340837</v>
+        <v>7341029</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3289,12 +3289,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
         <v>125368580</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>125368569</v>
       </c>
       <c r="B28" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,32 +3597,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125374129</v>
+        <v>125374109</v>
       </c>
       <c r="B30" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3632,13 +3632,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780323</v>
+        <v>780890</v>
       </c>
       <c r="R30" t="n">
-        <v>7341197</v>
+        <v>7340825</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3668,6 +3668,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3682,44 +3687,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374123</v>
+        <v>125374129</v>
       </c>
       <c r="B31" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,13 +3734,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780428</v>
+        <v>780323</v>
       </c>
       <c r="R31" t="n">
-        <v>7341058</v>
+        <v>7341197</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3765,11 +3770,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3784,44 +3784,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125368571</v>
+        <v>125374123</v>
       </c>
       <c r="B32" t="n">
-        <v>92546</v>
+        <v>92522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780646</v>
+        <v>780428</v>
       </c>
       <c r="R32" t="n">
-        <v>7340861</v>
+        <v>7341058</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3869,6 +3869,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3881,44 +3886,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125368587</v>
+        <v>125376207</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3928,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780344</v>
+        <v>780564</v>
       </c>
       <c r="R33" t="n">
-        <v>7341144</v>
+        <v>7340973</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,22 +3983,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125378924</v>
+        <v>125368571</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>92550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4001,21 +4006,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4025,13 +4030,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780766</v>
+        <v>780646</v>
       </c>
       <c r="R34" t="n">
-        <v>7340885</v>
+        <v>7340861</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4075,44 +4080,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125376207</v>
+        <v>125368587</v>
       </c>
       <c r="B35" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4122,10 +4127,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780564</v>
+        <v>780344</v>
       </c>
       <c r="R35" t="n">
-        <v>7340973</v>
+        <v>7341144</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4172,44 +4177,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374109</v>
+        <v>125378924</v>
       </c>
       <c r="B36" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4219,13 +4224,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780890</v>
+        <v>780766</v>
       </c>
       <c r="R36" t="n">
-        <v>7340825</v>
+        <v>7340885</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4255,11 +4260,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4274,12 +4274,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
         <v>125378920</v>
       </c>
       <c r="B37" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4384,45 +4384,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374103</v>
+        <v>125368573</v>
       </c>
       <c r="B38" t="n">
-        <v>56843</v>
+        <v>91528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780777</v>
+        <v>780591</v>
       </c>
       <c r="R38" t="n">
-        <v>7340841</v>
+        <v>7341254</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,11 +4457,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4474,44 +4469,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125378926</v>
+        <v>125374118</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780493</v>
+        <v>780370</v>
       </c>
       <c r="R39" t="n">
-        <v>7341109</v>
+        <v>7341315</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4557,6 +4552,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4571,44 +4571,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125374118</v>
+        <v>125378926</v>
       </c>
       <c r="B40" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,13 +4618,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780370</v>
+        <v>780493</v>
       </c>
       <c r="R40" t="n">
-        <v>7341315</v>
+        <v>7341109</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4654,11 +4654,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4673,12 +4668,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4688,7 +4683,7 @@
         <v>125368584</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4782,45 +4777,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125368573</v>
+        <v>125374103</v>
       </c>
       <c r="B42" t="n">
-        <v>91524</v>
+        <v>56843</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780591</v>
+        <v>780777</v>
       </c>
       <c r="R42" t="n">
-        <v>7341254</v>
+        <v>7340841</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,6 +4850,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4867,12 +4867,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4882,7 +4882,7 @@
         <v>125376203</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>125374131</v>
       </c>
       <c r="B44" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>125374132</v>
       </c>
       <c r="B45" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>125374119</v>
       </c>
       <c r="B46" t="n">
-        <v>91638</v>
+        <v>91642</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5272,32 +5272,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374096</v>
+        <v>125368575</v>
       </c>
       <c r="B47" t="n">
-        <v>92518</v>
+        <v>92714</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780394</v>
+        <v>780910</v>
       </c>
       <c r="R47" t="n">
-        <v>7341123</v>
+        <v>7340862</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,44 +5357,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125368575</v>
+        <v>125374096</v>
       </c>
       <c r="B48" t="n">
-        <v>92710</v>
+        <v>92522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780910</v>
+        <v>780394</v>
       </c>
       <c r="R48" t="n">
-        <v>7340862</v>
+        <v>7341123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,60 +5454,64 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125368577</v>
+        <v>125378916</v>
       </c>
       <c r="B49" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780480</v>
+        <v>780956</v>
       </c>
       <c r="R49" t="n">
-        <v>7341033</v>
+        <v>7340785</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5537,6 +5541,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5551,22 +5560,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374092</v>
+        <v>125368590</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,21 +5583,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5607,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780743</v>
+        <v>780707</v>
       </c>
       <c r="R50" t="n">
-        <v>7340811</v>
+        <v>7340834</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,64 +5657,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125378916</v>
+        <v>125368577</v>
       </c>
       <c r="B51" t="n">
-        <v>56843</v>
+        <v>78730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780956</v>
+        <v>780480</v>
       </c>
       <c r="R51" t="n">
-        <v>7340785</v>
+        <v>7341033</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5735,11 +5740,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5754,57 +5754,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374114</v>
+        <v>125374092</v>
       </c>
       <c r="B52" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780332</v>
+        <v>780743</v>
       </c>
       <c r="R52" t="n">
-        <v>7341182</v>
+        <v>7340811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5839,11 +5839,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5856,57 +5851,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125368590</v>
+        <v>125374114</v>
       </c>
       <c r="B53" t="n">
-        <v>78635</v>
+        <v>98338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>780707</v>
+        <v>780332</v>
       </c>
       <c r="R53" t="n">
-        <v>7340834</v>
+        <v>7341182</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5941,6 +5936,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Bladrosett. Inom ett område på ca 10kvm 50 tal</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5953,44 +5953,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125378928</v>
+        <v>125374125</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>91642</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780881</v>
+        <v>780339</v>
       </c>
       <c r="R54" t="n">
-        <v>7340820</v>
+        <v>7341191</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6050,22 +6050,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374105</v>
+        <v>125378928</v>
       </c>
       <c r="B55" t="n">
-        <v>91248</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,37 +6073,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780579</v>
+        <v>780881</v>
       </c>
       <c r="R55" t="n">
-        <v>7341020</v>
+        <v>7340820</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,60 +6147,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374125</v>
+        <v>125374105</v>
       </c>
       <c r="B56" t="n">
-        <v>91638</v>
+        <v>91252</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780339</v>
+        <v>780579</v>
       </c>
       <c r="R56" t="n">
-        <v>7341191</v>
+        <v>7341020</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6244,12 +6244,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
         <v>125374084</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>125368578</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>125374080</v>
       </c>
       <c r="B61" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125378911</v>
+        <v>125374078</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>78996</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>780332</v>
+        <v>780705</v>
       </c>
       <c r="R62" t="n">
-        <v>7341195</v>
+        <v>7340829</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6826,11 +6826,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6845,44 +6840,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125374078</v>
+        <v>125378911</v>
       </c>
       <c r="B63" t="n">
-        <v>78992</v>
+        <v>57651</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6892,13 +6887,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>780705</v>
+        <v>780332</v>
       </c>
       <c r="R63" t="n">
-        <v>7340829</v>
+        <v>7341195</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6928,6 +6923,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6942,64 +6942,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125378917</v>
+        <v>125374111</v>
       </c>
       <c r="B64" t="n">
-        <v>56843</v>
+        <v>98338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780909</v>
+        <v>780311</v>
       </c>
       <c r="R64" t="n">
-        <v>7340823</v>
+        <v>7341211</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7033,7 +7029,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7048,22 +7044,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374111</v>
+        <v>125368579</v>
       </c>
       <c r="B65" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7091,14 +7087,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780311</v>
+        <v>780564</v>
       </c>
       <c r="R65" t="n">
-        <v>7341211</v>
+        <v>7341334</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7133,11 +7129,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7150,60 +7141,64 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125368579</v>
+        <v>125378917</v>
       </c>
       <c r="B66" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780564</v>
+        <v>780909</v>
       </c>
       <c r="R66" t="n">
-        <v>7341334</v>
+        <v>7340823</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7233,6 +7228,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7247,12 +7247,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7262,7 +7262,7 @@
         <v>125368566</v>
       </c>
       <c r="B67" t="n">
-        <v>90266</v>
+        <v>90270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>125378919</v>
       </c>
       <c r="B68" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>125368586</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7551,45 +7551,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125376197</v>
+        <v>125368582</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>91393</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780912</v>
+        <v>780634</v>
       </c>
       <c r="R70" t="n">
-        <v>7340859</v>
+        <v>7340886</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7630,66 +7633,64 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125368582</v>
+        <v>125376197</v>
       </c>
       <c r="B71" t="n">
-        <v>91389</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780634</v>
+        <v>780912</v>
       </c>
       <c r="R71" t="n">
-        <v>7340886</v>
+        <v>7340859</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7730,19 +7731,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
         <v>125368595</v>
       </c>
       <c r="B72" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>125376201</v>
       </c>
       <c r="B74" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8045,45 +8045,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374116</v>
+        <v>125368591</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>780554</v>
+        <v>780620</v>
       </c>
       <c r="R75" t="n">
-        <v>7340907</v>
+        <v>7340897</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,57 +8130,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125368591</v>
+        <v>125374116</v>
       </c>
       <c r="B76" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>780620</v>
+        <v>780554</v>
       </c>
       <c r="R76" t="n">
-        <v>7340897</v>
+        <v>7340907</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8227,12 +8227,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
         <v>125374090</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>125368568</v>
       </c>
       <c r="B78" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>125376205</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>125374099</v>
       </c>
       <c r="B80" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8627,45 +8627,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420111</v>
+        <v>125420106</v>
       </c>
       <c r="B81" t="n">
-        <v>92710</v>
+        <v>56843</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780605</v>
+        <v>780582</v>
       </c>
       <c r="R81" t="n">
-        <v>7340903</v>
+        <v>7340956</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8724,53 +8732,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420106</v>
+        <v>125420111</v>
       </c>
       <c r="B82" t="n">
-        <v>56843</v>
+        <v>92714</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780582</v>
+        <v>780605</v>
       </c>
       <c r="R82" t="n">
-        <v>7340956</v>
+        <v>7340903</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8832,7 +8832,7 @@
         <v>125420107</v>
       </c>
       <c r="B83" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>125420113</v>
       </c>
       <c r="B84" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>125420110</v>
       </c>
       <c r="B86" t="n">
-        <v>92546</v>
+        <v>92550</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>125420098</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>125420109</v>
       </c>
       <c r="B88" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>125420114</v>
       </c>
       <c r="B90" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>125420097</v>
       </c>
       <c r="B91" t="n">
-        <v>90266</v>
+        <v>90270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3403,32 +3403,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125368569</v>
+        <v>125368574</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>56846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780564</v>
+        <v>780624</v>
       </c>
       <c r="R28" t="n">
-        <v>7341334</v>
+        <v>7340950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,32 +3500,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125368574</v>
+        <v>125368569</v>
       </c>
       <c r="B29" t="n">
-        <v>56846</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780624</v>
+        <v>780564</v>
       </c>
       <c r="R29" t="n">
-        <v>7340950</v>
+        <v>7341334</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125368573</v>
+        <v>125376203</v>
       </c>
       <c r="B38" t="n">
-        <v>91528</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780591</v>
+        <v>780331</v>
       </c>
       <c r="R38" t="n">
-        <v>7341254</v>
+        <v>7341207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,44 +4469,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374118</v>
+        <v>125374131</v>
       </c>
       <c r="B39" t="n">
-        <v>92522</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780370</v>
+        <v>780341</v>
       </c>
       <c r="R39" t="n">
-        <v>7341315</v>
+        <v>7341192</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,11 +4552,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>4 st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4571,22 +4566,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125378926</v>
+        <v>125368573</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>91528</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4594,21 +4589,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,13 +4613,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>780493</v>
+        <v>780591</v>
       </c>
       <c r="R40" t="n">
-        <v>7341109</v>
+        <v>7341254</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4668,44 +4663,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125368584</v>
+        <v>125374118</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4715,10 +4710,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780566</v>
+        <v>780370</v>
       </c>
       <c r="R41" t="n">
-        <v>7341030</v>
+        <v>7341315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,6 +4748,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4765,60 +4765,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374103</v>
+        <v>125378926</v>
       </c>
       <c r="B42" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780777</v>
+        <v>780493</v>
       </c>
       <c r="R42" t="n">
-        <v>7340841</v>
+        <v>7341109</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4848,11 +4848,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4867,44 +4862,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125376203</v>
+        <v>125368584</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4914,10 +4909,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780331</v>
+        <v>780566</v>
       </c>
       <c r="R43" t="n">
-        <v>7341207</v>
+        <v>7341030</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4964,60 +4959,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374131</v>
+        <v>125374103</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780341</v>
+        <v>780777</v>
       </c>
       <c r="R44" t="n">
-        <v>7341192</v>
+        <v>7340841</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5047,6 +5042,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5061,12 +5061,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5272,32 +5272,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125368575</v>
+        <v>125374096</v>
       </c>
       <c r="B47" t="n">
-        <v>92714</v>
+        <v>92522</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780910</v>
+        <v>780394</v>
       </c>
       <c r="R47" t="n">
-        <v>7340862</v>
+        <v>7341123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,44 +5357,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125374096</v>
+        <v>125368575</v>
       </c>
       <c r="B48" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780394</v>
+        <v>780910</v>
       </c>
       <c r="R48" t="n">
-        <v>7341123</v>
+        <v>7340862</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,64 +5454,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125378916</v>
+        <v>125368590</v>
       </c>
       <c r="B49" t="n">
-        <v>56843</v>
+        <v>78639</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780956</v>
+        <v>780707</v>
       </c>
       <c r="R49" t="n">
-        <v>7340785</v>
+        <v>7340834</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5541,11 +5537,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5560,22 +5551,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125368590</v>
+        <v>125368577</v>
       </c>
       <c r="B50" t="n">
-        <v>78639</v>
+        <v>78730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5583,21 +5574,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5607,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780707</v>
+        <v>780480</v>
       </c>
       <c r="R50" t="n">
-        <v>7340834</v>
+        <v>7341033</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5669,10 +5660,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125368577</v>
+        <v>125374092</v>
       </c>
       <c r="B51" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5680,21 +5671,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5704,10 +5695,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780480</v>
+        <v>780743</v>
       </c>
       <c r="R51" t="n">
-        <v>7341033</v>
+        <v>7340811</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5754,60 +5745,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125374092</v>
+        <v>125378916</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>780743</v>
+        <v>780956</v>
       </c>
       <c r="R52" t="n">
-        <v>7340811</v>
+        <v>7340785</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5837,6 +5832,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5851,12 +5851,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5965,32 +5965,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374125</v>
+        <v>125378928</v>
       </c>
       <c r="B54" t="n">
-        <v>91642</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780339</v>
+        <v>780881</v>
       </c>
       <c r="R54" t="n">
-        <v>7341191</v>
+        <v>7340820</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6050,22 +6050,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125378928</v>
+        <v>125374105</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,37 +6073,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780881</v>
+        <v>780579</v>
       </c>
       <c r="R55" t="n">
-        <v>7340820</v>
+        <v>7341020</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,22 +6147,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374105</v>
+        <v>125374084</v>
       </c>
       <c r="B56" t="n">
-        <v>91252</v>
+        <v>78730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,34 +6170,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780579</v>
+        <v>780527</v>
       </c>
       <c r="R56" t="n">
-        <v>7341020</v>
+        <v>7341044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,44 +6244,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374084</v>
+        <v>125374125</v>
       </c>
       <c r="B57" t="n">
-        <v>78730</v>
+        <v>91642</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4217</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780527</v>
+        <v>780339</v>
       </c>
       <c r="R57" t="n">
-        <v>7341044</v>
+        <v>7341191</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6341,12 +6341,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7454,45 +7454,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368586</v>
+        <v>125368582</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780564</v>
+        <v>780634</v>
       </c>
       <c r="R69" t="n">
-        <v>7341334</v>
+        <v>7340886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7533,6 +7536,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7551,48 +7555,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125368582</v>
+        <v>125376197</v>
       </c>
       <c r="B70" t="n">
-        <v>91393</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>780634</v>
+        <v>780912</v>
       </c>
       <c r="R70" t="n">
-        <v>7340886</v>
+        <v>7340859</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7633,29 +7634,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125376197</v>
+        <v>125368586</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7663,21 +7663,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780912</v>
+        <v>780564</v>
       </c>
       <c r="R71" t="n">
-        <v>7340859</v>
+        <v>7341334</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,12 +7737,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420110</v>
+        <v>125420098</v>
       </c>
       <c r="B86" t="n">
-        <v>92550</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9140,21 +9140,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780581</v>
+        <v>780771</v>
       </c>
       <c r="R86" t="n">
-        <v>7340927</v>
+        <v>7340901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9200,6 +9200,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9226,10 +9231,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420098</v>
+        <v>125420110</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>92550</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9237,21 +9242,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9261,10 +9266,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780771</v>
+        <v>780581</v>
       </c>
       <c r="R87" t="n">
-        <v>7340901</v>
+        <v>7340927</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9297,11 +9302,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125374075</v>
+        <v>125378929</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,57 +2118,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780877</v>
+        <v>780910</v>
       </c>
       <c r="R15" t="n">
-        <v>7340946</v>
+        <v>7340820</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,19 +2175,9 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,44 +2192,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125376199</v>
+        <v>125368592</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>75059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780542</v>
+        <v>780845</v>
       </c>
       <c r="R16" t="n">
-        <v>7341352</v>
+        <v>7340863</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,22 +2289,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125378929</v>
+        <v>125374075</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,37 +2312,57 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780910</v>
+        <v>780877</v>
       </c>
       <c r="R17" t="n">
-        <v>7340820</v>
+        <v>7340946</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2399,9 +2389,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,44 +2416,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125368592</v>
+        <v>125378930</v>
       </c>
       <c r="B18" t="n">
-        <v>75059</v>
+        <v>92522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780845</v>
+        <v>780354</v>
       </c>
       <c r="R18" t="n">
-        <v>7340863</v>
+        <v>7341240</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2513,44 +2513,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125378930</v>
+        <v>125376199</v>
       </c>
       <c r="B19" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780354</v>
+        <v>780542</v>
       </c>
       <c r="R19" t="n">
-        <v>7341240</v>
+        <v>7341352</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,22 +2610,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374108</v>
+        <v>125368564</v>
       </c>
       <c r="B20" t="n">
-        <v>91528</v>
+        <v>90270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,34 +2633,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780597</v>
+        <v>780518</v>
       </c>
       <c r="R20" t="n">
-        <v>7341251</v>
+        <v>7341011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368564</v>
+        <v>125368593</v>
       </c>
       <c r="B21" t="n">
-        <v>90270</v>
+        <v>77921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>780518</v>
+        <v>780561</v>
       </c>
       <c r="R21" t="n">
-        <v>7341011</v>
+        <v>7340968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125368593</v>
+        <v>125374108</v>
       </c>
       <c r="B23" t="n">
-        <v>77921</v>
+        <v>91528</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,34 +2924,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780561</v>
+        <v>780597</v>
       </c>
       <c r="R23" t="n">
-        <v>7340968</v>
+        <v>7341251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,12 +2998,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125374124</v>
+        <v>125378902</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780876</v>
+        <v>780545</v>
       </c>
       <c r="R25" t="n">
-        <v>7340837</v>
+        <v>7341029</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3192,22 +3192,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125378902</v>
+        <v>125374124</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3215,21 +3215,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>780545</v>
+        <v>780876</v>
       </c>
       <c r="R26" t="n">
-        <v>7341029</v>
+        <v>7340837</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3289,12 +3289,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
         <v>125368580</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125368574</v>
+        <v>125368569</v>
       </c>
       <c r="B28" t="n">
-        <v>56846</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780624</v>
+        <v>780564</v>
       </c>
       <c r="R28" t="n">
-        <v>7340950</v>
+        <v>7341334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,32 +3500,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125368569</v>
+        <v>125368574</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>56846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>780564</v>
+        <v>780624</v>
       </c>
       <c r="R29" t="n">
-        <v>7341334</v>
+        <v>7340950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125374109</v>
+        <v>125374123</v>
       </c>
       <c r="B30" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,21 +3608,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>780890</v>
+        <v>780428</v>
       </c>
       <c r="R30" t="n">
-        <v>7340825</v>
+        <v>7341058</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Tjäderspillning</t>
+          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3687,44 +3687,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374129</v>
+        <v>125376207</v>
       </c>
       <c r="B31" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>780323</v>
+        <v>780564</v>
       </c>
       <c r="R31" t="n">
-        <v>7341197</v>
+        <v>7340973</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3784,44 +3784,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125374123</v>
+        <v>125368571</v>
       </c>
       <c r="B32" t="n">
-        <v>92522</v>
+        <v>92550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>780428</v>
+        <v>780646</v>
       </c>
       <c r="R32" t="n">
-        <v>7341058</v>
+        <v>7340861</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3869,11 +3869,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer i häxring uppskattningsvis 15 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3886,44 +3881,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125376207</v>
+        <v>125368587</v>
       </c>
       <c r="B33" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3933,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>780564</v>
+        <v>780344</v>
       </c>
       <c r="R33" t="n">
-        <v>7340973</v>
+        <v>7341144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3983,22 +3978,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125368571</v>
+        <v>125378924</v>
       </c>
       <c r="B34" t="n">
-        <v>92550</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4006,21 +4001,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4030,13 +4025,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>780646</v>
+        <v>780766</v>
       </c>
       <c r="R34" t="n">
-        <v>7340861</v>
+        <v>7340885</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4080,44 +4075,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125368587</v>
+        <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4127,10 +4122,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>780344</v>
+        <v>780890</v>
       </c>
       <c r="R35" t="n">
-        <v>7341144</v>
+        <v>7340825</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,6 +4160,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4177,44 +4177,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125378924</v>
+        <v>125374129</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>780766</v>
+        <v>780323</v>
       </c>
       <c r="R36" t="n">
-        <v>7340885</v>
+        <v>7341197</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4274,12 +4274,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4384,32 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125376203</v>
+        <v>125378926</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>780331</v>
+        <v>780493</v>
       </c>
       <c r="R38" t="n">
-        <v>7341207</v>
+        <v>7341109</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4469,44 +4469,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374131</v>
+        <v>125368584</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>780341</v>
+        <v>780566</v>
       </c>
       <c r="R39" t="n">
-        <v>7341192</v>
+        <v>7341030</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4566,12 +4566,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374118</v>
+        <v>125374103</v>
       </c>
       <c r="B41" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4686,34 +4686,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>780370</v>
+        <v>780777</v>
       </c>
       <c r="R41" t="n">
-        <v>7341315</v>
+        <v>7340841</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4765,44 +4765,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristina Berglund</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125378926</v>
+        <v>125376203</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>780493</v>
+        <v>780331</v>
       </c>
       <c r="R42" t="n">
-        <v>7341109</v>
+        <v>7341207</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4862,44 +4862,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125368584</v>
+        <v>125374131</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>780566</v>
+        <v>780341</v>
       </c>
       <c r="R43" t="n">
-        <v>7341030</v>
+        <v>7341192</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4959,22 +4959,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374103</v>
+        <v>125374118</v>
       </c>
       <c r="B44" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4982,34 +4982,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>780777</v>
+        <v>780370</v>
       </c>
       <c r="R44" t="n">
-        <v>7340841</v>
+        <v>7341315</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5061,12 +5061,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Kristina Berglund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5272,32 +5272,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374096</v>
+        <v>125368575</v>
       </c>
       <c r="B47" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>780394</v>
+        <v>780910</v>
       </c>
       <c r="R47" t="n">
-        <v>7341123</v>
+        <v>7340862</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,44 +5357,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125368575</v>
+        <v>125374096</v>
       </c>
       <c r="B48" t="n">
-        <v>92714</v>
+        <v>92522</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>780910</v>
+        <v>780394</v>
       </c>
       <c r="R48" t="n">
-        <v>7340862</v>
+        <v>7341123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,22 +5454,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125368590</v>
+        <v>125368577</v>
       </c>
       <c r="B49" t="n">
-        <v>78639</v>
+        <v>78730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5477,21 +5477,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>780707</v>
+        <v>780480</v>
       </c>
       <c r="R49" t="n">
-        <v>7340834</v>
+        <v>7341033</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125368577</v>
+        <v>125374092</v>
       </c>
       <c r="B50" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>780480</v>
+        <v>780743</v>
       </c>
       <c r="R50" t="n">
-        <v>7341033</v>
+        <v>7340811</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,22 +5648,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125374092</v>
+        <v>125368590</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>780743</v>
+        <v>780707</v>
       </c>
       <c r="R51" t="n">
-        <v>7340811</v>
+        <v>7340834</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5745,12 +5745,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5866,7 +5866,7 @@
         <v>125374114</v>
       </c>
       <c r="B53" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5965,10 +5965,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125378928</v>
+        <v>125374105</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5976,37 +5976,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>780881</v>
+        <v>780579</v>
       </c>
       <c r="R54" t="n">
-        <v>7340820</v>
+        <v>7341020</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6050,60 +6050,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125374105</v>
+        <v>125374125</v>
       </c>
       <c r="B55" t="n">
-        <v>91252</v>
+        <v>91642</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>780579</v>
+        <v>780339</v>
       </c>
       <c r="R55" t="n">
-        <v>7341020</v>
+        <v>7341191</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6147,22 +6147,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125374084</v>
+        <v>125378928</v>
       </c>
       <c r="B56" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,21 +6170,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6194,13 +6194,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>780527</v>
+        <v>780881</v>
       </c>
       <c r="R56" t="n">
-        <v>7341044</v>
+        <v>7340820</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6244,44 +6244,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374125</v>
+        <v>125374084</v>
       </c>
       <c r="B57" t="n">
-        <v>91642</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4217</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>780339</v>
+        <v>780527</v>
       </c>
       <c r="R57" t="n">
-        <v>7341191</v>
+        <v>7341044</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6341,12 +6341,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6954,45 +6954,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374111</v>
+        <v>125368566</v>
       </c>
       <c r="B64" t="n">
-        <v>98338</v>
+        <v>90270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Boden, Dragträskberget, Nb</t>
+          <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>780311</v>
+        <v>780905</v>
       </c>
       <c r="R64" t="n">
-        <v>7341211</v>
+        <v>7340863</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7027,11 +7027,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7044,60 +7039,64 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maud Söderholm Häll</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125368579</v>
+        <v>125378917</v>
       </c>
       <c r="B65" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>780564</v>
+        <v>780909</v>
       </c>
       <c r="R65" t="n">
-        <v>7341334</v>
+        <v>7340823</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7127,6 +7126,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7141,64 +7145,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125378917</v>
+        <v>125374111</v>
       </c>
       <c r="B66" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Dragträskberget, Nb</t>
+          <t>Boden, Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>780909</v>
+        <v>780311</v>
       </c>
       <c r="R66" t="n">
-        <v>7340823</v>
+        <v>7341211</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bladrosetter 100-tal inom ett område på 5 kvm</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7247,44 +7247,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Maud Söderholm Häll</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125368566</v>
+        <v>125368579</v>
       </c>
       <c r="B67" t="n">
-        <v>90270</v>
+        <v>98339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>780905</v>
+        <v>780564</v>
       </c>
       <c r="R67" t="n">
-        <v>7340863</v>
+        <v>7341334</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7454,48 +7454,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125368582</v>
+        <v>125368586</v>
       </c>
       <c r="B69" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>780634</v>
+        <v>780564</v>
       </c>
       <c r="R69" t="n">
-        <v>7340886</v>
+        <v>7341334</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7536,7 +7533,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7652,45 +7648,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125368586</v>
+        <v>125368582</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>780564</v>
+        <v>780634</v>
       </c>
       <c r="R71" t="n">
-        <v>7341334</v>
+        <v>7340886</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,6 +7730,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>125376201</v>
       </c>
       <c r="B74" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125376205</v>
+        <v>125374099</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>780453</v>
+        <v>780470</v>
       </c>
       <c r="R79" t="n">
-        <v>7341309</v>
+        <v>7341026</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8518,44 +8518,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tobias Johansson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374099</v>
+        <v>125376205</v>
       </c>
       <c r="B80" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>780470</v>
+        <v>780453</v>
       </c>
       <c r="R80" t="n">
-        <v>7341026</v>
+        <v>7341309</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8615,65 +8615,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Tobias Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125420106</v>
+        <v>125420111</v>
       </c>
       <c r="B81" t="n">
-        <v>56843</v>
+        <v>92714</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>780582</v>
+        <v>780605</v>
       </c>
       <c r="R81" t="n">
-        <v>7340956</v>
+        <v>7340903</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8732,45 +8724,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125420111</v>
+        <v>125420106</v>
       </c>
       <c r="B82" t="n">
-        <v>92714</v>
+        <v>56843</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>780605</v>
+        <v>780582</v>
       </c>
       <c r="R82" t="n">
-        <v>7340903</v>
+        <v>7340956</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8929,7 +8929,7 @@
         <v>125420113</v>
       </c>
       <c r="B84" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9023,10 +9023,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125378914</v>
+        <v>125420098</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9034,41 +9034,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780360</v>
+        <v>780771</v>
       </c>
       <c r="R85" t="n">
-        <v>7341113</v>
+        <v>7340901</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9102,7 +9098,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Avskals gran</t>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9117,22 +9113,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420098</v>
+        <v>125420110</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>92550</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9140,21 +9136,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9164,10 +9160,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780771</v>
+        <v>780581</v>
       </c>
       <c r="R86" t="n">
-        <v>7340901</v>
+        <v>7340927</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9200,11 +9196,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9231,10 +9222,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125420110</v>
+        <v>125378914</v>
       </c>
       <c r="B87" t="n">
-        <v>92550</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9242,37 +9233,41 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780581</v>
+        <v>780360</v>
       </c>
       <c r="R87" t="n">
-        <v>7340927</v>
+        <v>7341113</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9302,6 +9297,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9316,12 +9316,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9023,10 +9023,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125420098</v>
+        <v>125378914</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9034,37 +9034,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>780771</v>
+        <v>780360</v>
       </c>
       <c r="R85" t="n">
-        <v>7340901</v>
+        <v>7341113</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>flera draperade granar</t>
+          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9113,22 +9117,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125420110</v>
+        <v>125420098</v>
       </c>
       <c r="B86" t="n">
-        <v>92550</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9136,21 +9140,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9160,10 +9164,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>780581</v>
+        <v>780771</v>
       </c>
       <c r="R86" t="n">
-        <v>7340927</v>
+        <v>7340901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9196,6 +9200,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>flera draperade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9222,10 +9231,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125378914</v>
+        <v>125420110</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>92550</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9233,41 +9242,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dragträskberget, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>780360</v>
+        <v>780581</v>
       </c>
       <c r="R87" t="n">
-        <v>7341113</v>
+        <v>7340927</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9297,11 +9302,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Avskals gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9316,12 +9316,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sofia Hagsand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9723,6 +9723,324 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129688582</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98757</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Svartlå, Nb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>780337</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7341195</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129688581</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98757</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Svartlå, Nb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>780323</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7341210</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129688550</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98757</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Svartlå, Nb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>780535</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7341352</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98757</v>
+        <v>98768</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98757</v>
+        <v>98768</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98757</v>
+        <v>98768</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -9728,7 +9728,7 @@
         <v>129688582</v>
       </c>
       <c r="B92" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129688581</v>
       </c>
       <c r="B93" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>129688550</v>
       </c>
       <c r="B94" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3503,7 +3503,7 @@
         <v>125368574</v>
       </c>
       <c r="B29" t="n">
-        <v>57019</v>
+        <v>57045</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>125374103</v>
       </c>
       <c r="B41" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>125378916</v>
       </c>
       <c r="B52" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>125378917</v>
       </c>
       <c r="B65" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>125374127</v>
       </c>
       <c r="B73" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>125420106</v>
       </c>
       <c r="B82" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3503,7 +3503,7 @@
         <v>125368574</v>
       </c>
       <c r="B29" t="n">
-        <v>57045</v>
+        <v>57047</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>125374103</v>
       </c>
       <c r="B41" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>125378916</v>
       </c>
       <c r="B52" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>125378917</v>
       </c>
       <c r="B65" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>125374127</v>
       </c>
       <c r="B73" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>125420106</v>
       </c>
       <c r="B82" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3503,7 +3503,7 @@
         <v>125368574</v>
       </c>
       <c r="B29" t="n">
-        <v>57047</v>
+        <v>57055</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>125374103</v>
       </c>
       <c r="B41" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>125378916</v>
       </c>
       <c r="B52" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>125378917</v>
       </c>
       <c r="B65" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>125374127</v>
       </c>
       <c r="B73" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>125420106</v>
       </c>
       <c r="B82" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18548-2025 artfynd.xlsx
+++ b/artfynd/A 18548-2025 artfynd.xlsx
@@ -3503,7 +3503,7 @@
         <v>125368574</v>
       </c>
       <c r="B29" t="n">
-        <v>57055</v>
+        <v>57056</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>125374109</v>
       </c>
       <c r="B35" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>125374103</v>
       </c>
       <c r="B41" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>125378916</v>
       </c>
       <c r="B52" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>125378917</v>
       </c>
       <c r="B65" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>125374127</v>
       </c>
       <c r="B73" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>125420106</v>
       </c>
       <c r="B82" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
